--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -635,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -667,12 +676,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="58" t="n">
+      <c r="B2" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -680,19 +689,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="D2" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="57" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="58" t="n">
+      <c r="B3" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -700,19 +709,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="59" t="inlineStr">
+      <c r="D3" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="57" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="58" t="n">
+      <c r="B4" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -720,19 +729,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -740,19 +749,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="58" t="n">
+      <c r="B6" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -760,19 +769,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="58" t="n">
+      <c r="B7" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -780,19 +789,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="57" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -800,19 +809,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="57" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="58" t="n">
+      <c r="B9" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -820,19 +829,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="57" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="58" t="n">
+      <c r="B10" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -840,19 +849,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="57" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="58" t="n">
+      <c r="B11" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -860,19 +869,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="58" t="n">
+      <c r="B12" s="61" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -880,19 +889,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="58" t="n">
+      <c r="B13" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -900,19 +909,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr">
+      <c r="D13" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n">
+      <c r="B14" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -920,19 +929,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B15" s="58" t="n">
+      <c r="B15" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -940,19 +949,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr">
+      <c r="D15" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="57" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="58" t="n">
+      <c r="B16" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -960,19 +969,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="D16" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="57" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="58" t="n">
+      <c r="B17" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -980,19 +989,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr">
+      <c r="D17" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="57" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="58" t="n">
+      <c r="B18" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1000,19 +1009,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="D18" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="57" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="58" t="n">
+      <c r="B19" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1020,19 +1029,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr">
+      <c r="D19" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="57" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="58" t="n">
+      <c r="B20" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1040,19 +1049,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr">
+      <c r="D20" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="57" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B21" s="58" t="n">
+      <c r="B21" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1060,19 +1069,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="59" t="inlineStr">
+      <c r="D21" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="57" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="58" t="n">
+      <c r="B22" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1080,19 +1089,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="59" t="inlineStr">
+      <c r="D22" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="57" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B23" s="58" t="n">
+      <c r="B23" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1100,19 +1109,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="59" t="inlineStr">
+      <c r="D23" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="57" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="58" t="n">
+      <c r="B24" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1120,19 +1129,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="59" t="inlineStr">
+      <c r="D24" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="57" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="58" t="n">
+      <c r="B25" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1140,19 +1149,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="59" t="inlineStr">
+      <c r="D25" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="57" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="58" t="n">
+      <c r="B26" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1160,19 +1169,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="59" t="inlineStr">
+      <c r="D26" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="57" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="58" t="n">
+      <c r="B27" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1180,19 +1189,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="59" t="inlineStr">
+      <c r="D27" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="57" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="58" t="n">
+      <c r="B28" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1200,19 +1209,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="59" t="inlineStr">
+      <c r="D28" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="57" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="58" t="n">
+      <c r="B29" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1220,19 +1229,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="59" t="inlineStr">
+      <c r="D29" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="57" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="58" t="n">
+      <c r="B30" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1240,19 +1249,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="59" t="inlineStr">
+      <c r="D30" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="57" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="58" t="n">
+      <c r="B31" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1260,19 +1269,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="59" t="inlineStr">
+      <c r="D31" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="57" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B32" s="58" t="n">
+      <c r="B32" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1280,19 +1289,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="59" t="inlineStr">
+      <c r="D32" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="57" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B33" s="58" t="n">
+      <c r="B33" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1300,19 +1309,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="59" t="inlineStr">
+      <c r="D33" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="57" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="58" t="n">
+      <c r="B34" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1320,19 +1329,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="59" t="inlineStr">
+      <c r="D34" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="57" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="58" t="n">
+      <c r="B35" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1340,19 +1349,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="59" t="inlineStr">
+      <c r="D35" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="57" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="58" t="n">
+      <c r="B36" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1360,19 +1369,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="59" t="inlineStr">
+      <c r="D36" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="57" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="58" t="n">
+      <c r="B37" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1380,19 +1389,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="59" t="inlineStr">
+      <c r="D37" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="57" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="58" t="n">
+      <c r="B38" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1400,19 +1409,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="59" t="inlineStr">
+      <c r="D38" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="57" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="58" t="n">
+      <c r="B39" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1420,19 +1429,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="59" t="inlineStr">
+      <c r="D39" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="57" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="58" t="n">
+      <c r="B40" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1440,19 +1449,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="59" t="inlineStr">
+      <c r="D40" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="57" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="58" t="n">
+      <c r="B41" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1460,19 +1469,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="59" t="inlineStr">
+      <c r="D41" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="57" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B42" s="58" t="n">
+      <c r="B42" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1480,19 +1489,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="59" t="inlineStr">
+      <c r="D42" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="57" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B43" s="58" t="n">
+      <c r="B43" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1500,19 +1509,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="59" t="inlineStr">
+      <c r="D43" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="57" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="58" t="n">
+      <c r="B44" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1520,19 +1529,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="59" t="inlineStr">
+      <c r="D44" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="57" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="58" t="n">
+      <c r="B45" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1540,19 +1549,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="59" t="inlineStr">
+      <c r="D45" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="57" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B46" s="58" t="n">
+      <c r="B46" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1560,19 +1569,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="59" t="inlineStr">
+      <c r="D46" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="57" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="58" t="n">
+      <c r="B47" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1580,19 +1589,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="59" t="inlineStr">
+      <c r="D47" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="57" t="inlineStr">
+      <c r="A48" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="58" t="n">
+      <c r="B48" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1600,19 +1609,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="59" t="inlineStr">
+      <c r="D48" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="57" t="inlineStr">
+      <c r="A49" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="58" t="n">
+      <c r="B49" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1620,19 +1629,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="59" t="inlineStr">
+      <c r="D49" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="57" t="inlineStr">
+      <c r="A50" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="58" t="n">
+      <c r="B50" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1640,19 +1649,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="59" t="inlineStr">
+      <c r="D50" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="57" t="inlineStr">
+      <c r="A51" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="58" t="n">
+      <c r="B51" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1660,19 +1669,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="59" t="inlineStr">
+      <c r="D51" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="57" t="inlineStr">
+      <c r="A52" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="58" t="n">
+      <c r="B52" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1680,19 +1689,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="59" t="inlineStr">
+      <c r="D52" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="57" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="58" t="n">
+      <c r="B53" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1700,19 +1709,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="59" t="inlineStr">
+      <c r="D53" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="57" t="inlineStr">
+      <c r="A54" s="60" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="58" t="n">
+      <c r="B54" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1720,19 +1729,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="59" t="inlineStr">
+      <c r="D54" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="57" t="inlineStr">
+      <c r="A55" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="58" t="n">
+      <c r="B55" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1740,19 +1749,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="59" t="inlineStr">
+      <c r="D55" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="57" t="inlineStr">
+      <c r="A56" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="58" t="n">
+      <c r="B56" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1760,19 +1769,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="59" t="inlineStr">
+      <c r="D56" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="57" t="inlineStr">
+      <c r="A57" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="58" t="n">
+      <c r="B57" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1780,19 +1789,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="59" t="inlineStr">
+      <c r="D57" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="57" t="inlineStr">
+      <c r="A58" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="58" t="n">
+      <c r="B58" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1800,19 +1809,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="59" t="inlineStr">
+      <c r="D58" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="57" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B59" s="58" t="n">
+      <c r="B59" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1820,19 +1829,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="59" t="inlineStr">
+      <c r="D59" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="57" t="inlineStr">
+      <c r="A60" s="60" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="58" t="n">
+      <c r="B60" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1840,19 +1849,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="59" t="inlineStr">
+      <c r="D60" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="57" t="inlineStr">
+      <c r="A61" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B61" s="58" t="n">
+      <c r="B61" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1860,19 +1869,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="59" t="inlineStr">
+      <c r="D61" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="57" t="inlineStr">
+      <c r="A62" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="58" t="n">
+      <c r="B62" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1880,19 +1889,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="59" t="inlineStr">
+      <c r="D62" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="57" t="inlineStr">
+      <c r="A63" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B63" s="58" t="n">
+      <c r="B63" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1900,19 +1909,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="59" t="inlineStr">
+      <c r="D63" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="57" t="inlineStr">
+      <c r="A64" s="60" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="58" t="n">
+      <c r="B64" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1920,19 +1929,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="59" t="inlineStr">
+      <c r="D64" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="57" t="inlineStr">
+      <c r="A65" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B65" s="58" t="n">
+      <c r="B65" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1940,19 +1949,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="59" t="inlineStr">
+      <c r="D65" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="57" t="inlineStr">
+      <c r="A66" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="58" t="n">
+      <c r="B66" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1960,19 +1969,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="59" t="inlineStr">
+      <c r="D66" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="57" t="inlineStr">
+      <c r="A67" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B67" s="58" t="n">
+      <c r="B67" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1980,19 +1989,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="59" t="inlineStr">
+      <c r="D67" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="57" t="inlineStr">
+      <c r="A68" s="60" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="58" t="n">
+      <c r="B68" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -2000,19 +2009,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="59" t="inlineStr">
+      <c r="D68" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="57" t="inlineStr">
+      <c r="A69" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="58" t="n">
+      <c r="B69" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2020,19 +2029,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="59" t="inlineStr">
+      <c r="D69" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="57" t="inlineStr">
+      <c r="A70" s="60" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="58" t="n">
+      <c r="B70" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2040,19 +2049,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="59" t="inlineStr">
+      <c r="D70" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="57" t="inlineStr">
+      <c r="A71" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="58" t="n">
+      <c r="B71" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2060,19 +2069,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="59" t="inlineStr">
+      <c r="D71" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="57" t="inlineStr">
+      <c r="A72" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="58" t="n">
+      <c r="B72" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2080,19 +2089,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="59" t="inlineStr">
+      <c r="D72" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="57" t="inlineStr">
+      <c r="A73" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="58" t="n">
+      <c r="B73" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2100,19 +2109,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="59" t="inlineStr">
+      <c r="D73" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="57" t="inlineStr">
+      <c r="A74" s="60" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="58" t="n">
+      <c r="B74" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2120,19 +2129,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="59" t="inlineStr">
+      <c r="D74" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="57" t="inlineStr">
+      <c r="A75" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="58" t="n">
+      <c r="B75" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2140,19 +2149,19 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="59" t="inlineStr">
+      <c r="D75" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="57" t="inlineStr">
+      <c r="A76" s="60" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B76" s="58" t="n">
+      <c r="B76" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2160,19 +2169,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D76" s="59" t="inlineStr">
+      <c r="D76" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="57" t="inlineStr">
+      <c r="A77" s="60" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B77" s="58" t="n">
+      <c r="B77" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2180,19 +2189,19 @@
           <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
         </is>
       </c>
-      <c r="D77" s="59" t="inlineStr">
+      <c r="D77" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765129/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="57" t="inlineStr">
+      <c r="A78" s="60" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="58" t="n">
+      <c r="B78" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2200,19 +2209,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D78" s="59" t="inlineStr">
+      <c r="D78" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="57" t="inlineStr">
+      <c r="A79" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B79" s="58" t="n">
+      <c r="B79" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2220,19 +2229,19 @@
           <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
-      <c r="D79" s="59" t="inlineStr">
+      <c r="D79" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="57" t="inlineStr">
+      <c r="A80" s="60" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B80" s="58" t="n">
+      <c r="B80" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2240,19 +2249,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D80" s="59" t="inlineStr">
+      <c r="D80" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="57" t="inlineStr">
+      <c r="A81" s="60" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B81" s="58" t="n">
+      <c r="B81" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2260,19 +2269,19 @@
           <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
         </is>
       </c>
-      <c r="D81" s="59" t="inlineStr">
+      <c r="D81" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450696746/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="57" t="inlineStr">
+      <c r="A82" s="60" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="58" t="n">
+      <c r="B82" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2280,19 +2289,19 @@
           <t>Logistics Analyst</t>
         </is>
       </c>
-      <c r="D82" s="59" t="inlineStr">
+      <c r="D82" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461266744/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="57" t="inlineStr">
+      <c r="A83" s="60" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B83" s="58" t="n">
+      <c r="B83" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2300,19 +2309,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D83" s="59" t="inlineStr">
+      <c r="D83" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="57" t="inlineStr">
+      <c r="A84" s="60" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B84" s="58" t="n">
+      <c r="B84" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2320,19 +2329,19 @@
           <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D84" s="59" t="inlineStr">
+      <c r="D84" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459309508/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="57" t="inlineStr">
+      <c r="A85" s="60" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" s="58" t="n">
+      <c r="B85" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2340,19 +2349,19 @@
           <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
         </is>
       </c>
-      <c r="D85" s="59" t="inlineStr">
+      <c r="D85" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770007/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="57" t="inlineStr">
+      <c r="A86" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="58" t="n">
+      <c r="B86" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2360,19 +2369,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D86" s="59" t="inlineStr">
+      <c r="D86" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="57" t="inlineStr">
+      <c r="A87" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B87" s="58" t="n">
+      <c r="B87" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2380,19 +2389,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D87" s="59" t="inlineStr">
+      <c r="D87" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="57" t="inlineStr">
+      <c r="A88" s="60" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B88" s="58" t="n">
+      <c r="B88" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2400,19 +2409,19 @@
           <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
-      <c r="D88" s="59" t="inlineStr">
+      <c r="D88" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="57" t="inlineStr">
+      <c r="A89" s="60" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="58" t="n">
+      <c r="B89" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2420,19 +2429,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D89" s="59" t="inlineStr">
+      <c r="D89" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="57" t="inlineStr">
+      <c r="A90" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B90" s="58" t="n">
+      <c r="B90" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2440,19 +2449,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D90" s="59" t="inlineStr">
+      <c r="D90" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="57" t="inlineStr">
+      <c r="A91" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B91" s="58" t="n">
+      <c r="B91" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2460,19 +2469,19 @@
           <t>Contract Administration Representative (French-speaking)</t>
         </is>
       </c>
-      <c r="D91" s="59" t="inlineStr">
+      <c r="D91" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461090763/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="57" t="inlineStr">
+      <c r="A92" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B92" s="58" t="n">
+      <c r="B92" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2480,19 +2489,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D92" s="59" t="inlineStr">
+      <c r="D92" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="57" t="inlineStr">
+      <c r="A93" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B93" s="58" t="n">
+      <c r="B93" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2500,19 +2509,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D93" s="59" t="inlineStr">
+      <c r="D93" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="57" t="inlineStr">
+      <c r="A94" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B94" s="58" t="n">
+      <c r="B94" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2520,19 +2529,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D94" s="59" t="inlineStr">
+      <c r="D94" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453089165/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="57" t="inlineStr">
+      <c r="A95" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B95" s="58" t="n">
+      <c r="B95" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2540,19 +2549,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D95" s="59" t="inlineStr">
+      <c r="D95" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="57" t="inlineStr">
+      <c r="A96" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B96" s="58" t="n">
+      <c r="B96" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2560,19 +2569,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D96" s="59" t="inlineStr">
+      <c r="D96" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="57" t="inlineStr">
+      <c r="A97" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B97" s="58" t="n">
+      <c r="B97" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2580,19 +2589,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D97" s="59" t="inlineStr">
+      <c r="D97" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="57" t="inlineStr">
+      <c r="A98" s="60" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B98" s="58" t="n">
+      <c r="B98" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2600,19 +2609,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D98" s="59" t="inlineStr">
+      <c r="D98" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="57" t="inlineStr">
+      <c r="A99" s="60" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B99" s="58" t="n">
+      <c r="B99" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2620,19 +2629,19 @@
           <t>Technical Support Representative 2</t>
         </is>
       </c>
-      <c r="D99" s="59" t="inlineStr">
+      <c r="D99" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438880089/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="57" t="inlineStr">
+      <c r="A100" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B100" s="58" t="n">
+      <c r="B100" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2640,19 +2649,19 @@
           <t>Spanish Bilingual Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D100" s="59" t="inlineStr">
+      <c r="D100" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458704406/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="57" t="inlineStr">
+      <c r="A101" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B101" s="58" t="n">
+      <c r="B101" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2660,19 +2669,19 @@
           <t>Spanish Bilingual TSR</t>
         </is>
       </c>
-      <c r="D101" s="59" t="inlineStr">
+      <c r="D101" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407814543/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="57" t="inlineStr">
+      <c r="A102" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B102" s="58" t="n">
+      <c r="B102" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2680,19 +2689,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D102" s="59" t="inlineStr">
+      <c r="D102" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="57" t="inlineStr">
+      <c r="A103" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B103" s="58" t="n">
+      <c r="B103" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2700,19 +2709,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D103" s="59" t="inlineStr">
+      <c r="D103" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="57" t="inlineStr">
+      <c r="A104" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B104" s="58" t="n">
+      <c r="B104" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2720,19 +2729,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D104" s="59" t="inlineStr">
+      <c r="D104" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="57" t="inlineStr">
+      <c r="A105" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B105" s="58" t="n">
+      <c r="B105" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2740,19 +2749,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D105" s="59" t="inlineStr">
+      <c r="D105" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="57" t="inlineStr">
+      <c r="A106" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B106" s="58" t="n">
+      <c r="B106" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2760,19 +2769,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D106" s="59" t="inlineStr">
+      <c r="D106" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439353245/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="57" t="inlineStr">
+      <c r="A107" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B107" s="58" t="n">
+      <c r="B107" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2780,19 +2789,19 @@
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="D107" s="59" t="inlineStr">
+      <c r="D107" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="57" t="inlineStr">
+      <c r="A108" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B108" s="58" t="n">
+      <c r="B108" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2800,19 +2809,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D108" s="59" t="inlineStr">
+      <c r="D108" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082223/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="57" t="inlineStr">
+      <c r="A109" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B109" s="58" t="n">
+      <c r="B109" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2820,19 +2829,19 @@
           <t>Business Process Analyst</t>
         </is>
       </c>
-      <c r="D109" s="59" t="inlineStr">
+      <c r="D109" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414569192/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="57" t="inlineStr">
+      <c r="A110" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B110" s="58" t="n">
+      <c r="B110" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2840,19 +2849,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D110" s="59" t="inlineStr">
+      <c r="D110" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456380639/</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="57" t="inlineStr">
+      <c r="A111" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B111" s="58" t="n">
+      <c r="B111" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2860,19 +2869,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D111" s="59" t="inlineStr">
+      <c r="D111" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456364824/</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="57" t="inlineStr">
+      <c r="A112" s="60" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B112" s="58" t="n">
+      <c r="B112" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -2880,19 +2889,19 @@
           <t>Associate Marketing Manager</t>
         </is>
       </c>
-      <c r="D112" s="59" t="inlineStr">
+      <c r="D112" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451399530/</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="57" t="inlineStr">
+      <c r="A113" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B113" s="58" t="n">
+      <c r="B113" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -2900,19 +2909,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D113" s="59" t="inlineStr">
+      <c r="D113" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="57" t="inlineStr">
+      <c r="A114" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B114" s="58" t="n">
+      <c r="B114" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -2920,19 +2929,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D114" s="59" t="inlineStr">
+      <c r="D114" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="57" t="inlineStr">
+      <c r="A115" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B115" s="58" t="n">
+      <c r="B115" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -2940,19 +2949,19 @@
           <t>Senior Sterilization Engineer</t>
         </is>
       </c>
-      <c r="D115" s="59" t="inlineStr">
+      <c r="D115" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410980549/</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="57" t="inlineStr">
+      <c r="A116" s="60" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B116" s="58" t="n">
+      <c r="B116" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -2960,19 +2969,19 @@
           <t>Accounts Payable Process Expert (Maternity Cover)</t>
         </is>
       </c>
-      <c r="D116" s="59" t="inlineStr">
+      <c r="D116" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462464542/</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="57" t="inlineStr">
+      <c r="A117" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B117" s="58" t="n">
+      <c r="B117" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -2980,19 +2989,19 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D117" s="59" t="inlineStr">
+      <c r="D117" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="57" t="inlineStr">
+      <c r="A118" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B118" s="58" t="n">
+      <c r="B118" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -3000,19 +3009,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D118" s="59" t="inlineStr">
+      <c r="D118" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="57" t="inlineStr">
+      <c r="A119" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B119" s="58" t="n">
+      <c r="B119" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3020,19 +3029,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D119" s="59" t="inlineStr">
+      <c r="D119" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="57" t="inlineStr">
+      <c r="A120" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B120" s="58" t="n">
+      <c r="B120" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3040,19 +3049,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D120" s="59" t="inlineStr">
+      <c r="D120" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="57" t="inlineStr">
+      <c r="A121" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B121" s="58" t="n">
+      <c r="B121" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3060,19 +3069,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D121" s="59" t="inlineStr">
+      <c r="D121" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="57" t="inlineStr">
+      <c r="A122" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B122" s="58" t="n">
+      <c r="B122" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3080,19 +3089,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D122" s="59" t="inlineStr">
+      <c r="D122" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="57" t="inlineStr">
+      <c r="A123" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B123" s="58" t="n">
+      <c r="B123" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3100,19 +3109,19 @@
           <t>Staff SRE SW Development Engineer</t>
         </is>
       </c>
-      <c r="D123" s="59" t="inlineStr">
+      <c r="D123" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387683946/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="57" t="inlineStr">
+      <c r="A124" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B124" s="58" t="n">
+      <c r="B124" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3120,19 +3129,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D124" s="59" t="inlineStr">
+      <c r="D124" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="57" t="inlineStr">
+      <c r="A125" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B125" s="58" t="n">
+      <c r="B125" s="61" t="n">
         <v>46275</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3140,19 +3149,19 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D125" s="59" t="inlineStr">
+      <c r="D125" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="57" t="inlineStr">
+      <c r="A126" s="60" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B126" s="58" t="n">
+      <c r="B126" s="61" t="n">
         <v>46276</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3160,369 +3169,369 @@
           <t>Third Party Risk and Supplier Onboarding Manager</t>
         </is>
       </c>
-      <c r="D126" s="59" t="inlineStr">
+      <c r="D126" s="62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466048486/</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="57" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B127" s="58" t="n">
-        <v>46270</v>
+      <c r="A127" s="60" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B127" s="61" t="n">
+        <v>46274</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Distributor Manager - Channel Excellence (MedTech)</t>
-        </is>
-      </c>
-      <c r="D127" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
+          <t>Senior Service Designer, Technical Support</t>
+        </is>
+      </c>
+      <c r="D127" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455960251/</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="57" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B128" s="58" t="n">
-        <v>46270</v>
+      <c r="A128" s="60" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B128" s="61" t="n">
+        <v>46273</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Distributor Manager - Channel Excellence (MedTech)</t>
-        </is>
-      </c>
-      <c r="D128" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
+          <t>Process Technician 2 (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D128" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="57" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B129" s="58" t="n">
+      <c r="A129" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B129" s="61" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Manager Systems Design Engineering</t>
+        </is>
+      </c>
+      <c r="D129" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464683405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B130" s="61" t="n">
         <v>46274</v>
       </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>Senior Service Designer, Technical Support</t>
-        </is>
-      </c>
-      <c r="D129" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455960251/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="57" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B130" s="58" t="n">
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Process Development Engineer</t>
+        </is>
+      </c>
+      <c r="D130" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="60" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B131" s="61" t="n">
         <v>46273</v>
       </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>Process Technician 2 (Front End Night Shift)</t>
-        </is>
-      </c>
-      <c r="D130" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="57" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B131" s="58" t="n">
-        <v>46272</v>
-      </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Supervisor Process Engineering</t>
-        </is>
-      </c>
-      <c r="D131" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464338496/</t>
+          <t>Manager, SW System &amp; Solution Dev Engineer</t>
+        </is>
+      </c>
+      <c r="D131" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="57" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B132" s="58" t="n">
-        <v>46272</v>
+      <c r="A132" s="60" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B132" s="61" t="n">
+        <v>46274</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Sr Production Supervisor (Front End Night Shift)</t>
-        </is>
-      </c>
-      <c r="D132" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455302580/</t>
+          <t>Supervisor Manufacturing</t>
+        </is>
+      </c>
+      <c r="D132" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4428861138/</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="57" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B133" s="58" t="n">
-        <v>46270</v>
+      <c r="A133" s="60" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B133" s="61" t="n">
+        <v>46274</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Engineering Technician 3 (Front End Day Shift)</t>
-        </is>
-      </c>
-      <c r="D133" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
+          <t>Staff Database Administrator</t>
+        </is>
+      </c>
+      <c r="D133" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="57" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="B134" s="58" t="n">
-        <v>46272</v>
+      <c r="A134" s="60" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B134" s="61" t="n">
+        <v>46274</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Territory Business Manager</t>
-        </is>
-      </c>
-      <c r="D134" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464350389/</t>
+          <t>Payroll Analyst (ANZ)</t>
+        </is>
+      </c>
+      <c r="D134" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="57" t="inlineStr">
+      <c r="A135" s="60" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B135" s="61" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Sr Enterprise Developer (Power Platform Developer)</t>
+        </is>
+      </c>
+      <c r="D135" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B135" s="58" t="n">
+      <c r="B136" s="61" t="n">
         <v>46273</v>
       </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>Manager Systems Design Engineering</t>
-        </is>
-      </c>
-      <c r="D135" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464683405/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="57" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Software QA Engineer 2</t>
+        </is>
+      </c>
+      <c r="D136" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="60" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B137" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="D137" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="60" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B138" s="61" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2 - Android</t>
+        </is>
+      </c>
+      <c r="D138" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B136" s="58" t="n">
+      <c r="B139" s="61" t="n">
         <v>46274</v>
       </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>Senior Staff Process Development Engineer</t>
-        </is>
-      </c>
-      <c r="D136" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="57" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Sr Workplace Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="D139" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="60" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B137" s="58" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>Manager, SW System &amp; Solution Dev Engineer</t>
-        </is>
-      </c>
-      <c r="D137" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="57" t="inlineStr">
+      <c r="B140" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Staff SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D140" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="60" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B141" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Director, Business Program Management Office</t>
+        </is>
+      </c>
+      <c r="D141" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="60" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B138" s="58" t="n">
+      <c r="B142" s="61" t="n">
         <v>46274</v>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>Supervisor Manufacturing</t>
-        </is>
-      </c>
-      <c r="D138" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4428861138/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="57" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B139" s="58" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Sr IT Project Manager</t>
-        </is>
-      </c>
-      <c r="D139" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="57" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B140" s="58" t="n">
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 4</t>
+        </is>
+      </c>
+      <c r="D142" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B143" s="61" t="n">
         <v>46274</v>
       </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>Staff Database Administrator</t>
-        </is>
-      </c>
-      <c r="D140" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="57" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B141" s="58" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>Payroll Analyst (ANZ)</t>
-        </is>
-      </c>
-      <c r="D141" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="57" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Systems Design &amp; Test Engineer 2</t>
+        </is>
+      </c>
+      <c r="D143" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B142" s="58" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
-        </is>
-      </c>
-      <c r="D142" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="57" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B143" s="58" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>Sr Enterprise Developer (Power Platform Developer)</t>
-        </is>
-      </c>
-      <c r="D143" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="57" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B144" s="58" t="n">
-        <v>46273</v>
+      <c r="B144" s="61" t="n">
+        <v>46275</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Software QA Engineer 2</t>
-        </is>
-      </c>
-      <c r="D144" s="59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
+          <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
+        </is>
+      </c>
+      <c r="D144" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439394782/</t>
         </is>
       </c>
     </row>
@@ -3533,261 +3542,701 @@
         </is>
       </c>
       <c r="B145" s="61" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
+          <t>Sr. SW Test Development Engineer V&amp;V</t>
+        </is>
+      </c>
+      <c r="D145" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B146" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
           <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
-      <c r="D145" s="62" t="inlineStr">
+      <c r="D146" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="60" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="63" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B147" s="64" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Financial Analyst</t>
+        </is>
+      </c>
+      <c r="D147" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4421230278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B146" s="61" t="n">
+      <c r="B148" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Sr Cybersecurity Analyst</t>
+        </is>
+      </c>
+      <c r="D148" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439085443/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B149" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D149" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4460357219/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="63" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B150" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Trade Compliance Analyst</t>
+        </is>
+      </c>
+      <c r="D150" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467033928/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B151" s="64" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manufacturing Engineer</t>
+        </is>
+      </c>
+      <c r="D151" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447583072/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="63" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B152" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>Staff Vendor Management Analyst</t>
+        </is>
+      </c>
+      <c r="D152" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458212554/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="63" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B153" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Staff Equipment Engineer</t>
+        </is>
+      </c>
+      <c r="D153" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458218533/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="63" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B154" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>APAC Product Manager - OTC/Consumer Health</t>
+        </is>
+      </c>
+      <c r="D154" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4422693615/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="63" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B155" s="64" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Technical Support - Manila</t>
+        </is>
+      </c>
+      <c r="D155" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417742237/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="63" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B156" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>Staff Desktop Support Engineer</t>
+        </is>
+      </c>
+      <c r="D156" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4398315987/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B157" s="64" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>Director HW Design Quality Engineering - New Product Introductions</t>
+        </is>
+      </c>
+      <c r="D157" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456789792/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B158" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>Manager SW Test Development Engineering</t>
+        </is>
+      </c>
+      <c r="D158" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4281993770/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B159" s="64" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
+        </is>
+      </c>
+      <c r="D159" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="63" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B160" s="64" t="n">
         <v>46274</v>
       </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>SW Test Development Engineer 1</t>
-        </is>
-      </c>
-      <c r="D146" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="60" t="inlineStr">
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor, Applications Support</t>
+        </is>
+      </c>
+      <c r="D160" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456333076/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B161" s="64" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Hardware Engineer 2</t>
+        </is>
+      </c>
+      <c r="D161" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="63" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B162" s="64" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>Territory Business Manager - South Island</t>
+        </is>
+      </c>
+      <c r="D162" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456111920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="63" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B163" s="64" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Sr Staff Program Manager</t>
+        </is>
+      </c>
+      <c r="D163" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448138066/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B164" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>Senior Manager- Manufacturing IT Strategic Initiatives and Architecture</t>
+        </is>
+      </c>
+      <c r="D164" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4421221561/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="63" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B165" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Manager Process Engineering</t>
+        </is>
+      </c>
+      <c r="D165" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467096658/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B147" s="61" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>SW Development Engineer 2 - Android</t>
-        </is>
-      </c>
-      <c r="D147" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="60" t="inlineStr">
+      <c r="B166" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2 - IOS</t>
+        </is>
+      </c>
+      <c r="D166" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465306719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B167" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Staff Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D167" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461770016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="63" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B148" s="61" t="n">
+      <c r="B168" s="64" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>District Business Manager - Ohio</t>
+        </is>
+      </c>
+      <c r="D168" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458551771/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B169" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D169" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4375183129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B170" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Lead Firmware V&amp;V</t>
+        </is>
+      </c>
+      <c r="D170" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4402920307/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B171" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D171" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461756319/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B172" s="64" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>Senior Lead Government Affairs Manager - Federal</t>
+        </is>
+      </c>
+      <c r="D172" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440825647/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="63" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B173" s="64" t="n">
         <v>46274</v>
       </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>Sr Workplace Solutions Analyst</t>
-        </is>
-      </c>
-      <c r="D148" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="60" t="inlineStr">
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Staff Database Administrator</t>
+        </is>
+      </c>
+      <c r="D173" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456333107/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B174" s="64" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Technician 2 (2A Sunday - Tuesday, every other Saturday from 5:00PM - 5:00AM )</t>
+        </is>
+      </c>
+      <c r="D174" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466467687/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B175" s="64" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Technician 2 (2B Wednesday - Friday, every other Saturday from 5:00PM - 5:00AM)</t>
+        </is>
+      </c>
+      <c r="D175" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466428944/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B176" s="64" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>New Business Development Manager, Trade Partnerships (eCommerce)</t>
+        </is>
+      </c>
+      <c r="D176" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459020959/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B149" s="61" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>Staff SW Development Engineer</t>
-        </is>
-      </c>
-      <c r="D149" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="60" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B150" s="61" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>Director, Business Program Management Office</t>
-        </is>
-      </c>
-      <c r="D150" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="60" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B151" s="61" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Support Specialist 3</t>
-        </is>
-      </c>
-      <c r="D151" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4445930979/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="60" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B152" s="61" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>Engineering Technician 4</t>
-        </is>
-      </c>
-      <c r="D152" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="60" t="inlineStr">
+      <c r="B177" s="64" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Sr Firmware V&amp;V</t>
+        </is>
+      </c>
+      <c r="D177" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4402292560/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="63" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B153" s="61" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>Systems Design &amp; Test Engineer 2</t>
-        </is>
-      </c>
-      <c r="D153" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="60" t="inlineStr">
+      <c r="B178" s="64" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>Sr Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="D178" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457557361/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="63" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B154" s="61" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
-        </is>
-      </c>
-      <c r="D154" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4439394782/</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="60" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B155" s="61" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>Sr. SW Test Development Engineer V&amp;V</t>
-        </is>
-      </c>
-      <c r="D155" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B156" s="61" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
-        </is>
-      </c>
-      <c r="D156" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="60" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B157" s="61" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>Lab Technician 3 (Chemistry) Back End Days</t>
-        </is>
-      </c>
-      <c r="D157" s="62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464341469/</t>
+      <c r="B179" s="64" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Staff Enterprise Applications Developer - IBM Maximo</t>
+        </is>
+      </c>
+      <c r="D179" s="65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4411935028/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D157"/>
+  <autoFilter ref="A1:D179"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -3945,6 +4394,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -644,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D179"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -676,12 +685,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="61" t="n">
+      <c r="B2" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -689,19 +698,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="62" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="61" t="n">
+      <c r="B3" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -709,19 +718,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="62" t="inlineStr">
+      <c r="D3" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="61" t="n">
+      <c r="B4" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -729,19 +738,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="61" t="n">
+      <c r="B5" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -749,19 +758,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="62" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="61" t="n">
+      <c r="B6" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -769,19 +778,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="62" t="inlineStr">
+      <c r="D6" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="61" t="n">
+      <c r="B7" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -789,19 +798,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="62" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="61" t="n">
+      <c r="B8" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -809,19 +818,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="62" t="inlineStr">
+      <c r="D8" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="61" t="n">
+      <c r="B9" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -829,19 +838,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="62" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="61" t="n">
+      <c r="B10" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -849,19 +858,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="62" t="inlineStr">
+      <c r="D10" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="61" t="n">
+      <c r="B11" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -869,19 +878,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="62" t="inlineStr">
+      <c r="D11" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="61" t="n">
+      <c r="B12" s="64" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -889,19 +898,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="62" t="inlineStr">
+      <c r="D12" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="61" t="n">
+      <c r="B13" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -909,19 +918,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="62" t="inlineStr">
+      <c r="D13" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="61" t="n">
+      <c r="B14" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -929,19 +938,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="62" t="inlineStr">
+      <c r="D14" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="n">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -949,19 +958,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="62" t="inlineStr">
+      <c r="D15" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="61" t="n">
+      <c r="B16" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -969,19 +978,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="62" t="inlineStr">
+      <c r="D16" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="61" t="n">
+      <c r="B17" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -989,19 +998,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="62" t="inlineStr">
+      <c r="D17" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="61" t="n">
+      <c r="B18" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1009,19 +1018,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="62" t="inlineStr">
+      <c r="D18" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="61" t="n">
+      <c r="B19" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1029,19 +1038,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="62" t="inlineStr">
+      <c r="D19" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="63" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="61" t="n">
+      <c r="B20" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1049,19 +1058,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="62" t="inlineStr">
+      <c r="D20" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B21" s="61" t="n">
+      <c r="A21" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1069,19 +1078,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="62" t="inlineStr">
+      <c r="D21" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="63" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="61" t="n">
+      <c r="B22" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1089,19 +1098,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="62" t="inlineStr">
+      <c r="D22" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B23" s="61" t="n">
+      <c r="A23" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1109,19 +1118,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="62" t="inlineStr">
+      <c r="D23" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="61" t="n">
+      <c r="B24" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1129,19 +1138,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="62" t="inlineStr">
+      <c r="D24" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="61" t="n">
+      <c r="B25" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1149,19 +1158,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="62" t="inlineStr">
+      <c r="D25" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="60" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="61" t="n">
+      <c r="B26" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1169,19 +1178,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="62" t="inlineStr">
+      <c r="D26" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="61" t="n">
+      <c r="B27" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1189,19 +1198,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="62" t="inlineStr">
+      <c r="D27" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="60" t="inlineStr">
+      <c r="A28" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="61" t="n">
+      <c r="B28" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1209,19 +1218,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="62" t="inlineStr">
+      <c r="D28" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="inlineStr">
+      <c r="A29" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="61" t="n">
+      <c r="B29" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1229,19 +1238,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="62" t="inlineStr">
+      <c r="D29" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="63" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="61" t="n">
+      <c r="B30" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1249,19 +1258,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="62" t="inlineStr">
+      <c r="D30" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="61" t="n">
+      <c r="B31" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1269,19 +1278,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="62" t="inlineStr">
+      <c r="D31" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="61" t="n">
+      <c r="A32" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1289,19 +1298,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="62" t="inlineStr">
+      <c r="D32" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="61" t="n">
+      <c r="A33" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1309,19 +1318,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="62" t="inlineStr">
+      <c r="D33" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="61" t="n">
+      <c r="B34" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1329,19 +1338,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="62" t="inlineStr">
+      <c r="D34" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="A35" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="61" t="n">
+      <c r="B35" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1349,19 +1358,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="62" t="inlineStr">
+      <c r="D35" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="61" t="n">
+      <c r="B36" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1369,19 +1378,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="62" t="inlineStr">
+      <c r="D36" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="60" t="inlineStr">
+      <c r="A37" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="61" t="n">
+      <c r="B37" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1389,19 +1398,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="62" t="inlineStr">
+      <c r="D37" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="60" t="inlineStr">
+      <c r="A38" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="61" t="n">
+      <c r="B38" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1409,19 +1418,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="62" t="inlineStr">
+      <c r="D38" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="60" t="inlineStr">
+      <c r="A39" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="61" t="n">
+      <c r="B39" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1429,19 +1438,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="62" t="inlineStr">
+      <c r="D39" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="60" t="inlineStr">
+      <c r="A40" s="63" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="61" t="n">
+      <c r="B40" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1449,19 +1458,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="62" t="inlineStr">
+      <c r="D40" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="A41" s="63" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="61" t="n">
+      <c r="B41" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1469,19 +1478,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="62" t="inlineStr">
+      <c r="D41" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B42" s="61" t="n">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B42" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1489,19 +1498,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="62" t="inlineStr">
+      <c r="D42" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="61" t="n">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1509,19 +1518,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="62" t="inlineStr">
+      <c r="D43" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="A44" s="63" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="61" t="n">
+      <c r="B44" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1529,19 +1538,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="62" t="inlineStr">
+      <c r="D44" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="60" t="inlineStr">
+      <c r="A45" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="61" t="n">
+      <c r="B45" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1549,19 +1558,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="62" t="inlineStr">
+      <c r="D45" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="61" t="n">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1569,19 +1578,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="62" t="inlineStr">
+      <c r="D46" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="60" t="inlineStr">
+      <c r="A47" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="61" t="n">
+      <c r="B47" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1589,19 +1598,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="62" t="inlineStr">
+      <c r="D47" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="60" t="inlineStr">
+      <c r="A48" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="61" t="n">
+      <c r="B48" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1609,19 +1618,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="62" t="inlineStr">
+      <c r="D48" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="60" t="inlineStr">
+      <c r="A49" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="61" t="n">
+      <c r="B49" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1629,19 +1638,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="62" t="inlineStr">
+      <c r="D49" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="60" t="inlineStr">
+      <c r="A50" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="61" t="n">
+      <c r="B50" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1649,19 +1658,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="62" t="inlineStr">
+      <c r="D50" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="60" t="inlineStr">
+      <c r="A51" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="61" t="n">
+      <c r="B51" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1669,19 +1678,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="62" t="inlineStr">
+      <c r="D51" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="60" t="inlineStr">
+      <c r="A52" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="61" t="n">
+      <c r="B52" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1689,19 +1698,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="62" t="inlineStr">
+      <c r="D52" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="60" t="inlineStr">
+      <c r="A53" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="61" t="n">
+      <c r="B53" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1709,19 +1718,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="62" t="inlineStr">
+      <c r="D53" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="60" t="inlineStr">
+      <c r="A54" s="63" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="61" t="n">
+      <c r="B54" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1729,19 +1738,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="62" t="inlineStr">
+      <c r="D54" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="60" t="inlineStr">
+      <c r="A55" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="61" t="n">
+      <c r="B55" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1749,19 +1758,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="62" t="inlineStr">
+      <c r="D55" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="60" t="inlineStr">
+      <c r="A56" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="61" t="n">
+      <c r="B56" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1769,19 +1778,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="62" t="inlineStr">
+      <c r="D56" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="60" t="inlineStr">
+      <c r="A57" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="61" t="n">
+      <c r="B57" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1789,19 +1798,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="62" t="inlineStr">
+      <c r="D57" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="60" t="inlineStr">
+      <c r="A58" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="61" t="n">
+      <c r="B58" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1809,19 +1818,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="62" t="inlineStr">
+      <c r="D58" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="61" t="n">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1829,19 +1838,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="62" t="inlineStr">
+      <c r="D59" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="60" t="inlineStr">
+      <c r="A60" s="63" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="61" t="n">
+      <c r="B60" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1849,19 +1858,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="62" t="inlineStr">
+      <c r="D60" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B61" s="61" t="n">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B61" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1869,19 +1878,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="62" t="inlineStr">
+      <c r="D61" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="60" t="inlineStr">
+      <c r="A62" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="61" t="n">
+      <c r="B62" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1889,19 +1898,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="62" t="inlineStr">
+      <c r="D62" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="61" t="n">
+      <c r="A63" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1909,19 +1918,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="62" t="inlineStr">
+      <c r="D63" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="60" t="inlineStr">
+      <c r="A64" s="63" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="61" t="n">
+      <c r="B64" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1929,19 +1938,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="62" t="inlineStr">
+      <c r="D64" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B65" s="61" t="n">
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B65" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1949,19 +1958,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="62" t="inlineStr">
+      <c r="D65" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="60" t="inlineStr">
+      <c r="A66" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="61" t="n">
+      <c r="B66" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1969,19 +1978,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="62" t="inlineStr">
+      <c r="D66" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B67" s="61" t="n">
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B67" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1989,19 +1998,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="62" t="inlineStr">
+      <c r="D67" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="60" t="inlineStr">
+      <c r="A68" s="63" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="61" t="n">
+      <c r="B68" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -2009,19 +2018,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="62" t="inlineStr">
+      <c r="D68" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="60" t="inlineStr">
+      <c r="A69" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="61" t="n">
+      <c r="B69" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2029,19 +2038,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="62" t="inlineStr">
+      <c r="D69" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="60" t="inlineStr">
+      <c r="A70" s="63" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="61" t="n">
+      <c r="B70" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2049,19 +2058,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="62" t="inlineStr">
+      <c r="D70" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="60" t="inlineStr">
+      <c r="A71" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="61" t="n">
+      <c r="B71" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2069,19 +2078,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="62" t="inlineStr">
+      <c r="D71" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="60" t="inlineStr">
+      <c r="A72" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="61" t="n">
+      <c r="B72" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2089,19 +2098,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="62" t="inlineStr">
+      <c r="D72" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="60" t="inlineStr">
+      <c r="A73" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="61" t="n">
+      <c r="B73" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2109,19 +2118,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="62" t="inlineStr">
+      <c r="D73" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="60" t="inlineStr">
+      <c r="A74" s="63" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="61" t="n">
+      <c r="B74" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2129,19 +2138,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="62" t="inlineStr">
+      <c r="D74" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="60" t="inlineStr">
+      <c r="A75" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="61" t="n">
+      <c r="B75" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2149,19 +2158,19 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="62" t="inlineStr">
+      <c r="D75" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="60" t="inlineStr">
+      <c r="A76" s="63" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B76" s="61" t="n">
+      <c r="B76" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2169,19 +2178,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D76" s="62" t="inlineStr">
+      <c r="D76" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="60" t="inlineStr">
+      <c r="A77" s="63" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B77" s="61" t="n">
+      <c r="B77" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2189,19 +2198,19 @@
           <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
         </is>
       </c>
-      <c r="D77" s="62" t="inlineStr">
+      <c r="D77" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765129/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="60" t="inlineStr">
+      <c r="A78" s="63" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="61" t="n">
+      <c r="B78" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2209,19 +2218,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D78" s="62" t="inlineStr">
+      <c r="D78" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="60" t="inlineStr">
+      <c r="A79" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B79" s="61" t="n">
+      <c r="B79" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2229,19 +2238,19 @@
           <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
-      <c r="D79" s="62" t="inlineStr">
+      <c r="D79" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="60" t="inlineStr">
+      <c r="A80" s="63" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B80" s="61" t="n">
+      <c r="B80" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2249,19 +2258,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D80" s="62" t="inlineStr">
+      <c r="D80" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="60" t="inlineStr">
+      <c r="A81" s="63" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B81" s="61" t="n">
+      <c r="B81" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2269,19 +2278,19 @@
           <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
         </is>
       </c>
-      <c r="D81" s="62" t="inlineStr">
+      <c r="D81" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450696746/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="60" t="inlineStr">
+      <c r="A82" s="63" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="61" t="n">
+      <c r="B82" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2289,19 +2298,19 @@
           <t>Logistics Analyst</t>
         </is>
       </c>
-      <c r="D82" s="62" t="inlineStr">
+      <c r="D82" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461266744/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="60" t="inlineStr">
+      <c r="A83" s="63" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B83" s="61" t="n">
+      <c r="B83" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2309,19 +2318,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D83" s="62" t="inlineStr">
+      <c r="D83" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="60" t="inlineStr">
+      <c r="A84" s="63" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B84" s="61" t="n">
+      <c r="B84" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2329,19 +2338,19 @@
           <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D84" s="62" t="inlineStr">
+      <c r="D84" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459309508/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="60" t="inlineStr">
+      <c r="A85" s="63" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" s="61" t="n">
+      <c r="B85" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2349,19 +2358,19 @@
           <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
         </is>
       </c>
-      <c r="D85" s="62" t="inlineStr">
+      <c r="D85" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770007/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="60" t="inlineStr">
+      <c r="A86" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="61" t="n">
+      <c r="B86" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2369,19 +2378,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D86" s="62" t="inlineStr">
+      <c r="D86" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="60" t="inlineStr">
+      <c r="A87" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B87" s="61" t="n">
+      <c r="B87" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2389,19 +2398,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D87" s="62" t="inlineStr">
+      <c r="D87" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="60" t="inlineStr">
+      <c r="A88" s="63" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B88" s="61" t="n">
+      <c r="B88" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2409,19 +2418,19 @@
           <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
-      <c r="D88" s="62" t="inlineStr">
+      <c r="D88" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="60" t="inlineStr">
+      <c r="A89" s="63" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="61" t="n">
+      <c r="B89" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2429,19 +2438,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D89" s="62" t="inlineStr">
+      <c r="D89" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="60" t="inlineStr">
+      <c r="A90" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B90" s="61" t="n">
+      <c r="B90" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2449,19 +2458,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D90" s="62" t="inlineStr">
+      <c r="D90" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="60" t="inlineStr">
+      <c r="A91" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B91" s="61" t="n">
+      <c r="B91" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2469,19 +2478,19 @@
           <t>Contract Administration Representative (French-speaking)</t>
         </is>
       </c>
-      <c r="D91" s="62" t="inlineStr">
+      <c r="D91" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461090763/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="60" t="inlineStr">
+      <c r="A92" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B92" s="61" t="n">
+      <c r="B92" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2489,19 +2498,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D92" s="62" t="inlineStr">
+      <c r="D92" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="60" t="inlineStr">
+      <c r="A93" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B93" s="61" t="n">
+      <c r="B93" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2509,19 +2518,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D93" s="62" t="inlineStr">
+      <c r="D93" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="60" t="inlineStr">
+      <c r="A94" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B94" s="61" t="n">
+      <c r="B94" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2529,19 +2538,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D94" s="62" t="inlineStr">
+      <c r="D94" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453089165/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="60" t="inlineStr">
+      <c r="A95" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B95" s="61" t="n">
+      <c r="B95" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2549,19 +2558,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D95" s="62" t="inlineStr">
+      <c r="D95" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="60" t="inlineStr">
+      <c r="A96" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B96" s="61" t="n">
+      <c r="B96" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2569,19 +2578,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D96" s="62" t="inlineStr">
+      <c r="D96" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="60" t="inlineStr">
+      <c r="A97" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B97" s="61" t="n">
+      <c r="B97" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2589,19 +2598,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D97" s="62" t="inlineStr">
+      <c r="D97" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="60" t="inlineStr">
+      <c r="A98" s="63" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B98" s="61" t="n">
+      <c r="B98" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2609,19 +2618,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D98" s="62" t="inlineStr">
+      <c r="D98" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="60" t="inlineStr">
+      <c r="A99" s="63" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B99" s="61" t="n">
+      <c r="B99" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2629,19 +2638,19 @@
           <t>Technical Support Representative 2</t>
         </is>
       </c>
-      <c r="D99" s="62" t="inlineStr">
+      <c r="D99" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438880089/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="60" t="inlineStr">
+      <c r="A100" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B100" s="61" t="n">
+      <c r="B100" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2649,19 +2658,19 @@
           <t>Spanish Bilingual Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D100" s="62" t="inlineStr">
+      <c r="D100" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458704406/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="60" t="inlineStr">
+      <c r="A101" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B101" s="61" t="n">
+      <c r="B101" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2669,19 +2678,19 @@
           <t>Spanish Bilingual TSR</t>
         </is>
       </c>
-      <c r="D101" s="62" t="inlineStr">
+      <c r="D101" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407814543/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B102" s="61" t="n">
+      <c r="A102" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B102" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2689,19 +2698,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D102" s="62" t="inlineStr">
+      <c r="D102" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="60" t="inlineStr">
+      <c r="A103" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B103" s="61" t="n">
+      <c r="B103" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2709,19 +2718,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D103" s="62" t="inlineStr">
+      <c r="D103" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B104" s="61" t="n">
+      <c r="A104" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B104" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2729,19 +2738,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D104" s="62" t="inlineStr">
+      <c r="D104" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B105" s="61" t="n">
+      <c r="A105" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B105" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2749,19 +2758,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D105" s="62" t="inlineStr">
+      <c r="D105" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B106" s="61" t="n">
+      <c r="A106" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B106" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2769,19 +2778,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D106" s="62" t="inlineStr">
+      <c r="D106" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439353245/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="60" t="inlineStr">
+      <c r="A107" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B107" s="61" t="n">
+      <c r="B107" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2789,19 +2798,19 @@
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="D107" s="62" t="inlineStr">
+      <c r="D107" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="60" t="inlineStr">
+      <c r="A108" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B108" s="61" t="n">
+      <c r="B108" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2809,19 +2818,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D108" s="62" t="inlineStr">
+      <c r="D108" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082223/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="60" t="inlineStr">
+      <c r="A109" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B109" s="61" t="n">
+      <c r="B109" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2829,19 +2838,19 @@
           <t>Business Process Analyst</t>
         </is>
       </c>
-      <c r="D109" s="62" t="inlineStr">
+      <c r="D109" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414569192/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B110" s="61" t="n">
+      <c r="A110" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2849,19 +2858,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D110" s="62" t="inlineStr">
+      <c r="D110" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456380639/</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B111" s="61" t="n">
+      <c r="A111" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B111" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2869,19 +2878,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D111" s="62" t="inlineStr">
+      <c r="D111" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456364824/</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="60" t="inlineStr">
+      <c r="A112" s="63" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B112" s="61" t="n">
+      <c r="B112" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -2889,19 +2898,19 @@
           <t>Associate Marketing Manager</t>
         </is>
       </c>
-      <c r="D112" s="62" t="inlineStr">
+      <c r="D112" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451399530/</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B113" s="61" t="n">
+      <c r="A113" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B113" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -2909,19 +2918,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D113" s="62" t="inlineStr">
+      <c r="D113" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B114" s="61" t="n">
+      <c r="A114" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B114" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -2929,19 +2938,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D114" s="62" t="inlineStr">
+      <c r="D114" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="60" t="inlineStr">
+      <c r="A115" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B115" s="61" t="n">
+      <c r="B115" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -2949,19 +2958,19 @@
           <t>Senior Sterilization Engineer</t>
         </is>
       </c>
-      <c r="D115" s="62" t="inlineStr">
+      <c r="D115" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410980549/</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="60" t="inlineStr">
+      <c r="A116" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B116" s="61" t="n">
+      <c r="B116" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -2969,19 +2978,19 @@
           <t>Accounts Payable Process Expert (Maternity Cover)</t>
         </is>
       </c>
-      <c r="D116" s="62" t="inlineStr">
+      <c r="D116" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462464542/</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="60" t="inlineStr">
+      <c r="A117" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B117" s="61" t="n">
+      <c r="B117" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -2989,19 +2998,19 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D117" s="62" t="inlineStr">
+      <c r="D117" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B118" s="61" t="n">
+      <c r="A118" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B118" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -3009,19 +3018,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D118" s="62" t="inlineStr">
+      <c r="D118" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="60" t="inlineStr">
+      <c r="A119" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B119" s="61" t="n">
+      <c r="B119" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3029,19 +3038,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D119" s="62" t="inlineStr">
+      <c r="D119" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B120" s="61" t="n">
+      <c r="A120" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B120" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3049,19 +3058,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D120" s="62" t="inlineStr">
+      <c r="D120" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="60" t="inlineStr">
+      <c r="A121" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B121" s="61" t="n">
+      <c r="B121" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3069,19 +3078,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D121" s="62" t="inlineStr">
+      <c r="D121" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B122" s="61" t="n">
+      <c r="A122" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B122" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3089,19 +3098,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D122" s="62" t="inlineStr">
+      <c r="D122" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="60" t="inlineStr">
+      <c r="A123" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B123" s="61" t="n">
+      <c r="B123" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3109,19 +3118,19 @@
           <t>Staff SRE SW Development Engineer</t>
         </is>
       </c>
-      <c r="D123" s="62" t="inlineStr">
+      <c r="D123" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387683946/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B124" s="61" t="n">
+      <c r="A124" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B124" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3129,19 +3138,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D124" s="62" t="inlineStr">
+      <c r="D124" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B125" s="61" t="n">
+      <c r="A125" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B125" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3149,19 +3158,19 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D125" s="62" t="inlineStr">
+      <c r="D125" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="60" t="inlineStr">
+      <c r="A126" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B126" s="61" t="n">
+      <c r="B126" s="64" t="n">
         <v>46276</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3169,19 +3178,19 @@
           <t>Third Party Risk and Supplier Onboarding Manager</t>
         </is>
       </c>
-      <c r="D126" s="62" t="inlineStr">
+      <c r="D126" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466048486/</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="60" t="inlineStr">
+      <c r="A127" s="63" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B127" s="61" t="n">
+      <c r="B127" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3189,19 +3198,19 @@
           <t>Senior Service Designer, Technical Support</t>
         </is>
       </c>
-      <c r="D127" s="62" t="inlineStr">
+      <c r="D127" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455960251/</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="60" t="inlineStr">
+      <c r="A128" s="63" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B128" s="61" t="n">
+      <c r="B128" s="64" t="n">
         <v>46273</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -3209,19 +3218,19 @@
           <t>Process Technician 2 (Front End Night Shift)</t>
         </is>
       </c>
-      <c r="D128" s="62" t="inlineStr">
+      <c r="D128" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455755200/</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B129" s="61" t="n">
+      <c r="A129" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B129" s="64" t="n">
         <v>46273</v>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -3229,19 +3238,19 @@
           <t>Manager Systems Design Engineering</t>
         </is>
       </c>
-      <c r="D129" s="62" t="inlineStr">
+      <c r="D129" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464683405/</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B130" s="61" t="n">
+      <c r="A130" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B130" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -3249,19 +3258,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D130" s="62" t="inlineStr">
+      <c r="D130" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464945232/</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="60" t="inlineStr">
+      <c r="A131" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B131" s="61" t="n">
+      <c r="B131" s="64" t="n">
         <v>46273</v>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -3269,19 +3278,19 @@
           <t>Manager, SW System &amp; Solution Dev Engineer</t>
         </is>
       </c>
-      <c r="D131" s="62" t="inlineStr">
+      <c r="D131" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="60" t="inlineStr">
+      <c r="A132" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B132" s="61" t="n">
+      <c r="B132" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -3289,19 +3298,19 @@
           <t>Supervisor Manufacturing</t>
         </is>
       </c>
-      <c r="D132" s="62" t="inlineStr">
+      <c r="D132" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4428861138/</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="60" t="inlineStr">
+      <c r="A133" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B133" s="61" t="n">
+      <c r="B133" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -3309,19 +3318,19 @@
           <t>Staff Database Administrator</t>
         </is>
       </c>
-      <c r="D133" s="62" t="inlineStr">
+      <c r="D133" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322200/</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="60" t="inlineStr">
+      <c r="A134" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B134" s="61" t="n">
+      <c r="B134" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -3329,19 +3338,19 @@
           <t>Payroll Analyst (ANZ)</t>
         </is>
       </c>
-      <c r="D134" s="62" t="inlineStr">
+      <c r="D134" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456178209/</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="60" t="inlineStr">
+      <c r="A135" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B135" s="61" t="n">
+      <c r="B135" s="64" t="n">
         <v>46273</v>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3349,19 +3358,19 @@
           <t>Sr Enterprise Developer (Power Platform Developer)</t>
         </is>
       </c>
-      <c r="D135" s="62" t="inlineStr">
+      <c r="D135" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455767052/</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B136" s="61" t="n">
+      <c r="A136" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B136" s="64" t="n">
         <v>46273</v>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3369,19 +3378,19 @@
           <t>Software QA Engineer 2</t>
         </is>
       </c>
-      <c r="D136" s="62" t="inlineStr">
+      <c r="D136" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464606837/</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="60" t="inlineStr">
+      <c r="A137" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B137" s="61" t="n">
+      <c r="B137" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -3389,19 +3398,19 @@
           <t>SW Test Development Engineer 1</t>
         </is>
       </c>
-      <c r="D137" s="62" t="inlineStr">
+      <c r="D137" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465029007/</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="60" t="inlineStr">
+      <c r="A138" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B138" s="61" t="n">
+      <c r="B138" s="64" t="n">
         <v>46273</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -3409,19 +3418,19 @@
           <t>SW Development Engineer 2 - Android</t>
         </is>
       </c>
-      <c r="D138" s="62" t="inlineStr">
+      <c r="D138" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464610755/</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B139" s="61" t="n">
+      <c r="A139" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B139" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -3429,19 +3438,19 @@
           <t>Sr Workplace Solutions Analyst</t>
         </is>
       </c>
-      <c r="D139" s="62" t="inlineStr">
+      <c r="D139" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322161/</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="60" t="inlineStr">
+      <c r="A140" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B140" s="61" t="n">
+      <c r="B140" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -3449,19 +3458,19 @@
           <t>Staff SW Development Engineer</t>
         </is>
       </c>
-      <c r="D140" s="62" t="inlineStr">
+      <c r="D140" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465323573/</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="60" t="inlineStr">
+      <c r="A141" s="63" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B141" s="61" t="n">
+      <c r="B141" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -3469,19 +3478,19 @@
           <t>Director, Business Program Management Office</t>
         </is>
       </c>
-      <c r="D141" s="62" t="inlineStr">
+      <c r="D141" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456105988/</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="60" t="inlineStr">
+      <c r="A142" s="63" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B142" s="61" t="n">
+      <c r="B142" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -3489,19 +3498,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D142" s="62" t="inlineStr">
+      <c r="D142" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456115187/</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B143" s="61" t="n">
+      <c r="A143" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B143" s="64" t="n">
         <v>46274</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -3509,19 +3518,19 @@
           <t>Systems Design &amp; Test Engineer 2</t>
         </is>
       </c>
-      <c r="D143" s="62" t="inlineStr">
+      <c r="D143" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443989564/</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B144" s="61" t="n">
+      <c r="A144" s="63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B144" s="64" t="n">
         <v>46275</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -3529,19 +3538,19 @@
           <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
         </is>
       </c>
-      <c r="D144" s="62" t="inlineStr">
+      <c r="D144" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439394782/</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="60" t="inlineStr">
+      <c r="A145" s="63" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B145" s="61" t="n">
+      <c r="B145" s="64" t="n">
         <v>46273</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -3549,7 +3558,7 @@
           <t>Sr. SW Test Development Engineer V&amp;V</t>
         </is>
       </c>
-      <c r="D145" s="62" t="inlineStr">
+      <c r="D145" s="65" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387839555/</t>
         </is>
@@ -4235,8 +4244,68 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B180" s="67" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Technician 4 ( Dobson ) 2B Night Shift: Wed-Fri, every other Sat.</t>
+        </is>
+      </c>
+      <c r="D180" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467703315/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B181" s="67" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>HCP Marketing Manager (Stelo)</t>
+        </is>
+      </c>
+      <c r="D181" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442796306/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B182" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Federal Clinical Educator - East</t>
+        </is>
+      </c>
+      <c r="D182" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455357586/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D179"/>
+  <autoFilter ref="A1:D182"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -4416,6 +4485,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId181"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -653,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -685,12 +694,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="64" t="n">
+      <c r="B2" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -698,19 +707,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="65" t="inlineStr">
+      <c r="D2" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="63" t="inlineStr">
+      <c r="A3" s="66" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="64" t="n">
+      <c r="B3" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -718,19 +727,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="65" t="inlineStr">
+      <c r="D3" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="64" t="n">
+      <c r="B4" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -738,19 +747,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="65" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="64" t="n">
+      <c r="B5" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -758,19 +767,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="65" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="63" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="64" t="n">
+      <c r="B6" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -778,19 +787,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="65" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="64" t="n">
+      <c r="B7" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -798,19 +807,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="63" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="64" t="n">
+      <c r="B8" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -818,19 +827,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="65" t="inlineStr">
+      <c r="D8" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="64" t="n">
+      <c r="B9" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -838,19 +847,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D9" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="63" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="64" t="n">
+      <c r="B10" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -858,19 +867,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="65" t="inlineStr">
+      <c r="D10" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="64" t="n">
+      <c r="B11" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -878,19 +887,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="65" t="inlineStr">
+      <c r="D11" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="63" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="64" t="n">
+      <c r="B12" s="67" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -898,19 +907,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="65" t="inlineStr">
+      <c r="D12" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="64" t="n">
+      <c r="B13" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -918,19 +927,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="65" t="inlineStr">
+      <c r="D13" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="63" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="64" t="n">
+      <c r="B14" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -938,19 +947,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="65" t="inlineStr">
+      <c r="D14" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="64" t="n">
+      <c r="A15" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -958,19 +967,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="65" t="inlineStr">
+      <c r="D15" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="63" t="inlineStr">
+      <c r="A16" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="64" t="n">
+      <c r="B16" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -978,19 +987,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="65" t="inlineStr">
+      <c r="D16" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="63" t="inlineStr">
+      <c r="A17" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="64" t="n">
+      <c r="B17" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -998,19 +1007,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="65" t="inlineStr">
+      <c r="D17" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="63" t="inlineStr">
+      <c r="A18" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="64" t="n">
+      <c r="B18" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1018,19 +1027,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="65" t="inlineStr">
+      <c r="D18" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="63" t="inlineStr">
+      <c r="A19" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="64" t="n">
+      <c r="B19" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1038,19 +1047,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="65" t="inlineStr">
+      <c r="D19" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="63" t="inlineStr">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="64" t="n">
+      <c r="B20" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1058,19 +1067,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="65" t="inlineStr">
+      <c r="D20" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B21" s="64" t="n">
+      <c r="A21" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1078,19 +1087,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="65" t="inlineStr">
+      <c r="D21" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="63" t="inlineStr">
+      <c r="A22" s="66" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="64" t="n">
+      <c r="B22" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1098,19 +1107,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="65" t="inlineStr">
+      <c r="D22" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B23" s="64" t="n">
+      <c r="A23" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B23" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1118,19 +1127,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="65" t="inlineStr">
+      <c r="D23" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="64" t="n">
+      <c r="B24" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1138,19 +1147,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="65" t="inlineStr">
+      <c r="D24" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="63" t="inlineStr">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="64" t="n">
+      <c r="B25" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1158,19 +1167,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="65" t="inlineStr">
+      <c r="D25" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="63" t="inlineStr">
+      <c r="A26" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="64" t="n">
+      <c r="B26" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1178,19 +1187,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="65" t="inlineStr">
+      <c r="D26" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="63" t="inlineStr">
+      <c r="A27" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="64" t="n">
+      <c r="B27" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1198,19 +1207,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="65" t="inlineStr">
+      <c r="D27" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="63" t="inlineStr">
+      <c r="A28" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="64" t="n">
+      <c r="B28" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1218,19 +1227,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="65" t="inlineStr">
+      <c r="D28" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="63" t="inlineStr">
+      <c r="A29" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="64" t="n">
+      <c r="B29" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1238,19 +1247,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="65" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="63" t="inlineStr">
+      <c r="A30" s="66" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="64" t="n">
+      <c r="B30" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1258,19 +1267,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="65" t="inlineStr">
+      <c r="D30" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="63" t="inlineStr">
+      <c r="A31" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="64" t="n">
+      <c r="B31" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1278,19 +1287,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="65" t="inlineStr">
+      <c r="D31" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="64" t="n">
+      <c r="A32" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1298,19 +1307,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="65" t="inlineStr">
+      <c r="D32" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="64" t="n">
+      <c r="A33" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1318,19 +1327,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="65" t="inlineStr">
+      <c r="D33" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="63" t="inlineStr">
+      <c r="A34" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="64" t="n">
+      <c r="B34" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1338,19 +1347,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="65" t="inlineStr">
+      <c r="D34" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="63" t="inlineStr">
+      <c r="A35" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="64" t="n">
+      <c r="B35" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1358,19 +1367,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="65" t="inlineStr">
+      <c r="D35" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="63" t="inlineStr">
+      <c r="A36" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="64" t="n">
+      <c r="B36" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1378,19 +1387,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="65" t="inlineStr">
+      <c r="D36" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="63" t="inlineStr">
+      <c r="A37" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="64" t="n">
+      <c r="B37" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1398,19 +1407,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="65" t="inlineStr">
+      <c r="D37" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="63" t="inlineStr">
+      <c r="A38" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="64" t="n">
+      <c r="B38" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1418,19 +1427,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="65" t="inlineStr">
+      <c r="D38" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="63" t="inlineStr">
+      <c r="A39" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="64" t="n">
+      <c r="B39" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1438,19 +1447,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="65" t="inlineStr">
+      <c r="D39" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="63" t="inlineStr">
+      <c r="A40" s="66" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="64" t="n">
+      <c r="B40" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1458,19 +1467,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="65" t="inlineStr">
+      <c r="D40" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="63" t="inlineStr">
+      <c r="A41" s="66" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="64" t="n">
+      <c r="B41" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1478,19 +1487,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="65" t="inlineStr">
+      <c r="D41" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B42" s="64" t="n">
+      <c r="A42" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B42" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1498,19 +1507,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="65" t="inlineStr">
+      <c r="D42" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="64" t="n">
+      <c r="A43" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1518,19 +1527,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="65" t="inlineStr">
+      <c r="D43" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="63" t="inlineStr">
+      <c r="A44" s="66" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="64" t="n">
+      <c r="B44" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1538,19 +1547,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="65" t="inlineStr">
+      <c r="D44" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="63" t="inlineStr">
+      <c r="A45" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="64" t="n">
+      <c r="B45" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1558,19 +1567,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="65" t="inlineStr">
+      <c r="D45" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="64" t="n">
+      <c r="A46" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1578,19 +1587,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="65" t="inlineStr">
+      <c r="D46" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="63" t="inlineStr">
+      <c r="A47" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="64" t="n">
+      <c r="B47" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1598,19 +1607,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="65" t="inlineStr">
+      <c r="D47" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="63" t="inlineStr">
+      <c r="A48" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="64" t="n">
+      <c r="B48" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1618,19 +1627,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="65" t="inlineStr">
+      <c r="D48" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="63" t="inlineStr">
+      <c r="A49" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="64" t="n">
+      <c r="B49" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1638,19 +1647,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="65" t="inlineStr">
+      <c r="D49" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="63" t="inlineStr">
+      <c r="A50" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="64" t="n">
+      <c r="B50" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1658,19 +1667,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="65" t="inlineStr">
+      <c r="D50" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="63" t="inlineStr">
+      <c r="A51" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="64" t="n">
+      <c r="B51" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1678,19 +1687,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="65" t="inlineStr">
+      <c r="D51" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="63" t="inlineStr">
+      <c r="A52" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="64" t="n">
+      <c r="B52" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1698,19 +1707,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="65" t="inlineStr">
+      <c r="D52" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="63" t="inlineStr">
+      <c r="A53" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="64" t="n">
+      <c r="B53" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1718,19 +1727,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="65" t="inlineStr">
+      <c r="D53" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="63" t="inlineStr">
+      <c r="A54" s="66" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="64" t="n">
+      <c r="B54" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1738,19 +1747,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="65" t="inlineStr">
+      <c r="D54" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="63" t="inlineStr">
+      <c r="A55" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="64" t="n">
+      <c r="B55" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1758,19 +1767,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="65" t="inlineStr">
+      <c r="D55" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="63" t="inlineStr">
+      <c r="A56" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="64" t="n">
+      <c r="B56" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1778,19 +1787,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="65" t="inlineStr">
+      <c r="D56" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="63" t="inlineStr">
+      <c r="A57" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="64" t="n">
+      <c r="B57" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1798,19 +1807,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="65" t="inlineStr">
+      <c r="D57" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="63" t="inlineStr">
+      <c r="A58" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="64" t="n">
+      <c r="B58" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1818,19 +1827,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="65" t="inlineStr">
+      <c r="D58" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="64" t="n">
+      <c r="A59" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1838,19 +1847,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="65" t="inlineStr">
+      <c r="D59" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="63" t="inlineStr">
+      <c r="A60" s="66" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="64" t="n">
+      <c r="B60" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1858,19 +1867,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="65" t="inlineStr">
+      <c r="D60" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B61" s="64" t="n">
+      <c r="A61" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B61" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1878,19 +1887,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="65" t="inlineStr">
+      <c r="D61" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="63" t="inlineStr">
+      <c r="A62" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="64" t="n">
+      <c r="B62" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1898,19 +1907,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="65" t="inlineStr">
+      <c r="D62" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="64" t="n">
+      <c r="A63" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1918,19 +1927,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="65" t="inlineStr">
+      <c r="D63" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="63" t="inlineStr">
+      <c r="A64" s="66" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="64" t="n">
+      <c r="B64" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1938,19 +1947,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="65" t="inlineStr">
+      <c r="D64" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B65" s="64" t="n">
+      <c r="A65" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B65" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1958,19 +1967,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="65" t="inlineStr">
+      <c r="D65" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="63" t="inlineStr">
+      <c r="A66" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="64" t="n">
+      <c r="B66" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1978,19 +1987,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="65" t="inlineStr">
+      <c r="D66" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B67" s="64" t="n">
+      <c r="A67" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B67" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1998,19 +2007,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="65" t="inlineStr">
+      <c r="D67" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="63" t="inlineStr">
+      <c r="A68" s="66" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="64" t="n">
+      <c r="B68" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -2018,19 +2027,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="65" t="inlineStr">
+      <c r="D68" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="63" t="inlineStr">
+      <c r="A69" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="64" t="n">
+      <c r="B69" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2038,19 +2047,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="65" t="inlineStr">
+      <c r="D69" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="63" t="inlineStr">
+      <c r="A70" s="66" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="64" t="n">
+      <c r="B70" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2058,19 +2067,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="65" t="inlineStr">
+      <c r="D70" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="63" t="inlineStr">
+      <c r="A71" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="64" t="n">
+      <c r="B71" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2078,19 +2087,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="65" t="inlineStr">
+      <c r="D71" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="63" t="inlineStr">
+      <c r="A72" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="64" t="n">
+      <c r="B72" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2098,19 +2107,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="65" t="inlineStr">
+      <c r="D72" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="63" t="inlineStr">
+      <c r="A73" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="64" t="n">
+      <c r="B73" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2118,19 +2127,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="65" t="inlineStr">
+      <c r="D73" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="63" t="inlineStr">
+      <c r="A74" s="66" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="64" t="n">
+      <c r="B74" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2138,19 +2147,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="65" t="inlineStr">
+      <c r="D74" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="63" t="inlineStr">
+      <c r="A75" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="64" t="n">
+      <c r="B75" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2158,19 +2167,19 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="65" t="inlineStr">
+      <c r="D75" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="63" t="inlineStr">
+      <c r="A76" s="66" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B76" s="64" t="n">
+      <c r="B76" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2178,19 +2187,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D76" s="65" t="inlineStr">
+      <c r="D76" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="63" t="inlineStr">
+      <c r="A77" s="66" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B77" s="64" t="n">
+      <c r="B77" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2198,19 +2207,19 @@
           <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
         </is>
       </c>
-      <c r="D77" s="65" t="inlineStr">
+      <c r="D77" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765129/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="63" t="inlineStr">
+      <c r="A78" s="66" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="64" t="n">
+      <c r="B78" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2218,19 +2227,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D78" s="65" t="inlineStr">
+      <c r="D78" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="63" t="inlineStr">
+      <c r="A79" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B79" s="64" t="n">
+      <c r="B79" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2238,19 +2247,19 @@
           <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
-      <c r="D79" s="65" t="inlineStr">
+      <c r="D79" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="63" t="inlineStr">
+      <c r="A80" s="66" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B80" s="64" t="n">
+      <c r="B80" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2258,19 +2267,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D80" s="65" t="inlineStr">
+      <c r="D80" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="63" t="inlineStr">
+      <c r="A81" s="66" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B81" s="64" t="n">
+      <c r="B81" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2278,19 +2287,19 @@
           <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
         </is>
       </c>
-      <c r="D81" s="65" t="inlineStr">
+      <c r="D81" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450696746/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="63" t="inlineStr">
+      <c r="A82" s="66" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="64" t="n">
+      <c r="B82" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2298,19 +2307,19 @@
           <t>Logistics Analyst</t>
         </is>
       </c>
-      <c r="D82" s="65" t="inlineStr">
+      <c r="D82" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461266744/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="63" t="inlineStr">
+      <c r="A83" s="66" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B83" s="64" t="n">
+      <c r="B83" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2318,19 +2327,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D83" s="65" t="inlineStr">
+      <c r="D83" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="63" t="inlineStr">
+      <c r="A84" s="66" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B84" s="64" t="n">
+      <c r="B84" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2338,19 +2347,19 @@
           <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D84" s="65" t="inlineStr">
+      <c r="D84" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459309508/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="63" t="inlineStr">
+      <c r="A85" s="66" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" s="64" t="n">
+      <c r="B85" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2358,19 +2367,19 @@
           <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
         </is>
       </c>
-      <c r="D85" s="65" t="inlineStr">
+      <c r="D85" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770007/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="63" t="inlineStr">
+      <c r="A86" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="64" t="n">
+      <c r="B86" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2378,19 +2387,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D86" s="65" t="inlineStr">
+      <c r="D86" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="63" t="inlineStr">
+      <c r="A87" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B87" s="64" t="n">
+      <c r="B87" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2398,19 +2407,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D87" s="65" t="inlineStr">
+      <c r="D87" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="63" t="inlineStr">
+      <c r="A88" s="66" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B88" s="64" t="n">
+      <c r="B88" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2418,19 +2427,19 @@
           <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
-      <c r="D88" s="65" t="inlineStr">
+      <c r="D88" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="63" t="inlineStr">
+      <c r="A89" s="66" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="64" t="n">
+      <c r="B89" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2438,19 +2447,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D89" s="65" t="inlineStr">
+      <c r="D89" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="63" t="inlineStr">
+      <c r="A90" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B90" s="64" t="n">
+      <c r="B90" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2458,19 +2467,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D90" s="65" t="inlineStr">
+      <c r="D90" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="63" t="inlineStr">
+      <c r="A91" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B91" s="64" t="n">
+      <c r="B91" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2478,19 +2487,19 @@
           <t>Contract Administration Representative (French-speaking)</t>
         </is>
       </c>
-      <c r="D91" s="65" t="inlineStr">
+      <c r="D91" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461090763/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="63" t="inlineStr">
+      <c r="A92" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B92" s="64" t="n">
+      <c r="B92" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2498,19 +2507,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D92" s="65" t="inlineStr">
+      <c r="D92" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="63" t="inlineStr">
+      <c r="A93" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B93" s="64" t="n">
+      <c r="B93" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2518,19 +2527,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D93" s="65" t="inlineStr">
+      <c r="D93" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="63" t="inlineStr">
+      <c r="A94" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B94" s="64" t="n">
+      <c r="B94" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2538,19 +2547,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D94" s="65" t="inlineStr">
+      <c r="D94" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453089165/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="63" t="inlineStr">
+      <c r="A95" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B95" s="64" t="n">
+      <c r="B95" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2558,19 +2567,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D95" s="65" t="inlineStr">
+      <c r="D95" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="63" t="inlineStr">
+      <c r="A96" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B96" s="64" t="n">
+      <c r="B96" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2578,19 +2587,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D96" s="65" t="inlineStr">
+      <c r="D96" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="63" t="inlineStr">
+      <c r="A97" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B97" s="64" t="n">
+      <c r="B97" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2598,19 +2607,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D97" s="65" t="inlineStr">
+      <c r="D97" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="63" t="inlineStr">
+      <c r="A98" s="66" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B98" s="64" t="n">
+      <c r="B98" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2618,19 +2627,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D98" s="65" t="inlineStr">
+      <c r="D98" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="63" t="inlineStr">
+      <c r="A99" s="66" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B99" s="64" t="n">
+      <c r="B99" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2638,19 +2647,19 @@
           <t>Technical Support Representative 2</t>
         </is>
       </c>
-      <c r="D99" s="65" t="inlineStr">
+      <c r="D99" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438880089/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="63" t="inlineStr">
+      <c r="A100" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B100" s="64" t="n">
+      <c r="B100" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2658,19 +2667,19 @@
           <t>Spanish Bilingual Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D100" s="65" t="inlineStr">
+      <c r="D100" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458704406/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="63" t="inlineStr">
+      <c r="A101" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B101" s="64" t="n">
+      <c r="B101" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2678,19 +2687,19 @@
           <t>Spanish Bilingual TSR</t>
         </is>
       </c>
-      <c r="D101" s="65" t="inlineStr">
+      <c r="D101" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407814543/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B102" s="64" t="n">
+      <c r="A102" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B102" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2698,19 +2707,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D102" s="65" t="inlineStr">
+      <c r="D102" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="63" t="inlineStr">
+      <c r="A103" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B103" s="64" t="n">
+      <c r="B103" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2718,19 +2727,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D103" s="65" t="inlineStr">
+      <c r="D103" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B104" s="64" t="n">
+      <c r="A104" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B104" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2738,19 +2747,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D104" s="65" t="inlineStr">
+      <c r="D104" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B105" s="64" t="n">
+      <c r="A105" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B105" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2758,19 +2767,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D105" s="65" t="inlineStr">
+      <c r="D105" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B106" s="64" t="n">
+      <c r="A106" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B106" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2778,19 +2787,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D106" s="65" t="inlineStr">
+      <c r="D106" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439353245/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="63" t="inlineStr">
+      <c r="A107" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B107" s="64" t="n">
+      <c r="B107" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2798,19 +2807,19 @@
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="D107" s="65" t="inlineStr">
+      <c r="D107" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="63" t="inlineStr">
+      <c r="A108" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B108" s="64" t="n">
+      <c r="B108" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2818,19 +2827,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D108" s="65" t="inlineStr">
+      <c r="D108" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082223/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="63" t="inlineStr">
+      <c r="A109" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B109" s="64" t="n">
+      <c r="B109" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2838,19 +2847,19 @@
           <t>Business Process Analyst</t>
         </is>
       </c>
-      <c r="D109" s="65" t="inlineStr">
+      <c r="D109" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414569192/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B110" s="64" t="n">
+      <c r="A110" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2858,19 +2867,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D110" s="65" t="inlineStr">
+      <c r="D110" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456380639/</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B111" s="64" t="n">
+      <c r="A111" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B111" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2878,19 +2887,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D111" s="65" t="inlineStr">
+      <c r="D111" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456364824/</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="63" t="inlineStr">
+      <c r="A112" s="66" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B112" s="64" t="n">
+      <c r="B112" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -2898,19 +2907,19 @@
           <t>Associate Marketing Manager</t>
         </is>
       </c>
-      <c r="D112" s="65" t="inlineStr">
+      <c r="D112" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451399530/</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B113" s="64" t="n">
+      <c r="A113" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B113" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -2918,19 +2927,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D113" s="65" t="inlineStr">
+      <c r="D113" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B114" s="64" t="n">
+      <c r="A114" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B114" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -2938,19 +2947,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D114" s="65" t="inlineStr">
+      <c r="D114" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="63" t="inlineStr">
+      <c r="A115" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B115" s="64" t="n">
+      <c r="B115" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -2958,19 +2967,19 @@
           <t>Senior Sterilization Engineer</t>
         </is>
       </c>
-      <c r="D115" s="65" t="inlineStr">
+      <c r="D115" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410980549/</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="63" t="inlineStr">
+      <c r="A116" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B116" s="64" t="n">
+      <c r="B116" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -2978,19 +2987,19 @@
           <t>Accounts Payable Process Expert (Maternity Cover)</t>
         </is>
       </c>
-      <c r="D116" s="65" t="inlineStr">
+      <c r="D116" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462464542/</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="63" t="inlineStr">
+      <c r="A117" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B117" s="64" t="n">
+      <c r="B117" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -2998,19 +3007,19 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D117" s="65" t="inlineStr">
+      <c r="D117" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B118" s="64" t="n">
+      <c r="A118" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B118" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -3018,19 +3027,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D118" s="65" t="inlineStr">
+      <c r="D118" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="63" t="inlineStr">
+      <c r="A119" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B119" s="64" t="n">
+      <c r="B119" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3038,19 +3047,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D119" s="65" t="inlineStr">
+      <c r="D119" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B120" s="64" t="n">
+      <c r="A120" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B120" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3058,19 +3067,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D120" s="65" t="inlineStr">
+      <c r="D120" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="63" t="inlineStr">
+      <c r="A121" s="66" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B121" s="64" t="n">
+      <c r="B121" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3078,19 +3087,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D121" s="65" t="inlineStr">
+      <c r="D121" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B122" s="64" t="n">
+      <c r="A122" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B122" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3098,19 +3107,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D122" s="65" t="inlineStr">
+      <c r="D122" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="63" t="inlineStr">
+      <c r="A123" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B123" s="64" t="n">
+      <c r="B123" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3118,19 +3127,19 @@
           <t>Staff SRE SW Development Engineer</t>
         </is>
       </c>
-      <c r="D123" s="65" t="inlineStr">
+      <c r="D123" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387683946/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B124" s="64" t="n">
+      <c r="A124" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B124" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3138,19 +3147,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D124" s="65" t="inlineStr">
+      <c r="D124" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B125" s="64" t="n">
+      <c r="A125" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B125" s="67" t="n">
         <v>46275</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3158,19 +3167,19 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D125" s="65" t="inlineStr">
+      <c r="D125" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="63" t="inlineStr">
+      <c r="A126" s="66" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B126" s="64" t="n">
+      <c r="B126" s="67" t="n">
         <v>46276</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3178,19 +3187,19 @@
           <t>Third Party Risk and Supplier Onboarding Manager</t>
         </is>
       </c>
-      <c r="D126" s="65" t="inlineStr">
+      <c r="D126" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466048486/</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="63" t="inlineStr">
+      <c r="A127" s="66" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B127" s="64" t="n">
+      <c r="B127" s="67" t="n">
         <v>46274</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3198,1114 +3207,1614 @@
           <t>Senior Service Designer, Technical Support</t>
         </is>
       </c>
-      <c r="D127" s="65" t="inlineStr">
+      <c r="D127" s="68" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455960251/</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="63" t="inlineStr">
+      <c r="A128" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B128" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Process Development Engineer</t>
+        </is>
+      </c>
+      <c r="D128" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="66" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B129" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Manufacturing</t>
+        </is>
+      </c>
+      <c r="D129" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4428861138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="66" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B130" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Staff Database Administrator</t>
+        </is>
+      </c>
+      <c r="D130" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="66" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B131" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Payroll Analyst (ANZ)</t>
+        </is>
+      </c>
+      <c r="D131" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B132" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="D132" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B133" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Sr Workplace Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="D133" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B134" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Staff SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D134" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="66" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B135" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Director, Business Program Management Office</t>
+        </is>
+      </c>
+      <c r="D135" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="66" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B136" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 4</t>
+        </is>
+      </c>
+      <c r="D136" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B137" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Systems Design &amp; Test Engineer 2</t>
+        </is>
+      </c>
+      <c r="D137" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B138" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
+        </is>
+      </c>
+      <c r="D138" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439394782/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B139" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 1 - Android</t>
+        </is>
+      </c>
+      <c r="D139" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="66" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B140" s="67" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Financial Analyst</t>
+        </is>
+      </c>
+      <c r="D140" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4421230278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B141" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Sr Cybersecurity Analyst</t>
+        </is>
+      </c>
+      <c r="D141" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439085443/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B142" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D142" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4460357219/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="66" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B143" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Trade Compliance Analyst</t>
+        </is>
+      </c>
+      <c r="D143" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467033928/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B144" s="67" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manufacturing Engineer</t>
+        </is>
+      </c>
+      <c r="D144" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447583072/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="66" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B128" s="64" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>Process Technician 2 (Front End Night Shift)</t>
-        </is>
-      </c>
-      <c r="D128" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B129" s="64" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>Manager Systems Design Engineering</t>
-        </is>
-      </c>
-      <c r="D129" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464683405/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B130" s="64" t="n">
+      <c r="B145" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Staff Vendor Management Analyst</t>
+        </is>
+      </c>
+      <c r="D145" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458212554/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="66" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B146" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Staff Equipment Engineer</t>
+        </is>
+      </c>
+      <c r="D146" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458218533/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="66" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B147" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>APAC Product Manager - OTC/Consumer Health</t>
+        </is>
+      </c>
+      <c r="D147" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4422693615/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="66" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B148" s="67" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Technical Support - Manila</t>
+        </is>
+      </c>
+      <c r="D148" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417742237/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="66" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B149" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Staff Desktop Support Engineer</t>
+        </is>
+      </c>
+      <c r="D149" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4398315987/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B150" s="67" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Director HW Design Quality Engineering - New Product Introductions</t>
+        </is>
+      </c>
+      <c r="D150" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456789792/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B151" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Manager SW Test Development Engineering</t>
+        </is>
+      </c>
+      <c r="D151" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4281993770/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B152" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
+        </is>
+      </c>
+      <c r="D152" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="66" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B153" s="67" t="n">
         <v>46274</v>
       </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>Senior Staff Process Development Engineer</t>
-        </is>
-      </c>
-      <c r="D130" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="63" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor, Applications Support</t>
+        </is>
+      </c>
+      <c r="D153" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456333076/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B154" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>Hardware Engineer 2</t>
+        </is>
+      </c>
+      <c r="D154" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="66" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B155" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Territory Business Manager - South Island</t>
+        </is>
+      </c>
+      <c r="D155" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456111920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="66" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B156" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>Sr Staff Program Manager</t>
+        </is>
+      </c>
+      <c r="D156" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448138066/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B157" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>Senior Manager- Manufacturing IT Strategic Initiatives and Architecture</t>
+        </is>
+      </c>
+      <c r="D157" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4421221561/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="66" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B158" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>Manager Process Engineering</t>
+        </is>
+      </c>
+      <c r="D158" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467096658/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="66" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B131" s="64" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="B159" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2 - IOS</t>
+        </is>
+      </c>
+      <c r="D159" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465306719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B160" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>Staff Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D160" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461770016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B161" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>District Business Manager - Ohio</t>
+        </is>
+      </c>
+      <c r="D161" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458551771/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B162" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D162" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4375183129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B163" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Lead Firmware V&amp;V</t>
+        </is>
+      </c>
+      <c r="D163" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4402920307/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B164" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D164" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461756319/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B165" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Senior Lead Government Affairs Manager - Federal</t>
+        </is>
+      </c>
+      <c r="D165" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440825647/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="66" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B166" s="67" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Staff Database Administrator</t>
+        </is>
+      </c>
+      <c r="D166" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456333107/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B167" s="67" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Technician 2 (2A Sunday - Tuesday, every other Saturday from 5:00PM - 5:00AM )</t>
+        </is>
+      </c>
+      <c r="D167" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466467687/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B168" s="67" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Technician 2 (2B Wednesday - Friday, every other Saturday from 5:00PM - 5:00AM)</t>
+        </is>
+      </c>
+      <c r="D168" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466428944/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B169" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>New Business Development Manager, Trade Partnerships (eCommerce)</t>
+        </is>
+      </c>
+      <c r="D169" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459020959/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B170" s="67" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Sr Firmware V&amp;V</t>
+        </is>
+      </c>
+      <c r="D170" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4402292560/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B171" s="67" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Sr Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="D171" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457557361/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B172" s="67" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>Staff Enterprise Applications Developer - IBM Maximo</t>
+        </is>
+      </c>
+      <c r="D172" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4411935028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B173" s="67" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Technician 4 ( Dobson ) 2B Night Shift: Wed-Fri, every other Sat.</t>
+        </is>
+      </c>
+      <c r="D173" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467703315/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B174" s="67" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>HCP Marketing Manager (Stelo)</t>
+        </is>
+      </c>
+      <c r="D174" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442796306/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B175" s="67" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Federal Clinical Educator - East</t>
+        </is>
+      </c>
+      <c r="D175" s="68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455357586/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="69" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B176" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>Sr Legal Counsel, EMEA Privacy</t>
+        </is>
+      </c>
+      <c r="D176" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448305175/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="69" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B177" s="70" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Lead Financial Analyst</t>
+        </is>
+      </c>
+      <c r="D177" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467930929/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="69" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B178" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2 - Android</t>
+        </is>
+      </c>
+      <c r="D178" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="69" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B179" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Manager Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D179" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467753397/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B180" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Staff Business Financial Analyst - IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="D180" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461264820/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="69" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B181" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Senior Market Access Manager CEE – Healthcare</t>
+        </is>
+      </c>
+      <c r="D181" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467756362/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="69" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B182" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Sr Equipment Engineer</t>
+        </is>
+      </c>
+      <c r="D182" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467749492/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B183" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Territory Business Manager - Central / SE Alabama</t>
+        </is>
+      </c>
+      <c r="D183" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448610622/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B184" s="70" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Associate Customer Insights Manager</t>
+        </is>
+      </c>
+      <c r="D184" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434083415/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B185" s="70" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Planner Analyst</t>
+        </is>
+      </c>
+      <c r="D185" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457555402/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B186" s="70" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering Manager</t>
+        </is>
+      </c>
+      <c r="D186" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447571908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B187" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Data Protection and Insider Risk</t>
+        </is>
+      </c>
+      <c r="D187" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467266843/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="69" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B188" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>Brand &amp; Portfolio Marketing Lead - DACH (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D188" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467076868/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="69" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B189" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
         <is>
           <t>Manager, SW System &amp; Solution Dev Engineer</t>
         </is>
       </c>
-      <c r="D131" s="65" t="inlineStr">
+      <c r="D189" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="63" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B190" s="70" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>Process Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D190" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466463712/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B191" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>Sr Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="D191" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453636185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B192" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Payor Analytics Senior Pricing Analyst</t>
+        </is>
+      </c>
+      <c r="D192" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467785422/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B193" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Associate Marketing Manager, Digital Projects</t>
+        </is>
+      </c>
+      <c r="D193" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458569116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B132" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>Supervisor Manufacturing</t>
-        </is>
-      </c>
-      <c r="D132" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4428861138/</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="63" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B133" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Staff Database Administrator</t>
-        </is>
-      </c>
-      <c r="D133" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="63" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B134" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>Payroll Analyst (ANZ)</t>
-        </is>
-      </c>
-      <c r="D134" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="63" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B135" s="64" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>Sr Enterprise Developer (Power Platform Developer)</t>
-        </is>
-      </c>
-      <c r="D135" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B136" s="64" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>Software QA Engineer 2</t>
-        </is>
-      </c>
-      <c r="D136" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="63" t="inlineStr">
+      <c r="B194" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>Sr Automation Engineer</t>
+        </is>
+      </c>
+      <c r="D194" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467078747/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="69" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B195" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>Technical Support Representative, Dutch Speaker</t>
+        </is>
+      </c>
+      <c r="D195" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4364850511/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B196" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Technician 3 ( 1A Sunday - Tuesday, every other Wednesday from 5:00AM to 5:00PM)</t>
+        </is>
+      </c>
+      <c r="D196" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466422908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B197" s="70" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>Sr SW Test Development Engineer</t>
+        </is>
+      </c>
+      <c r="D197" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457511030/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="69" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B198" s="70" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Production Operator - Days - Athenry</t>
+        </is>
+      </c>
+      <c r="D198" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457002672/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B137" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>SW Test Development Engineer 1</t>
-        </is>
-      </c>
-      <c r="D137" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="63" t="inlineStr">
+      <c r="B199" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D199" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457076040/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B200" s="70" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff SW Systems Engineer - Mobile Apps</t>
+        </is>
+      </c>
+      <c r="D200" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438120759/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B201" s="70" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Staff Algorithm Engineer - Emerging Sensing Technologies</t>
+        </is>
+      </c>
+      <c r="D201" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447244362/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B202" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 1 (Shift 1A: Days - Sun - Tues every other Wed from 5AM to 5PM )</t>
+        </is>
+      </c>
+      <c r="D202" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456781801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B203" s="70" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Sr New Business Development Manager</t>
+        </is>
+      </c>
+      <c r="D203" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467430423/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B138" s="64" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>SW Development Engineer 2 - Android</t>
-        </is>
-      </c>
-      <c r="D138" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B139" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Sr Workplace Solutions Analyst</t>
-        </is>
-      </c>
-      <c r="D139" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="63" t="inlineStr">
+      <c r="B204" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>Sr. SW Test Development Engineer V&amp;V</t>
+        </is>
+      </c>
+      <c r="D204" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B205" s="70" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>Staff SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D205" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466372374/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B140" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>Staff SW Development Engineer</t>
-        </is>
-      </c>
-      <c r="D140" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="63" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B141" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>Director, Business Program Management Office</t>
-        </is>
-      </c>
-      <c r="D141" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="63" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B142" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>Engineering Technician 4</t>
-        </is>
-      </c>
-      <c r="D142" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B143" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>Systems Design &amp; Test Engineer 2</t>
-        </is>
-      </c>
-      <c r="D143" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B144" s="64" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
-        </is>
-      </c>
-      <c r="D144" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4439394782/</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="63" t="inlineStr">
+      <c r="B206" s="70" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>Sr SW Development Engineer - Android</t>
+        </is>
+      </c>
+      <c r="D206" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465019023/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B145" s="64" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>Sr. SW Test Development Engineer V&amp;V</t>
-        </is>
-      </c>
-      <c r="D145" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B146" s="64" t="n">
+      <c r="B207" s="70" t="n">
         <v>46279</v>
       </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>SW Development Engineer 1 - Android</t>
-        </is>
-      </c>
-      <c r="D146" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="63" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B147" s="64" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Financial Analyst</t>
-        </is>
-      </c>
-      <c r="D147" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4421230278/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B148" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>Sr Cybersecurity Analyst</t>
-        </is>
-      </c>
-      <c r="D148" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4439085443/</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B149" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>SW Development Engineer 2</t>
-        </is>
-      </c>
-      <c r="D149" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4460357219/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="63" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B150" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>Trade Compliance Analyst</t>
-        </is>
-      </c>
-      <c r="D150" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4467033928/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B151" s="64" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>Sr Manufacturing Engineer</t>
-        </is>
-      </c>
-      <c r="D151" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4447583072/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="63" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B152" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>Staff Vendor Management Analyst</t>
-        </is>
-      </c>
-      <c r="D152" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4458212554/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="63" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B153" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>Staff Equipment Engineer</t>
-        </is>
-      </c>
-      <c r="D153" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4458218533/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="63" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="B154" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>APAC Product Manager - OTC/Consumer Health</t>
-        </is>
-      </c>
-      <c r="D154" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4422693615/</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="63" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B155" s="64" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>Supervisor Technical Support - Manila</t>
-        </is>
-      </c>
-      <c r="D155" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4417742237/</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="63" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B156" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>Staff Desktop Support Engineer</t>
-        </is>
-      </c>
-      <c r="D156" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4398315987/</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B157" s="64" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>Director HW Design Quality Engineering - New Product Introductions</t>
-        </is>
-      </c>
-      <c r="D157" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456789792/</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B158" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>Manager SW Test Development Engineering</t>
-        </is>
-      </c>
-      <c r="D158" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4281993770/</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B159" s="64" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
-        </is>
-      </c>
-      <c r="D159" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="63" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B160" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>Supervisor, Applications Support</t>
-        </is>
-      </c>
-      <c r="D160" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456333076/</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B161" s="64" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>Hardware Engineer 2</t>
-        </is>
-      </c>
-      <c r="D161" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="63" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="B162" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>Territory Business Manager - South Island</t>
-        </is>
-      </c>
-      <c r="D162" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456111920/</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="63" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B163" s="64" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>Sr Staff Program Manager</t>
-        </is>
-      </c>
-      <c r="D163" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4448138066/</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B164" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>Senior Manager- Manufacturing IT Strategic Initiatives and Architecture</t>
-        </is>
-      </c>
-      <c r="D164" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4421221561/</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="63" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B165" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>Manager Process Engineering</t>
-        </is>
-      </c>
-      <c r="D165" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4467096658/</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B166" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>SW Development Engineer 2 - IOS</t>
-        </is>
-      </c>
-      <c r="D166" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465306719/</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B167" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>Staff Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D167" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4461770016/</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B168" s="64" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>District Business Manager - Ohio</t>
-        </is>
-      </c>
-      <c r="D168" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4458551771/</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B169" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D169" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4375183129/</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B170" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>Lead Firmware V&amp;V</t>
-        </is>
-      </c>
-      <c r="D170" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4402920307/</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B171" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D171" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4461756319/</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B172" s="64" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>Senior Lead Government Affairs Manager - Federal</t>
-        </is>
-      </c>
-      <c r="D172" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4440825647/</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="63" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B173" s="64" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>Staff Database Administrator</t>
-        </is>
-      </c>
-      <c r="D173" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456333107/</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B174" s="64" t="n">
-        <v>46277</v>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>Equipment Technician 2 (2A Sunday - Tuesday, every other Saturday from 5:00PM - 5:00AM )</t>
-        </is>
-      </c>
-      <c r="D174" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4466467687/</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B175" s="64" t="n">
-        <v>46277</v>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>Equipment Technician 2 (2B Wednesday - Friday, every other Saturday from 5:00PM - 5:00AM)</t>
-        </is>
-      </c>
-      <c r="D175" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4466428944/</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B176" s="64" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>New Business Development Manager, Trade Partnerships (eCommerce)</t>
-        </is>
-      </c>
-      <c r="D176" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4459020959/</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="63" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B177" s="64" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>Sr Firmware V&amp;V</t>
-        </is>
-      </c>
-      <c r="D177" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4402292560/</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B178" s="64" t="n">
-        <v>46277</v>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>Sr Software QA Engineer</t>
-        </is>
-      </c>
-      <c r="D178" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4457557361/</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B179" s="64" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>Staff Enterprise Applications Developer - IBM Maximo</t>
-        </is>
-      </c>
-      <c r="D179" s="65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4411935028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B180" s="67" t="n">
-        <v>46280</v>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>Equipment Technician 4 ( Dobson ) 2B Night Shift: Wed-Fri, every other Sat.</t>
-        </is>
-      </c>
-      <c r="D180" s="68" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4467703315/</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B181" s="67" t="n">
-        <v>46277</v>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>HCP Marketing Manager (Stelo)</t>
-        </is>
-      </c>
-      <c r="D181" s="68" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4442796306/</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B182" s="67" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Federal Clinical Educator - East</t>
-        </is>
-      </c>
-      <c r="D182" s="68" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455357586/</t>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Sr SW Development Engineer - IOS</t>
+        </is>
+      </c>
+      <c r="D207" s="71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465020025/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D182"/>
+  <autoFilter ref="A1:D207"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -4488,6 +4997,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId206"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -662,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D207"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -694,12 +703,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="66" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="67" t="n">
+      <c r="B2" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -707,19 +716,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="68" t="inlineStr">
+      <c r="D2" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="66" t="inlineStr">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="67" t="n">
+      <c r="B3" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -727,19 +736,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="68" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="67" t="n">
+      <c r="B4" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -747,19 +756,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="68" t="inlineStr">
+      <c r="D4" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="67" t="n">
+      <c r="B5" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -767,19 +776,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="68" t="inlineStr">
+      <c r="D5" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="67" t="n">
+      <c r="B6" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -787,19 +796,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="68" t="inlineStr">
+      <c r="D6" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="67" t="n">
+      <c r="B7" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -807,19 +816,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="68" t="inlineStr">
+      <c r="D7" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="67" t="n">
+      <c r="B8" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -827,19 +836,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="68" t="inlineStr">
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="67" t="n">
+      <c r="B9" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -847,19 +856,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="68" t="inlineStr">
+      <c r="D9" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="67" t="n">
+      <c r="B10" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -867,19 +876,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="68" t="inlineStr">
+      <c r="D10" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="66" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="67" t="n">
+      <c r="B11" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -887,19 +896,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="68" t="inlineStr">
+      <c r="D11" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="66" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="67" t="n">
+      <c r="B12" s="70" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -907,19 +916,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="68" t="inlineStr">
+      <c r="D12" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="66" t="inlineStr">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="67" t="n">
+      <c r="B13" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -927,19 +936,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="68" t="inlineStr">
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="67" t="n">
+      <c r="B14" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -947,19 +956,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="68" t="inlineStr">
+      <c r="D14" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="67" t="n">
+      <c r="A15" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -967,19 +976,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="68" t="inlineStr">
+      <c r="D15" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="66" t="inlineStr">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="67" t="n">
+      <c r="B16" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -987,19 +996,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="68" t="inlineStr">
+      <c r="D16" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="66" t="inlineStr">
+      <c r="A17" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="67" t="n">
+      <c r="B17" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1007,19 +1016,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="68" t="inlineStr">
+      <c r="D17" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="66" t="inlineStr">
+      <c r="A18" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="67" t="n">
+      <c r="B18" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1027,19 +1036,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="68" t="inlineStr">
+      <c r="D18" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="66" t="inlineStr">
+      <c r="A19" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="67" t="n">
+      <c r="B19" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1047,19 +1056,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="68" t="inlineStr">
+      <c r="D19" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="66" t="inlineStr">
+      <c r="A20" s="69" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="67" t="n">
+      <c r="B20" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1067,19 +1076,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="68" t="inlineStr">
+      <c r="D20" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B21" s="67" t="n">
+      <c r="A21" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1087,19 +1096,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="68" t="inlineStr">
+      <c r="D21" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="66" t="inlineStr">
+      <c r="A22" s="69" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="67" t="n">
+      <c r="B22" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1107,19 +1116,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="68" t="inlineStr">
+      <c r="D22" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B23" s="67" t="n">
+      <c r="A23" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B23" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1127,19 +1136,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="68" t="inlineStr">
+      <c r="D23" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="66" t="inlineStr">
+      <c r="A24" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="67" t="n">
+      <c r="B24" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1147,19 +1156,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="68" t="inlineStr">
+      <c r="D24" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="66" t="inlineStr">
+      <c r="A25" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="67" t="n">
+      <c r="B25" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1167,19 +1176,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="68" t="inlineStr">
+      <c r="D25" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="66" t="inlineStr">
+      <c r="A26" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="67" t="n">
+      <c r="B26" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1187,19 +1196,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="68" t="inlineStr">
+      <c r="D26" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="66" t="inlineStr">
+      <c r="A27" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="67" t="n">
+      <c r="B27" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1207,19 +1216,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="68" t="inlineStr">
+      <c r="D27" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="66" t="inlineStr">
+      <c r="A28" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="67" t="n">
+      <c r="B28" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1227,19 +1236,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="68" t="inlineStr">
+      <c r="D28" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="66" t="inlineStr">
+      <c r="A29" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="67" t="n">
+      <c r="B29" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1247,19 +1256,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="68" t="inlineStr">
+      <c r="D29" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="66" t="inlineStr">
+      <c r="A30" s="69" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="67" t="n">
+      <c r="B30" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1267,19 +1276,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="68" t="inlineStr">
+      <c r="D30" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="66" t="inlineStr">
+      <c r="A31" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="67" t="n">
+      <c r="B31" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1287,19 +1296,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="68" t="inlineStr">
+      <c r="D31" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="67" t="n">
+      <c r="A32" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1307,19 +1316,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="68" t="inlineStr">
+      <c r="D32" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="67" t="n">
+      <c r="A33" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1327,19 +1336,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="68" t="inlineStr">
+      <c r="D33" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="66" t="inlineStr">
+      <c r="A34" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="67" t="n">
+      <c r="B34" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1347,19 +1356,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="68" t="inlineStr">
+      <c r="D34" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="66" t="inlineStr">
+      <c r="A35" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="67" t="n">
+      <c r="B35" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1367,19 +1376,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="68" t="inlineStr">
+      <c r="D35" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="66" t="inlineStr">
+      <c r="A36" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="67" t="n">
+      <c r="B36" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1387,19 +1396,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="68" t="inlineStr">
+      <c r="D36" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="66" t="inlineStr">
+      <c r="A37" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="67" t="n">
+      <c r="B37" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1407,19 +1416,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="68" t="inlineStr">
+      <c r="D37" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="66" t="inlineStr">
+      <c r="A38" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="67" t="n">
+      <c r="B38" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1427,19 +1436,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="68" t="inlineStr">
+      <c r="D38" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="66" t="inlineStr">
+      <c r="A39" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="67" t="n">
+      <c r="B39" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1447,19 +1456,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="68" t="inlineStr">
+      <c r="D39" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="66" t="inlineStr">
+      <c r="A40" s="69" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="67" t="n">
+      <c r="B40" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1467,19 +1476,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="68" t="inlineStr">
+      <c r="D40" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="66" t="inlineStr">
+      <c r="A41" s="69" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="67" t="n">
+      <c r="B41" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1487,19 +1496,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="68" t="inlineStr">
+      <c r="D41" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B42" s="67" t="n">
+      <c r="A42" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B42" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1507,19 +1516,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="68" t="inlineStr">
+      <c r="D42" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="67" t="n">
+      <c r="A43" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1527,19 +1536,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="68" t="inlineStr">
+      <c r="D43" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="66" t="inlineStr">
+      <c r="A44" s="69" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="67" t="n">
+      <c r="B44" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1547,19 +1556,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="68" t="inlineStr">
+      <c r="D44" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="66" t="inlineStr">
+      <c r="A45" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="67" t="n">
+      <c r="B45" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1567,19 +1576,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="68" t="inlineStr">
+      <c r="D45" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="67" t="n">
+      <c r="A46" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1587,19 +1596,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="68" t="inlineStr">
+      <c r="D46" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="66" t="inlineStr">
+      <c r="A47" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="67" t="n">
+      <c r="B47" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1607,19 +1616,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="68" t="inlineStr">
+      <c r="D47" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="66" t="inlineStr">
+      <c r="A48" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="67" t="n">
+      <c r="B48" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1627,19 +1636,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="68" t="inlineStr">
+      <c r="D48" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="66" t="inlineStr">
+      <c r="A49" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="67" t="n">
+      <c r="B49" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1647,19 +1656,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="68" t="inlineStr">
+      <c r="D49" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="66" t="inlineStr">
+      <c r="A50" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="67" t="n">
+      <c r="B50" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1667,19 +1676,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="68" t="inlineStr">
+      <c r="D50" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="66" t="inlineStr">
+      <c r="A51" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="67" t="n">
+      <c r="B51" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1687,19 +1696,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="68" t="inlineStr">
+      <c r="D51" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="66" t="inlineStr">
+      <c r="A52" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="67" t="n">
+      <c r="B52" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1707,19 +1716,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="68" t="inlineStr">
+      <c r="D52" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="66" t="inlineStr">
+      <c r="A53" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="67" t="n">
+      <c r="B53" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1727,19 +1736,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="68" t="inlineStr">
+      <c r="D53" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="66" t="inlineStr">
+      <c r="A54" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="67" t="n">
+      <c r="B54" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1747,19 +1756,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="68" t="inlineStr">
+      <c r="D54" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="66" t="inlineStr">
+      <c r="A55" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="67" t="n">
+      <c r="B55" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1767,19 +1776,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="68" t="inlineStr">
+      <c r="D55" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="66" t="inlineStr">
+      <c r="A56" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="67" t="n">
+      <c r="B56" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1787,19 +1796,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="68" t="inlineStr">
+      <c r="D56" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="66" t="inlineStr">
+      <c r="A57" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="67" t="n">
+      <c r="B57" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1807,19 +1816,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="68" t="inlineStr">
+      <c r="D57" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="66" t="inlineStr">
+      <c r="A58" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="67" t="n">
+      <c r="B58" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1827,19 +1836,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="68" t="inlineStr">
+      <c r="D58" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="67" t="n">
+      <c r="A59" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1847,19 +1856,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="68" t="inlineStr">
+      <c r="D59" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="66" t="inlineStr">
+      <c r="A60" s="69" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="67" t="n">
+      <c r="B60" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1867,19 +1876,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="68" t="inlineStr">
+      <c r="D60" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B61" s="67" t="n">
+      <c r="A61" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B61" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1887,19 +1896,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="68" t="inlineStr">
+      <c r="D61" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="66" t="inlineStr">
+      <c r="A62" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="67" t="n">
+      <c r="B62" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1907,19 +1916,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="68" t="inlineStr">
+      <c r="D62" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="67" t="n">
+      <c r="A63" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1927,19 +1936,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="68" t="inlineStr">
+      <c r="D63" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="66" t="inlineStr">
+      <c r="A64" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="67" t="n">
+      <c r="B64" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1947,19 +1956,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="68" t="inlineStr">
+      <c r="D64" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B65" s="67" t="n">
+      <c r="A65" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B65" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1967,19 +1976,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="68" t="inlineStr">
+      <c r="D65" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="66" t="inlineStr">
+      <c r="A66" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="67" t="n">
+      <c r="B66" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1987,19 +1996,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="68" t="inlineStr">
+      <c r="D66" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B67" s="67" t="n">
+      <c r="A67" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B67" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2007,19 +2016,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="68" t="inlineStr">
+      <c r="D67" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="66" t="inlineStr">
+      <c r="A68" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="67" t="n">
+      <c r="B68" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -2027,19 +2036,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="68" t="inlineStr">
+      <c r="D68" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="66" t="inlineStr">
+      <c r="A69" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="67" t="n">
+      <c r="B69" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2047,19 +2056,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="68" t="inlineStr">
+      <c r="D69" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="66" t="inlineStr">
+      <c r="A70" s="69" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="67" t="n">
+      <c r="B70" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2067,19 +2076,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="68" t="inlineStr">
+      <c r="D70" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="66" t="inlineStr">
+      <c r="A71" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="67" t="n">
+      <c r="B71" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2087,19 +2096,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="68" t="inlineStr">
+      <c r="D71" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="66" t="inlineStr">
+      <c r="A72" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="67" t="n">
+      <c r="B72" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2107,19 +2116,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="68" t="inlineStr">
+      <c r="D72" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="66" t="inlineStr">
+      <c r="A73" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="67" t="n">
+      <c r="B73" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2127,19 +2136,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="68" t="inlineStr">
+      <c r="D73" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="66" t="inlineStr">
+      <c r="A74" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="67" t="n">
+      <c r="B74" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2147,19 +2156,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="68" t="inlineStr">
+      <c r="D74" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="66" t="inlineStr">
+      <c r="A75" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="67" t="n">
+      <c r="B75" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2167,19 +2176,19 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="68" t="inlineStr">
+      <c r="D75" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="66" t="inlineStr">
+      <c r="A76" s="69" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B76" s="67" t="n">
+      <c r="B76" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2187,19 +2196,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D76" s="68" t="inlineStr">
+      <c r="D76" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="66" t="inlineStr">
+      <c r="A77" s="69" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B77" s="67" t="n">
+      <c r="B77" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2207,19 +2216,19 @@
           <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
         </is>
       </c>
-      <c r="D77" s="68" t="inlineStr">
+      <c r="D77" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765129/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="66" t="inlineStr">
+      <c r="A78" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="67" t="n">
+      <c r="B78" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2227,19 +2236,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D78" s="68" t="inlineStr">
+      <c r="D78" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="66" t="inlineStr">
+      <c r="A79" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B79" s="67" t="n">
+      <c r="B79" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2247,19 +2256,19 @@
           <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
-      <c r="D79" s="68" t="inlineStr">
+      <c r="D79" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="66" t="inlineStr">
+      <c r="A80" s="69" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B80" s="67" t="n">
+      <c r="B80" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2267,19 +2276,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D80" s="68" t="inlineStr">
+      <c r="D80" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="66" t="inlineStr">
+      <c r="A81" s="69" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B81" s="67" t="n">
+      <c r="B81" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2287,19 +2296,19 @@
           <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
         </is>
       </c>
-      <c r="D81" s="68" t="inlineStr">
+      <c r="D81" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450696746/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="66" t="inlineStr">
+      <c r="A82" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="67" t="n">
+      <c r="B82" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2307,19 +2316,19 @@
           <t>Logistics Analyst</t>
         </is>
       </c>
-      <c r="D82" s="68" t="inlineStr">
+      <c r="D82" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461266744/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="66" t="inlineStr">
+      <c r="A83" s="69" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B83" s="67" t="n">
+      <c r="B83" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2327,19 +2336,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D83" s="68" t="inlineStr">
+      <c r="D83" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="66" t="inlineStr">
+      <c r="A84" s="69" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B84" s="67" t="n">
+      <c r="B84" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2347,19 +2356,19 @@
           <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D84" s="68" t="inlineStr">
+      <c r="D84" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459309508/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="66" t="inlineStr">
+      <c r="A85" s="69" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" s="67" t="n">
+      <c r="B85" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2367,19 +2376,19 @@
           <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
         </is>
       </c>
-      <c r="D85" s="68" t="inlineStr">
+      <c r="D85" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770007/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="66" t="inlineStr">
+      <c r="A86" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="67" t="n">
+      <c r="B86" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2387,19 +2396,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D86" s="68" t="inlineStr">
+      <c r="D86" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="66" t="inlineStr">
+      <c r="A87" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B87" s="67" t="n">
+      <c r="B87" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2407,19 +2416,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D87" s="68" t="inlineStr">
+      <c r="D87" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="66" t="inlineStr">
+      <c r="A88" s="69" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B88" s="67" t="n">
+      <c r="B88" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2427,19 +2436,19 @@
           <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
-      <c r="D88" s="68" t="inlineStr">
+      <c r="D88" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="66" t="inlineStr">
+      <c r="A89" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="67" t="n">
+      <c r="B89" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2447,19 +2456,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D89" s="68" t="inlineStr">
+      <c r="D89" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="66" t="inlineStr">
+      <c r="A90" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B90" s="67" t="n">
+      <c r="B90" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2467,19 +2476,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D90" s="68" t="inlineStr">
+      <c r="D90" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="66" t="inlineStr">
+      <c r="A91" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B91" s="67" t="n">
+      <c r="B91" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2487,19 +2496,19 @@
           <t>Contract Administration Representative (French-speaking)</t>
         </is>
       </c>
-      <c r="D91" s="68" t="inlineStr">
+      <c r="D91" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461090763/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="66" t="inlineStr">
+      <c r="A92" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B92" s="67" t="n">
+      <c r="B92" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2507,19 +2516,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D92" s="68" t="inlineStr">
+      <c r="D92" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="66" t="inlineStr">
+      <c r="A93" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B93" s="67" t="n">
+      <c r="B93" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2527,19 +2536,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D93" s="68" t="inlineStr">
+      <c r="D93" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="66" t="inlineStr">
+      <c r="A94" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B94" s="67" t="n">
+      <c r="B94" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2547,19 +2556,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D94" s="68" t="inlineStr">
+      <c r="D94" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453089165/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="66" t="inlineStr">
+      <c r="A95" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B95" s="67" t="n">
+      <c r="B95" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2567,19 +2576,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D95" s="68" t="inlineStr">
+      <c r="D95" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="66" t="inlineStr">
+      <c r="A96" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B96" s="67" t="n">
+      <c r="B96" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2587,19 +2596,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D96" s="68" t="inlineStr">
+      <c r="D96" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="66" t="inlineStr">
+      <c r="A97" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B97" s="67" t="n">
+      <c r="B97" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2607,19 +2616,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D97" s="68" t="inlineStr">
+      <c r="D97" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="66" t="inlineStr">
+      <c r="A98" s="69" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B98" s="67" t="n">
+      <c r="B98" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2627,19 +2636,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D98" s="68" t="inlineStr">
+      <c r="D98" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="66" t="inlineStr">
+      <c r="A99" s="69" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B99" s="67" t="n">
+      <c r="B99" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2647,19 +2656,19 @@
           <t>Technical Support Representative 2</t>
         </is>
       </c>
-      <c r="D99" s="68" t="inlineStr">
+      <c r="D99" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438880089/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="66" t="inlineStr">
+      <c r="A100" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B100" s="67" t="n">
+      <c r="B100" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2667,19 +2676,19 @@
           <t>Spanish Bilingual Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D100" s="68" t="inlineStr">
+      <c r="D100" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458704406/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="66" t="inlineStr">
+      <c r="A101" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B101" s="67" t="n">
+      <c r="B101" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2687,19 +2696,19 @@
           <t>Spanish Bilingual TSR</t>
         </is>
       </c>
-      <c r="D101" s="68" t="inlineStr">
+      <c r="D101" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407814543/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B102" s="67" t="n">
+      <c r="A102" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B102" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2707,19 +2716,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D102" s="68" t="inlineStr">
+      <c r="D102" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="66" t="inlineStr">
+      <c r="A103" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B103" s="67" t="n">
+      <c r="B103" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2727,19 +2736,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D103" s="68" t="inlineStr">
+      <c r="D103" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B104" s="67" t="n">
+      <c r="A104" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B104" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2747,19 +2756,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D104" s="68" t="inlineStr">
+      <c r="D104" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B105" s="67" t="n">
+      <c r="A105" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B105" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2767,19 +2776,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D105" s="68" t="inlineStr">
+      <c r="D105" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B106" s="67" t="n">
+      <c r="A106" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B106" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2787,19 +2796,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D106" s="68" t="inlineStr">
+      <c r="D106" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439353245/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="66" t="inlineStr">
+      <c r="A107" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B107" s="67" t="n">
+      <c r="B107" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2807,19 +2816,19 @@
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="D107" s="68" t="inlineStr">
+      <c r="D107" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="66" t="inlineStr">
+      <c r="A108" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B108" s="67" t="n">
+      <c r="B108" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2827,19 +2836,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D108" s="68" t="inlineStr">
+      <c r="D108" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082223/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="66" t="inlineStr">
+      <c r="A109" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B109" s="67" t="n">
+      <c r="B109" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2847,19 +2856,19 @@
           <t>Business Process Analyst</t>
         </is>
       </c>
-      <c r="D109" s="68" t="inlineStr">
+      <c r="D109" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414569192/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B110" s="67" t="n">
+      <c r="A110" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2867,19 +2876,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D110" s="68" t="inlineStr">
+      <c r="D110" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456380639/</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B111" s="67" t="n">
+      <c r="A111" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B111" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2887,19 +2896,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D111" s="68" t="inlineStr">
+      <c r="D111" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456364824/</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="66" t="inlineStr">
+      <c r="A112" s="69" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B112" s="67" t="n">
+      <c r="B112" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -2907,19 +2916,19 @@
           <t>Associate Marketing Manager</t>
         </is>
       </c>
-      <c r="D112" s="68" t="inlineStr">
+      <c r="D112" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451399530/</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B113" s="67" t="n">
+      <c r="A113" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B113" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -2927,19 +2936,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D113" s="68" t="inlineStr">
+      <c r="D113" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B114" s="67" t="n">
+      <c r="A114" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B114" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -2947,19 +2956,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D114" s="68" t="inlineStr">
+      <c r="D114" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="66" t="inlineStr">
+      <c r="A115" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B115" s="67" t="n">
+      <c r="B115" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -2967,19 +2976,19 @@
           <t>Senior Sterilization Engineer</t>
         </is>
       </c>
-      <c r="D115" s="68" t="inlineStr">
+      <c r="D115" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410980549/</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="66" t="inlineStr">
+      <c r="A116" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B116" s="67" t="n">
+      <c r="B116" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -2987,19 +2996,19 @@
           <t>Accounts Payable Process Expert (Maternity Cover)</t>
         </is>
       </c>
-      <c r="D116" s="68" t="inlineStr">
+      <c r="D116" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462464542/</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="66" t="inlineStr">
+      <c r="A117" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B117" s="67" t="n">
+      <c r="B117" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -3007,19 +3016,19 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D117" s="68" t="inlineStr">
+      <c r="D117" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B118" s="67" t="n">
+      <c r="A118" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B118" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -3027,19 +3036,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D118" s="68" t="inlineStr">
+      <c r="D118" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="66" t="inlineStr">
+      <c r="A119" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B119" s="67" t="n">
+      <c r="B119" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3047,19 +3056,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D119" s="68" t="inlineStr">
+      <c r="D119" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B120" s="67" t="n">
+      <c r="A120" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B120" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3067,19 +3076,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D120" s="68" t="inlineStr">
+      <c r="D120" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="66" t="inlineStr">
+      <c r="A121" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B121" s="67" t="n">
+      <c r="B121" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3087,19 +3096,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D121" s="68" t="inlineStr">
+      <c r="D121" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B122" s="67" t="n">
+      <c r="A122" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B122" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3107,19 +3116,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D122" s="68" t="inlineStr">
+      <c r="D122" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="66" t="inlineStr">
+      <c r="A123" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B123" s="67" t="n">
+      <c r="B123" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3127,19 +3136,19 @@
           <t>Staff SRE SW Development Engineer</t>
         </is>
       </c>
-      <c r="D123" s="68" t="inlineStr">
+      <c r="D123" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387683946/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B124" s="67" t="n">
+      <c r="A124" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B124" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3147,19 +3156,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D124" s="68" t="inlineStr">
+      <c r="D124" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B125" s="67" t="n">
+      <c r="A125" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B125" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3167,19 +3176,19 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D125" s="68" t="inlineStr">
+      <c r="D125" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="66" t="inlineStr">
+      <c r="A126" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B126" s="67" t="n">
+      <c r="B126" s="70" t="n">
         <v>46276</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3187,19 +3196,19 @@
           <t>Third Party Risk and Supplier Onboarding Manager</t>
         </is>
       </c>
-      <c r="D126" s="68" t="inlineStr">
+      <c r="D126" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466048486/</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="66" t="inlineStr">
+      <c r="A127" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B127" s="67" t="n">
+      <c r="B127" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3207,19 +3216,19 @@
           <t>Senior Service Designer, Technical Support</t>
         </is>
       </c>
-      <c r="D127" s="68" t="inlineStr">
+      <c r="D127" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455960251/</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B128" s="67" t="n">
+      <c r="A128" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B128" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -3227,19 +3236,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D128" s="68" t="inlineStr">
+      <c r="D128" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464945232/</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="66" t="inlineStr">
+      <c r="A129" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B129" s="67" t="n">
+      <c r="B129" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -3247,19 +3256,19 @@
           <t>Supervisor Manufacturing</t>
         </is>
       </c>
-      <c r="D129" s="68" t="inlineStr">
+      <c r="D129" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4428861138/</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="66" t="inlineStr">
+      <c r="A130" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B130" s="67" t="n">
+      <c r="B130" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -3267,19 +3276,19 @@
           <t>Staff Database Administrator</t>
         </is>
       </c>
-      <c r="D130" s="68" t="inlineStr">
+      <c r="D130" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322200/</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="66" t="inlineStr">
+      <c r="A131" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B131" s="67" t="n">
+      <c r="B131" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -3287,19 +3296,19 @@
           <t>Payroll Analyst (ANZ)</t>
         </is>
       </c>
-      <c r="D131" s="68" t="inlineStr">
+      <c r="D131" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456178209/</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="66" t="inlineStr">
+      <c r="A132" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B132" s="67" t="n">
+      <c r="B132" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -3307,19 +3316,19 @@
           <t>SW Test Development Engineer 1</t>
         </is>
       </c>
-      <c r="D132" s="68" t="inlineStr">
+      <c r="D132" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465029007/</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B133" s="67" t="n">
+      <c r="A133" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B133" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -3327,19 +3336,19 @@
           <t>Sr Workplace Solutions Analyst</t>
         </is>
       </c>
-      <c r="D133" s="68" t="inlineStr">
+      <c r="D133" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322161/</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="66" t="inlineStr">
+      <c r="A134" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B134" s="67" t="n">
+      <c r="B134" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -3347,19 +3356,19 @@
           <t>Staff SW Development Engineer</t>
         </is>
       </c>
-      <c r="D134" s="68" t="inlineStr">
+      <c r="D134" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465323573/</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="66" t="inlineStr">
+      <c r="A135" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B135" s="67" t="n">
+      <c r="B135" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3367,19 +3376,19 @@
           <t>Director, Business Program Management Office</t>
         </is>
       </c>
-      <c r="D135" s="68" t="inlineStr">
+      <c r="D135" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456105988/</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="66" t="inlineStr">
+      <c r="A136" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B136" s="67" t="n">
+      <c r="B136" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3387,19 +3396,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D136" s="68" t="inlineStr">
+      <c r="D136" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456115187/</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B137" s="67" t="n">
+      <c r="A137" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B137" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -3407,19 +3416,19 @@
           <t>Systems Design &amp; Test Engineer 2</t>
         </is>
       </c>
-      <c r="D137" s="68" t="inlineStr">
+      <c r="D137" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443989564/</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B138" s="67" t="n">
+      <c r="A138" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B138" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -3427,19 +3436,19 @@
           <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
         </is>
       </c>
-      <c r="D138" s="68" t="inlineStr">
+      <c r="D138" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439394782/</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="66" t="inlineStr">
+      <c r="A139" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B139" s="67" t="n">
+      <c r="B139" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -3447,19 +3456,19 @@
           <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
-      <c r="D139" s="68" t="inlineStr">
+      <c r="D139" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="66" t="inlineStr">
+      <c r="A140" s="69" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B140" s="67" t="n">
+      <c r="B140" s="70" t="n">
         <v>46278</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -3467,19 +3476,19 @@
           <t>Sr. Financial Analyst</t>
         </is>
       </c>
-      <c r="D140" s="68" t="inlineStr">
+      <c r="D140" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4421230278/</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="66" t="inlineStr">
+      <c r="A141" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B141" s="67" t="n">
+      <c r="B141" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -3487,19 +3496,19 @@
           <t>Sr Cybersecurity Analyst</t>
         </is>
       </c>
-      <c r="D141" s="68" t="inlineStr">
+      <c r="D141" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439085443/</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="66" t="inlineStr">
+      <c r="A142" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B142" s="67" t="n">
+      <c r="B142" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -3507,19 +3516,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D142" s="68" t="inlineStr">
+      <c r="D142" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="66" t="inlineStr">
+      <c r="A143" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B143" s="67" t="n">
+      <c r="B143" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -3527,19 +3536,19 @@
           <t>Trade Compliance Analyst</t>
         </is>
       </c>
-      <c r="D143" s="68" t="inlineStr">
+      <c r="D143" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467033928/</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B144" s="67" t="n">
+      <c r="A144" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B144" s="70" t="n">
         <v>46278</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -3547,19 +3556,19 @@
           <t>Sr Manufacturing Engineer</t>
         </is>
       </c>
-      <c r="D144" s="68" t="inlineStr">
+      <c r="D144" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447583072/</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="66" t="inlineStr">
+      <c r="A145" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B145" s="67" t="n">
+      <c r="B145" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -3567,19 +3576,19 @@
           <t>Staff Vendor Management Analyst</t>
         </is>
       </c>
-      <c r="D145" s="68" t="inlineStr">
+      <c r="D145" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458212554/</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="66" t="inlineStr">
+      <c r="A146" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B146" s="67" t="n">
+      <c r="B146" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -3587,19 +3596,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D146" s="68" t="inlineStr">
+      <c r="D146" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458218533/</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="66" t="inlineStr">
+      <c r="A147" s="69" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B147" s="67" t="n">
+      <c r="B147" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -3607,19 +3616,19 @@
           <t>APAC Product Manager - OTC/Consumer Health</t>
         </is>
       </c>
-      <c r="D147" s="68" t="inlineStr">
+      <c r="D147" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4422693615/</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="66" t="inlineStr">
+      <c r="A148" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B148" s="67" t="n">
+      <c r="B148" s="70" t="n">
         <v>46278</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -3627,19 +3636,19 @@
           <t>Supervisor Technical Support - Manila</t>
         </is>
       </c>
-      <c r="D148" s="68" t="inlineStr">
+      <c r="D148" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417742237/</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="66" t="inlineStr">
+      <c r="A149" s="69" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B149" s="67" t="n">
+      <c r="B149" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -3647,19 +3656,19 @@
           <t>Staff Desktop Support Engineer</t>
         </is>
       </c>
-      <c r="D149" s="68" t="inlineStr">
+      <c r="D149" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4398315987/</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B150" s="67" t="n">
+      <c r="A150" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B150" s="70" t="n">
         <v>46276</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -3667,19 +3676,19 @@
           <t>Director HW Design Quality Engineering - New Product Introductions</t>
         </is>
       </c>
-      <c r="D150" s="68" t="inlineStr">
+      <c r="D150" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456789792/</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="66" t="inlineStr">
+      <c r="A151" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B151" s="67" t="n">
+      <c r="B151" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -3687,19 +3696,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D151" s="68" t="inlineStr">
+      <c r="D151" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B152" s="67" t="n">
+      <c r="A152" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B152" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -3707,19 +3716,19 @@
           <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
         </is>
       </c>
-      <c r="D152" s="68" t="inlineStr">
+      <c r="D152" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="66" t="inlineStr">
+      <c r="A153" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B153" s="67" t="n">
+      <c r="B153" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -3727,19 +3736,19 @@
           <t>Supervisor, Applications Support</t>
         </is>
       </c>
-      <c r="D153" s="68" t="inlineStr">
+      <c r="D153" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456333076/</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B154" s="67" t="n">
+      <c r="A154" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B154" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -3747,19 +3756,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D154" s="68" t="inlineStr">
+      <c r="D154" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="66" t="inlineStr">
+      <c r="A155" s="69" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B155" s="67" t="n">
+      <c r="B155" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -3767,19 +3776,19 @@
           <t>Territory Business Manager - South Island</t>
         </is>
       </c>
-      <c r="D155" s="68" t="inlineStr">
+      <c r="D155" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456111920/</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="66" t="inlineStr">
+      <c r="A156" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B156" s="67" t="n">
+      <c r="B156" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -3787,19 +3796,19 @@
           <t>Sr Staff Program Manager</t>
         </is>
       </c>
-      <c r="D156" s="68" t="inlineStr">
+      <c r="D156" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448138066/</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B157" s="67" t="n">
+      <c r="A157" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B157" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -3807,19 +3816,19 @@
           <t>Senior Manager- Manufacturing IT Strategic Initiatives and Architecture</t>
         </is>
       </c>
-      <c r="D157" s="68" t="inlineStr">
+      <c r="D157" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4421221561/</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="66" t="inlineStr">
+      <c r="A158" s="69" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B158" s="67" t="n">
+      <c r="B158" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -3827,19 +3836,19 @@
           <t>Manager Process Engineering</t>
         </is>
       </c>
-      <c r="D158" s="68" t="inlineStr">
+      <c r="D158" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467096658/</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="66" t="inlineStr">
+      <c r="A159" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B159" s="67" t="n">
+      <c r="B159" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -3847,19 +3856,19 @@
           <t>SW Development Engineer 2 - IOS</t>
         </is>
       </c>
-      <c r="D159" s="68" t="inlineStr">
+      <c r="D159" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465306719/</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="66" t="inlineStr">
+      <c r="A160" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B160" s="67" t="n">
+      <c r="B160" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -3867,19 +3876,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D160" s="68" t="inlineStr">
+      <c r="D160" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B161" s="67" t="n">
+      <c r="A161" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B161" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -3887,19 +3896,19 @@
           <t>District Business Manager - Ohio</t>
         </is>
       </c>
-      <c r="D161" s="68" t="inlineStr">
+      <c r="D161" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458551771/</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="66" t="inlineStr">
+      <c r="A162" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B162" s="67" t="n">
+      <c r="B162" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -3907,19 +3916,19 @@
           <t>Systems Engineer</t>
         </is>
       </c>
-      <c r="D162" s="68" t="inlineStr">
+      <c r="D162" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4375183129/</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="66" t="inlineStr">
+      <c r="A163" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B163" s="67" t="n">
+      <c r="B163" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -3927,19 +3936,19 @@
           <t>Lead Firmware V&amp;V</t>
         </is>
       </c>
-      <c r="D163" s="68" t="inlineStr">
+      <c r="D163" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4402920307/</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="66" t="inlineStr">
+      <c r="A164" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B164" s="67" t="n">
+      <c r="B164" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -3947,19 +3956,19 @@
           <t>Sr. Systems Engineer</t>
         </is>
       </c>
-      <c r="D164" s="68" t="inlineStr">
+      <c r="D164" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461756319/</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B165" s="67" t="n">
+      <c r="A165" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B165" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -3967,19 +3976,19 @@
           <t>Senior Lead Government Affairs Manager - Federal</t>
         </is>
       </c>
-      <c r="D165" s="68" t="inlineStr">
+      <c r="D165" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440825647/</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="66" t="inlineStr">
+      <c r="A166" s="69" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B166" s="67" t="n">
+      <c r="B166" s="70" t="n">
         <v>46274</v>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -3987,19 +3996,19 @@
           <t>Staff Database Administrator</t>
         </is>
       </c>
-      <c r="D166" s="68" t="inlineStr">
+      <c r="D166" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456333107/</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B167" s="67" t="n">
+      <c r="A167" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B167" s="70" t="n">
         <v>46277</v>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -4007,19 +4016,19 @@
           <t>Equipment Technician 2 (2A Sunday - Tuesday, every other Saturday from 5:00PM - 5:00AM )</t>
         </is>
       </c>
-      <c r="D167" s="68" t="inlineStr">
+      <c r="D167" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466467687/</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B168" s="67" t="n">
+      <c r="A168" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B168" s="70" t="n">
         <v>46277</v>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -4027,19 +4036,19 @@
           <t>Equipment Technician 2 (2B Wednesday - Friday, every other Saturday from 5:00PM - 5:00AM)</t>
         </is>
       </c>
-      <c r="D168" s="68" t="inlineStr">
+      <c r="D168" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466428944/</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B169" s="67" t="n">
+      <c r="A169" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B169" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -4047,19 +4056,19 @@
           <t>New Business Development Manager, Trade Partnerships (eCommerce)</t>
         </is>
       </c>
-      <c r="D169" s="68" t="inlineStr">
+      <c r="D169" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459020959/</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="66" t="inlineStr">
+      <c r="A170" s="69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B170" s="67" t="n">
+      <c r="B170" s="70" t="n">
         <v>46279</v>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -4067,19 +4076,19 @@
           <t>Sr Firmware V&amp;V</t>
         </is>
       </c>
-      <c r="D170" s="68" t="inlineStr">
+      <c r="D170" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4402292560/</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B171" s="67" t="n">
+      <c r="A171" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B171" s="70" t="n">
         <v>46277</v>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -4087,19 +4096,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D171" s="68" t="inlineStr">
+      <c r="D171" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457557361/</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B172" s="67" t="n">
+      <c r="A172" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B172" s="70" t="n">
         <v>46278</v>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -4107,19 +4116,19 @@
           <t>Staff Enterprise Applications Developer - IBM Maximo</t>
         </is>
       </c>
-      <c r="D172" s="68" t="inlineStr">
+      <c r="D172" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411935028/</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B173" s="67" t="n">
+      <c r="A173" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B173" s="70" t="n">
         <v>46280</v>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -4127,19 +4136,19 @@
           <t>Equipment Technician 4 ( Dobson ) 2B Night Shift: Wed-Fri, every other Sat.</t>
         </is>
       </c>
-      <c r="D173" s="68" t="inlineStr">
+      <c r="D173" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467703315/</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B174" s="67" t="n">
+      <c r="A174" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B174" s="70" t="n">
         <v>46277</v>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -4147,19 +4156,19 @@
           <t>HCP Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D174" s="68" t="inlineStr">
+      <c r="D174" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442796306/</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B175" s="67" t="n">
+      <c r="A175" s="69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B175" s="70" t="n">
         <v>46275</v>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -4167,7 +4176,7 @@
           <t>Sr. Federal Clinical Educator - East</t>
         </is>
       </c>
-      <c r="D175" s="68" t="inlineStr">
+      <c r="D175" s="71" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455357586/</t>
         </is>
@@ -4813,8 +4822,48 @@
         </is>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B208" s="73" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>Sr Process Engineer</t>
+        </is>
+      </c>
+      <c r="D208" s="74" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457557359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B209" s="73" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
+        </is>
+      </c>
+      <c r="D209" s="74" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D207"/>
+  <autoFilter ref="A1:D209"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -5022,6 +5071,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId208"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$214</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -671,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -703,12 +712,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="70" t="n">
+      <c r="B2" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -716,19 +725,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="71" t="inlineStr">
+      <c r="D2" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="69" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="70" t="n">
+      <c r="B3" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -736,19 +745,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="71" t="inlineStr">
+      <c r="D3" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="69" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="70" t="n">
+      <c r="B4" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -756,19 +765,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="71" t="inlineStr">
+      <c r="D4" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="69" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="70" t="n">
+      <c r="B5" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -776,19 +785,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="71" t="inlineStr">
+      <c r="D5" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="69" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="70" t="n">
+      <c r="B6" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -796,19 +805,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="71" t="inlineStr">
+      <c r="D6" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="69" t="inlineStr">
+      <c r="A7" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="70" t="n">
+      <c r="B7" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -816,19 +825,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="71" t="inlineStr">
+      <c r="D7" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="69" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="70" t="n">
+      <c r="B8" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -836,19 +845,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="71" t="inlineStr">
+      <c r="D8" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="69" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="70" t="n">
+      <c r="B9" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -856,19 +865,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="71" t="inlineStr">
+      <c r="D9" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="69" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="70" t="n">
+      <c r="B10" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -876,19 +885,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="71" t="inlineStr">
+      <c r="D10" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="69" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="70" t="n">
+      <c r="B11" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -896,19 +905,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="71" t="inlineStr">
+      <c r="D11" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="69" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="70" t="n">
+      <c r="B12" s="73" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -916,19 +925,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="71" t="inlineStr">
+      <c r="D12" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="69" t="inlineStr">
+      <c r="A13" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="70" t="n">
+      <c r="B13" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -936,19 +945,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="71" t="inlineStr">
+      <c r="D13" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="69" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="70" t="n">
+      <c r="B14" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -956,19 +965,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="71" t="inlineStr">
+      <c r="D14" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="70" t="n">
+      <c r="A15" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -976,19 +985,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="71" t="inlineStr">
+      <c r="D15" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="69" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="70" t="n">
+      <c r="B16" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -996,19 +1005,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="71" t="inlineStr">
+      <c r="D16" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="69" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="70" t="n">
+      <c r="B17" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1016,19 +1025,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="71" t="inlineStr">
+      <c r="D17" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="69" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="70" t="n">
+      <c r="B18" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1036,19 +1045,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="71" t="inlineStr">
+      <c r="D18" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="69" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="70" t="n">
+      <c r="B19" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1056,19 +1065,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="71" t="inlineStr">
+      <c r="D19" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="69" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="70" t="n">
+      <c r="B20" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1076,19 +1085,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="71" t="inlineStr">
+      <c r="D20" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B21" s="70" t="n">
+      <c r="A21" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1096,19 +1105,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="71" t="inlineStr">
+      <c r="D21" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="69" t="inlineStr">
+      <c r="A22" s="72" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="70" t="n">
+      <c r="B22" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1116,19 +1125,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="71" t="inlineStr">
+      <c r="D22" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B23" s="70" t="n">
+      <c r="A23" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B23" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1136,19 +1145,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="71" t="inlineStr">
+      <c r="D23" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="69" t="inlineStr">
+      <c r="A24" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="70" t="n">
+      <c r="B24" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1156,19 +1165,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="71" t="inlineStr">
+      <c r="D24" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="69" t="inlineStr">
+      <c r="A25" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="70" t="n">
+      <c r="B25" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1176,19 +1185,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="71" t="inlineStr">
+      <c r="D25" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="69" t="inlineStr">
+      <c r="A26" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="70" t="n">
+      <c r="B26" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1196,19 +1205,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="71" t="inlineStr">
+      <c r="D26" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="69" t="inlineStr">
+      <c r="A27" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="70" t="n">
+      <c r="B27" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1216,19 +1225,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="71" t="inlineStr">
+      <c r="D27" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="69" t="inlineStr">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="70" t="n">
+      <c r="B28" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1236,19 +1245,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="71" t="inlineStr">
+      <c r="D28" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="69" t="inlineStr">
+      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="70" t="n">
+      <c r="B29" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1256,19 +1265,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="71" t="inlineStr">
+      <c r="D29" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="69" t="inlineStr">
+      <c r="A30" s="72" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="70" t="n">
+      <c r="B30" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1276,19 +1285,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="71" t="inlineStr">
+      <c r="D30" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="69" t="inlineStr">
+      <c r="A31" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="70" t="n">
+      <c r="B31" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1296,19 +1305,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="71" t="inlineStr">
+      <c r="D31" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="70" t="n">
+      <c r="A32" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1316,19 +1325,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="71" t="inlineStr">
+      <c r="D32" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="70" t="n">
+      <c r="A33" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1336,19 +1345,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="71" t="inlineStr">
+      <c r="D33" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="69" t="inlineStr">
+      <c r="A34" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="70" t="n">
+      <c r="B34" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1356,19 +1365,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="71" t="inlineStr">
+      <c r="D34" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="69" t="inlineStr">
+      <c r="A35" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="70" t="n">
+      <c r="B35" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1376,19 +1385,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="71" t="inlineStr">
+      <c r="D35" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="69" t="inlineStr">
+      <c r="A36" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="70" t="n">
+      <c r="B36" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1396,19 +1405,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="71" t="inlineStr">
+      <c r="D36" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="69" t="inlineStr">
+      <c r="A37" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="70" t="n">
+      <c r="B37" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1416,19 +1425,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="71" t="inlineStr">
+      <c r="D37" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="69" t="inlineStr">
+      <c r="A38" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="70" t="n">
+      <c r="B38" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1436,19 +1445,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="71" t="inlineStr">
+      <c r="D38" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="69" t="inlineStr">
+      <c r="A39" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="70" t="n">
+      <c r="B39" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1456,19 +1465,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="71" t="inlineStr">
+      <c r="D39" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="69" t="inlineStr">
+      <c r="A40" s="72" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="70" t="n">
+      <c r="B40" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1476,19 +1485,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="71" t="inlineStr">
+      <c r="D40" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="69" t="inlineStr">
+      <c r="A41" s="72" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="70" t="n">
+      <c r="B41" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1496,19 +1505,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="71" t="inlineStr">
+      <c r="D41" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B42" s="70" t="n">
+      <c r="A42" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B42" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1516,19 +1525,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="71" t="inlineStr">
+      <c r="D42" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="70" t="n">
+      <c r="A43" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1536,19 +1545,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="71" t="inlineStr">
+      <c r="D43" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="69" t="inlineStr">
+      <c r="A44" s="72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="70" t="n">
+      <c r="B44" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1556,19 +1565,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="71" t="inlineStr">
+      <c r="D44" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="69" t="inlineStr">
+      <c r="A45" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="70" t="n">
+      <c r="B45" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1576,19 +1585,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="71" t="inlineStr">
+      <c r="D45" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="70" t="n">
+      <c r="A46" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1596,19 +1605,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="71" t="inlineStr">
+      <c r="D46" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="69" t="inlineStr">
+      <c r="A47" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="70" t="n">
+      <c r="B47" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1616,19 +1625,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="71" t="inlineStr">
+      <c r="D47" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="69" t="inlineStr">
+      <c r="A48" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="70" t="n">
+      <c r="B48" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1636,19 +1645,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="71" t="inlineStr">
+      <c r="D48" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="69" t="inlineStr">
+      <c r="A49" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="70" t="n">
+      <c r="B49" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1656,19 +1665,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="71" t="inlineStr">
+      <c r="D49" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="69" t="inlineStr">
+      <c r="A50" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="70" t="n">
+      <c r="B50" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1676,19 +1685,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="71" t="inlineStr">
+      <c r="D50" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="69" t="inlineStr">
+      <c r="A51" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="70" t="n">
+      <c r="B51" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1696,19 +1705,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="71" t="inlineStr">
+      <c r="D51" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="69" t="inlineStr">
+      <c r="A52" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="70" t="n">
+      <c r="B52" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1716,19 +1725,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="71" t="inlineStr">
+      <c r="D52" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="69" t="inlineStr">
+      <c r="A53" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="70" t="n">
+      <c r="B53" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1736,19 +1745,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="71" t="inlineStr">
+      <c r="D53" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="69" t="inlineStr">
+      <c r="A54" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="70" t="n">
+      <c r="B54" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1756,19 +1765,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="71" t="inlineStr">
+      <c r="D54" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="69" t="inlineStr">
+      <c r="A55" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="70" t="n">
+      <c r="B55" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1776,19 +1785,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="71" t="inlineStr">
+      <c r="D55" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="69" t="inlineStr">
+      <c r="A56" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="70" t="n">
+      <c r="B56" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1796,19 +1805,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="71" t="inlineStr">
+      <c r="D56" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="69" t="inlineStr">
+      <c r="A57" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="70" t="n">
+      <c r="B57" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1816,19 +1825,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="71" t="inlineStr">
+      <c r="D57" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="69" t="inlineStr">
+      <c r="A58" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="70" t="n">
+      <c r="B58" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1836,19 +1845,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="71" t="inlineStr">
+      <c r="D58" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="70" t="n">
+      <c r="A59" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1856,19 +1865,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="71" t="inlineStr">
+      <c r="D59" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="69" t="inlineStr">
+      <c r="A60" s="72" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="70" t="n">
+      <c r="B60" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1876,19 +1885,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="71" t="inlineStr">
+      <c r="D60" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B61" s="70" t="n">
+      <c r="A61" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B61" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1896,19 +1905,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="71" t="inlineStr">
+      <c r="D61" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="69" t="inlineStr">
+      <c r="A62" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="70" t="n">
+      <c r="B62" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1916,19 +1925,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="71" t="inlineStr">
+      <c r="D62" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="70" t="n">
+      <c r="A63" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1936,19 +1945,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="71" t="inlineStr">
+      <c r="D63" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="69" t="inlineStr">
+      <c r="A64" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="70" t="n">
+      <c r="B64" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1956,19 +1965,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="71" t="inlineStr">
+      <c r="D64" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B65" s="70" t="n">
+      <c r="A65" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B65" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1976,19 +1985,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="71" t="inlineStr">
+      <c r="D65" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="69" t="inlineStr">
+      <c r="A66" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="70" t="n">
+      <c r="B66" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1996,19 +2005,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="71" t="inlineStr">
+      <c r="D66" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B67" s="70" t="n">
+      <c r="A67" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B67" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2016,19 +2025,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="71" t="inlineStr">
+      <c r="D67" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="69" t="inlineStr">
+      <c r="A68" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="70" t="n">
+      <c r="B68" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -2036,19 +2045,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="71" t="inlineStr">
+      <c r="D68" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="69" t="inlineStr">
+      <c r="A69" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="70" t="n">
+      <c r="B69" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2056,19 +2065,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="71" t="inlineStr">
+      <c r="D69" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="69" t="inlineStr">
+      <c r="A70" s="72" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="70" t="n">
+      <c r="B70" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2076,19 +2085,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="71" t="inlineStr">
+      <c r="D70" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="69" t="inlineStr">
+      <c r="A71" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="70" t="n">
+      <c r="B71" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2096,19 +2105,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="71" t="inlineStr">
+      <c r="D71" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="69" t="inlineStr">
+      <c r="A72" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="70" t="n">
+      <c r="B72" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2116,19 +2125,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="71" t="inlineStr">
+      <c r="D72" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="69" t="inlineStr">
+      <c r="A73" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="70" t="n">
+      <c r="B73" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2136,19 +2145,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="71" t="inlineStr">
+      <c r="D73" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="69" t="inlineStr">
+      <c r="A74" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="70" t="n">
+      <c r="B74" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2156,19 +2165,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="71" t="inlineStr">
+      <c r="D74" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="69" t="inlineStr">
+      <c r="A75" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="70" t="n">
+      <c r="B75" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2176,19 +2185,19 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="71" t="inlineStr">
+      <c r="D75" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="69" t="inlineStr">
+      <c r="A76" s="72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B76" s="70" t="n">
+      <c r="B76" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2196,19 +2205,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D76" s="71" t="inlineStr">
+      <c r="D76" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="69" t="inlineStr">
+      <c r="A77" s="72" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B77" s="70" t="n">
+      <c r="B77" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2216,19 +2225,19 @@
           <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
         </is>
       </c>
-      <c r="D77" s="71" t="inlineStr">
+      <c r="D77" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765129/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="69" t="inlineStr">
+      <c r="A78" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="70" t="n">
+      <c r="B78" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2236,19 +2245,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D78" s="71" t="inlineStr">
+      <c r="D78" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="69" t="inlineStr">
+      <c r="A79" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B79" s="70" t="n">
+      <c r="B79" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2256,19 +2265,19 @@
           <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
-      <c r="D79" s="71" t="inlineStr">
+      <c r="D79" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="69" t="inlineStr">
+      <c r="A80" s="72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B80" s="70" t="n">
+      <c r="B80" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2276,19 +2285,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D80" s="71" t="inlineStr">
+      <c r="D80" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="69" t="inlineStr">
+      <c r="A81" s="72" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B81" s="70" t="n">
+      <c r="B81" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2296,19 +2305,19 @@
           <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
         </is>
       </c>
-      <c r="D81" s="71" t="inlineStr">
+      <c r="D81" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450696746/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="69" t="inlineStr">
+      <c r="A82" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="70" t="n">
+      <c r="B82" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2316,19 +2325,19 @@
           <t>Logistics Analyst</t>
         </is>
       </c>
-      <c r="D82" s="71" t="inlineStr">
+      <c r="D82" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461266744/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="69" t="inlineStr">
+      <c r="A83" s="72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B83" s="70" t="n">
+      <c r="B83" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2336,19 +2345,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D83" s="71" t="inlineStr">
+      <c r="D83" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="69" t="inlineStr">
+      <c r="A84" s="72" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B84" s="70" t="n">
+      <c r="B84" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2356,19 +2365,19 @@
           <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D84" s="71" t="inlineStr">
+      <c r="D84" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459309508/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="69" t="inlineStr">
+      <c r="A85" s="72" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" s="70" t="n">
+      <c r="B85" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2376,19 +2385,19 @@
           <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
         </is>
       </c>
-      <c r="D85" s="71" t="inlineStr">
+      <c r="D85" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770007/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="69" t="inlineStr">
+      <c r="A86" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="70" t="n">
+      <c r="B86" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2396,19 +2405,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D86" s="71" t="inlineStr">
+      <c r="D86" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="69" t="inlineStr">
+      <c r="A87" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B87" s="70" t="n">
+      <c r="B87" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2416,19 +2425,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D87" s="71" t="inlineStr">
+      <c r="D87" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="69" t="inlineStr">
+      <c r="A88" s="72" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B88" s="70" t="n">
+      <c r="B88" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2436,19 +2445,19 @@
           <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
-      <c r="D88" s="71" t="inlineStr">
+      <c r="D88" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="69" t="inlineStr">
+      <c r="A89" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="70" t="n">
+      <c r="B89" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2456,19 +2465,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D89" s="71" t="inlineStr">
+      <c r="D89" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="69" t="inlineStr">
+      <c r="A90" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B90" s="70" t="n">
+      <c r="B90" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2476,19 +2485,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D90" s="71" t="inlineStr">
+      <c r="D90" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="69" t="inlineStr">
+      <c r="A91" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B91" s="70" t="n">
+      <c r="B91" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2496,19 +2505,19 @@
           <t>Contract Administration Representative (French-speaking)</t>
         </is>
       </c>
-      <c r="D91" s="71" t="inlineStr">
+      <c r="D91" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461090763/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="69" t="inlineStr">
+      <c r="A92" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B92" s="70" t="n">
+      <c r="B92" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2516,19 +2525,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D92" s="71" t="inlineStr">
+      <c r="D92" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="69" t="inlineStr">
+      <c r="A93" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B93" s="70" t="n">
+      <c r="B93" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2536,19 +2545,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D93" s="71" t="inlineStr">
+      <c r="D93" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="69" t="inlineStr">
+      <c r="A94" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B94" s="70" t="n">
+      <c r="B94" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2556,19 +2565,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D94" s="71" t="inlineStr">
+      <c r="D94" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453089165/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="69" t="inlineStr">
+      <c r="A95" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B95" s="70" t="n">
+      <c r="B95" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2576,19 +2585,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D95" s="71" t="inlineStr">
+      <c r="D95" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="69" t="inlineStr">
+      <c r="A96" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B96" s="70" t="n">
+      <c r="B96" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2596,19 +2605,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D96" s="71" t="inlineStr">
+      <c r="D96" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="69" t="inlineStr">
+      <c r="A97" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B97" s="70" t="n">
+      <c r="B97" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2616,19 +2625,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D97" s="71" t="inlineStr">
+      <c r="D97" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="69" t="inlineStr">
+      <c r="A98" s="72" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B98" s="70" t="n">
+      <c r="B98" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2636,19 +2645,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D98" s="71" t="inlineStr">
+      <c r="D98" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="69" t="inlineStr">
+      <c r="A99" s="72" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B99" s="70" t="n">
+      <c r="B99" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2656,19 +2665,19 @@
           <t>Technical Support Representative 2</t>
         </is>
       </c>
-      <c r="D99" s="71" t="inlineStr">
+      <c r="D99" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438880089/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="69" t="inlineStr">
+      <c r="A100" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B100" s="70" t="n">
+      <c r="B100" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2676,19 +2685,19 @@
           <t>Spanish Bilingual Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D100" s="71" t="inlineStr">
+      <c r="D100" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458704406/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="69" t="inlineStr">
+      <c r="A101" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B101" s="70" t="n">
+      <c r="B101" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2696,19 +2705,19 @@
           <t>Spanish Bilingual TSR</t>
         </is>
       </c>
-      <c r="D101" s="71" t="inlineStr">
+      <c r="D101" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407814543/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B102" s="70" t="n">
+      <c r="A102" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B102" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2716,19 +2725,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D102" s="71" t="inlineStr">
+      <c r="D102" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="69" t="inlineStr">
+      <c r="A103" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B103" s="70" t="n">
+      <c r="B103" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2736,19 +2745,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D103" s="71" t="inlineStr">
+      <c r="D103" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B104" s="70" t="n">
+      <c r="A104" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B104" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2756,19 +2765,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D104" s="71" t="inlineStr">
+      <c r="D104" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B105" s="70" t="n">
+      <c r="A105" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B105" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2776,19 +2785,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D105" s="71" t="inlineStr">
+      <c r="D105" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B106" s="70" t="n">
+      <c r="A106" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B106" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2796,19 +2805,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D106" s="71" t="inlineStr">
+      <c r="D106" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439353245/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="69" t="inlineStr">
+      <c r="A107" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B107" s="70" t="n">
+      <c r="B107" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2816,19 +2825,19 @@
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="D107" s="71" t="inlineStr">
+      <c r="D107" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="69" t="inlineStr">
+      <c r="A108" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B108" s="70" t="n">
+      <c r="B108" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2836,19 +2845,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D108" s="71" t="inlineStr">
+      <c r="D108" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082223/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="69" t="inlineStr">
+      <c r="A109" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B109" s="70" t="n">
+      <c r="B109" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2856,19 +2865,19 @@
           <t>Business Process Analyst</t>
         </is>
       </c>
-      <c r="D109" s="71" t="inlineStr">
+      <c r="D109" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414569192/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B110" s="70" t="n">
+      <c r="A110" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2876,19 +2885,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D110" s="71" t="inlineStr">
+      <c r="D110" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456380639/</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B111" s="70" t="n">
+      <c r="A111" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B111" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2896,19 +2905,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D111" s="71" t="inlineStr">
+      <c r="D111" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456364824/</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="69" t="inlineStr">
+      <c r="A112" s="72" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B112" s="70" t="n">
+      <c r="B112" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -2916,19 +2925,19 @@
           <t>Associate Marketing Manager</t>
         </is>
       </c>
-      <c r="D112" s="71" t="inlineStr">
+      <c r="D112" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451399530/</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B113" s="70" t="n">
+      <c r="A113" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B113" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -2936,19 +2945,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D113" s="71" t="inlineStr">
+      <c r="D113" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B114" s="70" t="n">
+      <c r="A114" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B114" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -2956,19 +2965,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D114" s="71" t="inlineStr">
+      <c r="D114" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="69" t="inlineStr">
+      <c r="A115" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B115" s="70" t="n">
+      <c r="B115" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -2976,19 +2985,19 @@
           <t>Senior Sterilization Engineer</t>
         </is>
       </c>
-      <c r="D115" s="71" t="inlineStr">
+      <c r="D115" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410980549/</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="69" t="inlineStr">
+      <c r="A116" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B116" s="70" t="n">
+      <c r="B116" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -2996,19 +3005,19 @@
           <t>Accounts Payable Process Expert (Maternity Cover)</t>
         </is>
       </c>
-      <c r="D116" s="71" t="inlineStr">
+      <c r="D116" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462464542/</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="69" t="inlineStr">
+      <c r="A117" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B117" s="70" t="n">
+      <c r="B117" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -3016,19 +3025,19 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D117" s="71" t="inlineStr">
+      <c r="D117" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B118" s="70" t="n">
+      <c r="A118" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B118" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -3036,19 +3045,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D118" s="71" t="inlineStr">
+      <c r="D118" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="69" t="inlineStr">
+      <c r="A119" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B119" s="70" t="n">
+      <c r="B119" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3056,19 +3065,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D119" s="71" t="inlineStr">
+      <c r="D119" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B120" s="70" t="n">
+      <c r="A120" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B120" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3076,19 +3085,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D120" s="71" t="inlineStr">
+      <c r="D120" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="69" t="inlineStr">
+      <c r="A121" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B121" s="70" t="n">
+      <c r="B121" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3096,19 +3105,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D121" s="71" t="inlineStr">
+      <c r="D121" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B122" s="70" t="n">
+      <c r="A122" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B122" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3116,19 +3125,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D122" s="71" t="inlineStr">
+      <c r="D122" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="69" t="inlineStr">
+      <c r="A123" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B123" s="70" t="n">
+      <c r="B123" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3136,19 +3145,19 @@
           <t>Staff SRE SW Development Engineer</t>
         </is>
       </c>
-      <c r="D123" s="71" t="inlineStr">
+      <c r="D123" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387683946/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B124" s="70" t="n">
+      <c r="A124" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B124" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3156,19 +3165,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D124" s="71" t="inlineStr">
+      <c r="D124" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B125" s="70" t="n">
+      <c r="A125" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B125" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3176,19 +3185,19 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D125" s="71" t="inlineStr">
+      <c r="D125" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="69" t="inlineStr">
+      <c r="A126" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B126" s="70" t="n">
+      <c r="B126" s="73" t="n">
         <v>46276</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3196,19 +3205,19 @@
           <t>Third Party Risk and Supplier Onboarding Manager</t>
         </is>
       </c>
-      <c r="D126" s="71" t="inlineStr">
+      <c r="D126" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466048486/</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="69" t="inlineStr">
+      <c r="A127" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B127" s="70" t="n">
+      <c r="B127" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3216,19 +3225,19 @@
           <t>Senior Service Designer, Technical Support</t>
         </is>
       </c>
-      <c r="D127" s="71" t="inlineStr">
+      <c r="D127" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455960251/</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B128" s="70" t="n">
+      <c r="A128" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B128" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -3236,19 +3245,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D128" s="71" t="inlineStr">
+      <c r="D128" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464945232/</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="69" t="inlineStr">
+      <c r="A129" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B129" s="70" t="n">
+      <c r="B129" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -3256,19 +3265,19 @@
           <t>Supervisor Manufacturing</t>
         </is>
       </c>
-      <c r="D129" s="71" t="inlineStr">
+      <c r="D129" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4428861138/</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="69" t="inlineStr">
+      <c r="A130" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B130" s="70" t="n">
+      <c r="B130" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -3276,19 +3285,19 @@
           <t>Staff Database Administrator</t>
         </is>
       </c>
-      <c r="D130" s="71" t="inlineStr">
+      <c r="D130" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322200/</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="69" t="inlineStr">
+      <c r="A131" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B131" s="70" t="n">
+      <c r="B131" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -3296,19 +3305,19 @@
           <t>Payroll Analyst (ANZ)</t>
         </is>
       </c>
-      <c r="D131" s="71" t="inlineStr">
+      <c r="D131" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456178209/</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="69" t="inlineStr">
+      <c r="A132" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B132" s="70" t="n">
+      <c r="B132" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -3316,19 +3325,19 @@
           <t>SW Test Development Engineer 1</t>
         </is>
       </c>
-      <c r="D132" s="71" t="inlineStr">
+      <c r="D132" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465029007/</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B133" s="70" t="n">
+      <c r="A133" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B133" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -3336,19 +3345,19 @@
           <t>Sr Workplace Solutions Analyst</t>
         </is>
       </c>
-      <c r="D133" s="71" t="inlineStr">
+      <c r="D133" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322161/</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="69" t="inlineStr">
+      <c r="A134" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B134" s="70" t="n">
+      <c r="B134" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -3356,19 +3365,19 @@
           <t>Staff SW Development Engineer</t>
         </is>
       </c>
-      <c r="D134" s="71" t="inlineStr">
+      <c r="D134" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465323573/</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="69" t="inlineStr">
+      <c r="A135" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B135" s="70" t="n">
+      <c r="B135" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3376,19 +3385,19 @@
           <t>Director, Business Program Management Office</t>
         </is>
       </c>
-      <c r="D135" s="71" t="inlineStr">
+      <c r="D135" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456105988/</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="69" t="inlineStr">
+      <c r="A136" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B136" s="70" t="n">
+      <c r="B136" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3396,19 +3405,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D136" s="71" t="inlineStr">
+      <c r="D136" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456115187/</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B137" s="70" t="n">
+      <c r="A137" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B137" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -3416,19 +3425,19 @@
           <t>Systems Design &amp; Test Engineer 2</t>
         </is>
       </c>
-      <c r="D137" s="71" t="inlineStr">
+      <c r="D137" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443989564/</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B138" s="70" t="n">
+      <c r="A138" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B138" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -3436,19 +3445,19 @@
           <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
         </is>
       </c>
-      <c r="D138" s="71" t="inlineStr">
+      <c r="D138" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439394782/</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="69" t="inlineStr">
+      <c r="A139" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B139" s="70" t="n">
+      <c r="B139" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -3456,19 +3465,19 @@
           <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
-      <c r="D139" s="71" t="inlineStr">
+      <c r="D139" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="69" t="inlineStr">
+      <c r="A140" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B140" s="70" t="n">
+      <c r="B140" s="73" t="n">
         <v>46278</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -3476,19 +3485,19 @@
           <t>Sr. Financial Analyst</t>
         </is>
       </c>
-      <c r="D140" s="71" t="inlineStr">
+      <c r="D140" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4421230278/</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="69" t="inlineStr">
+      <c r="A141" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B141" s="70" t="n">
+      <c r="B141" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -3496,19 +3505,19 @@
           <t>Sr Cybersecurity Analyst</t>
         </is>
       </c>
-      <c r="D141" s="71" t="inlineStr">
+      <c r="D141" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439085443/</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="69" t="inlineStr">
+      <c r="A142" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B142" s="70" t="n">
+      <c r="B142" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -3516,19 +3525,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D142" s="71" t="inlineStr">
+      <c r="D142" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="69" t="inlineStr">
+      <c r="A143" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B143" s="70" t="n">
+      <c r="B143" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -3536,19 +3545,19 @@
           <t>Trade Compliance Analyst</t>
         </is>
       </c>
-      <c r="D143" s="71" t="inlineStr">
+      <c r="D143" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467033928/</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B144" s="70" t="n">
+      <c r="A144" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B144" s="73" t="n">
         <v>46278</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -3556,19 +3565,19 @@
           <t>Sr Manufacturing Engineer</t>
         </is>
       </c>
-      <c r="D144" s="71" t="inlineStr">
+      <c r="D144" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447583072/</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="69" t="inlineStr">
+      <c r="A145" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B145" s="70" t="n">
+      <c r="B145" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -3576,19 +3585,19 @@
           <t>Staff Vendor Management Analyst</t>
         </is>
       </c>
-      <c r="D145" s="71" t="inlineStr">
+      <c r="D145" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458212554/</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="69" t="inlineStr">
+      <c r="A146" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B146" s="70" t="n">
+      <c r="B146" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -3596,19 +3605,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D146" s="71" t="inlineStr">
+      <c r="D146" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458218533/</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="69" t="inlineStr">
+      <c r="A147" s="72" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B147" s="70" t="n">
+      <c r="B147" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -3616,19 +3625,19 @@
           <t>APAC Product Manager - OTC/Consumer Health</t>
         </is>
       </c>
-      <c r="D147" s="71" t="inlineStr">
+      <c r="D147" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4422693615/</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="69" t="inlineStr">
+      <c r="A148" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B148" s="70" t="n">
+      <c r="B148" s="73" t="n">
         <v>46278</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -3636,19 +3645,19 @@
           <t>Supervisor Technical Support - Manila</t>
         </is>
       </c>
-      <c r="D148" s="71" t="inlineStr">
+      <c r="D148" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417742237/</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="69" t="inlineStr">
+      <c r="A149" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B149" s="70" t="n">
+      <c r="B149" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -3656,19 +3665,19 @@
           <t>Staff Desktop Support Engineer</t>
         </is>
       </c>
-      <c r="D149" s="71" t="inlineStr">
+      <c r="D149" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4398315987/</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B150" s="70" t="n">
+      <c r="A150" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B150" s="73" t="n">
         <v>46276</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -3676,19 +3685,19 @@
           <t>Director HW Design Quality Engineering - New Product Introductions</t>
         </is>
       </c>
-      <c r="D150" s="71" t="inlineStr">
+      <c r="D150" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456789792/</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="69" t="inlineStr">
+      <c r="A151" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B151" s="70" t="n">
+      <c r="B151" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -3696,19 +3705,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D151" s="71" t="inlineStr">
+      <c r="D151" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B152" s="70" t="n">
+      <c r="A152" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B152" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -3716,19 +3725,19 @@
           <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
         </is>
       </c>
-      <c r="D152" s="71" t="inlineStr">
+      <c r="D152" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="69" t="inlineStr">
+      <c r="A153" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B153" s="70" t="n">
+      <c r="B153" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -3736,19 +3745,19 @@
           <t>Supervisor, Applications Support</t>
         </is>
       </c>
-      <c r="D153" s="71" t="inlineStr">
+      <c r="D153" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456333076/</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B154" s="70" t="n">
+      <c r="A154" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B154" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -3756,19 +3765,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D154" s="71" t="inlineStr">
+      <c r="D154" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="69" t="inlineStr">
+      <c r="A155" s="72" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B155" s="70" t="n">
+      <c r="B155" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -3776,19 +3785,19 @@
           <t>Territory Business Manager - South Island</t>
         </is>
       </c>
-      <c r="D155" s="71" t="inlineStr">
+      <c r="D155" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456111920/</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="69" t="inlineStr">
+      <c r="A156" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B156" s="70" t="n">
+      <c r="B156" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -3796,19 +3805,19 @@
           <t>Sr Staff Program Manager</t>
         </is>
       </c>
-      <c r="D156" s="71" t="inlineStr">
+      <c r="D156" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448138066/</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B157" s="70" t="n">
+      <c r="A157" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B157" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -3816,19 +3825,19 @@
           <t>Senior Manager- Manufacturing IT Strategic Initiatives and Architecture</t>
         </is>
       </c>
-      <c r="D157" s="71" t="inlineStr">
+      <c r="D157" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4421221561/</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="69" t="inlineStr">
+      <c r="A158" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B158" s="70" t="n">
+      <c r="B158" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -3836,19 +3845,19 @@
           <t>Manager Process Engineering</t>
         </is>
       </c>
-      <c r="D158" s="71" t="inlineStr">
+      <c r="D158" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467096658/</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="69" t="inlineStr">
+      <c r="A159" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B159" s="70" t="n">
+      <c r="B159" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -3856,19 +3865,19 @@
           <t>SW Development Engineer 2 - IOS</t>
         </is>
       </c>
-      <c r="D159" s="71" t="inlineStr">
+      <c r="D159" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465306719/</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="69" t="inlineStr">
+      <c r="A160" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B160" s="70" t="n">
+      <c r="B160" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -3876,19 +3885,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D160" s="71" t="inlineStr">
+      <c r="D160" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B161" s="70" t="n">
+      <c r="A161" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B161" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -3896,19 +3905,19 @@
           <t>District Business Manager - Ohio</t>
         </is>
       </c>
-      <c r="D161" s="71" t="inlineStr">
+      <c r="D161" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458551771/</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="69" t="inlineStr">
+      <c r="A162" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B162" s="70" t="n">
+      <c r="B162" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -3916,19 +3925,19 @@
           <t>Systems Engineer</t>
         </is>
       </c>
-      <c r="D162" s="71" t="inlineStr">
+      <c r="D162" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4375183129/</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="69" t="inlineStr">
+      <c r="A163" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B163" s="70" t="n">
+      <c r="B163" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -3936,19 +3945,19 @@
           <t>Lead Firmware V&amp;V</t>
         </is>
       </c>
-      <c r="D163" s="71" t="inlineStr">
+      <c r="D163" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4402920307/</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="69" t="inlineStr">
+      <c r="A164" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B164" s="70" t="n">
+      <c r="B164" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -3956,19 +3965,19 @@
           <t>Sr. Systems Engineer</t>
         </is>
       </c>
-      <c r="D164" s="71" t="inlineStr">
+      <c r="D164" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461756319/</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B165" s="70" t="n">
+      <c r="A165" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B165" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -3976,19 +3985,19 @@
           <t>Senior Lead Government Affairs Manager - Federal</t>
         </is>
       </c>
-      <c r="D165" s="71" t="inlineStr">
+      <c r="D165" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440825647/</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="69" t="inlineStr">
+      <c r="A166" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B166" s="70" t="n">
+      <c r="B166" s="73" t="n">
         <v>46274</v>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -3996,19 +4005,19 @@
           <t>Staff Database Administrator</t>
         </is>
       </c>
-      <c r="D166" s="71" t="inlineStr">
+      <c r="D166" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456333107/</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B167" s="70" t="n">
+      <c r="A167" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B167" s="73" t="n">
         <v>46277</v>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -4016,19 +4025,19 @@
           <t>Equipment Technician 2 (2A Sunday - Tuesday, every other Saturday from 5:00PM - 5:00AM )</t>
         </is>
       </c>
-      <c r="D167" s="71" t="inlineStr">
+      <c r="D167" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466467687/</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B168" s="70" t="n">
+      <c r="A168" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B168" s="73" t="n">
         <v>46277</v>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -4036,19 +4045,19 @@
           <t>Equipment Technician 2 (2B Wednesday - Friday, every other Saturday from 5:00PM - 5:00AM)</t>
         </is>
       </c>
-      <c r="D168" s="71" t="inlineStr">
+      <c r="D168" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466428944/</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B169" s="70" t="n">
+      <c r="A169" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B169" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -4056,19 +4065,19 @@
           <t>New Business Development Manager, Trade Partnerships (eCommerce)</t>
         </is>
       </c>
-      <c r="D169" s="71" t="inlineStr">
+      <c r="D169" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459020959/</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="69" t="inlineStr">
+      <c r="A170" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B170" s="70" t="n">
+      <c r="B170" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -4076,19 +4085,19 @@
           <t>Sr Firmware V&amp;V</t>
         </is>
       </c>
-      <c r="D170" s="71" t="inlineStr">
+      <c r="D170" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4402292560/</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B171" s="70" t="n">
+      <c r="A171" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B171" s="73" t="n">
         <v>46277</v>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -4096,19 +4105,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D171" s="71" t="inlineStr">
+      <c r="D171" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457557361/</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B172" s="70" t="n">
+      <c r="A172" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B172" s="73" t="n">
         <v>46278</v>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -4116,19 +4125,19 @@
           <t>Staff Enterprise Applications Developer - IBM Maximo</t>
         </is>
       </c>
-      <c r="D172" s="71" t="inlineStr">
+      <c r="D172" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411935028/</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B173" s="70" t="n">
+      <c r="A173" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B173" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -4136,19 +4145,19 @@
           <t>Equipment Technician 4 ( Dobson ) 2B Night Shift: Wed-Fri, every other Sat.</t>
         </is>
       </c>
-      <c r="D173" s="71" t="inlineStr">
+      <c r="D173" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467703315/</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B174" s="70" t="n">
+      <c r="A174" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B174" s="73" t="n">
         <v>46277</v>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -4156,19 +4165,19 @@
           <t>HCP Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D174" s="71" t="inlineStr">
+      <c r="D174" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442796306/</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B175" s="70" t="n">
+      <c r="A175" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B175" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -4176,19 +4185,19 @@
           <t>Sr. Federal Clinical Educator - East</t>
         </is>
       </c>
-      <c r="D175" s="71" t="inlineStr">
+      <c r="D175" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455357586/</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="69" t="inlineStr">
+      <c r="A176" s="72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B176" s="70" t="n">
+      <c r="B176" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -4196,19 +4205,19 @@
           <t>Sr Legal Counsel, EMEA Privacy</t>
         </is>
       </c>
-      <c r="D176" s="71" t="inlineStr">
+      <c r="D176" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448305175/</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="69" t="inlineStr">
+      <c r="A177" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B177" s="70" t="n">
+      <c r="B177" s="73" t="n">
         <v>46281</v>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -4216,19 +4225,19 @@
           <t>Lead Financial Analyst</t>
         </is>
       </c>
-      <c r="D177" s="71" t="inlineStr">
+      <c r="D177" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467930929/</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="69" t="inlineStr">
+      <c r="A178" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B178" s="70" t="n">
+      <c r="B178" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -4236,19 +4245,19 @@
           <t>SW Development Engineer 2 - Android</t>
         </is>
       </c>
-      <c r="D178" s="71" t="inlineStr">
+      <c r="D178" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464610755/</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="69" t="inlineStr">
+      <c r="A179" s="72" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B179" s="70" t="n">
+      <c r="B179" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -4256,19 +4265,19 @@
           <t>Manager Accounts Payable</t>
         </is>
       </c>
-      <c r="D179" s="71" t="inlineStr">
+      <c r="D179" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467753397/</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B180" s="70" t="n">
+      <c r="A180" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B180" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -4276,19 +4285,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D180" s="71" t="inlineStr">
+      <c r="D180" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="69" t="inlineStr">
+      <c r="A181" s="72" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B181" s="70" t="n">
+      <c r="B181" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -4296,19 +4305,19 @@
           <t>Senior Market Access Manager CEE – Healthcare</t>
         </is>
       </c>
-      <c r="D181" s="71" t="inlineStr">
+      <c r="D181" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467756362/</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="69" t="inlineStr">
+      <c r="A182" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B182" s="70" t="n">
+      <c r="B182" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -4316,19 +4325,19 @@
           <t>Sr Equipment Engineer</t>
         </is>
       </c>
-      <c r="D182" s="71" t="inlineStr">
+      <c r="D182" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467749492/</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B183" s="70" t="n">
+      <c r="A183" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B183" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -4336,19 +4345,19 @@
           <t>Territory Business Manager - Central / SE Alabama</t>
         </is>
       </c>
-      <c r="D183" s="71" t="inlineStr">
+      <c r="D183" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448610622/</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B184" s="70" t="n">
+      <c r="A184" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B184" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -4356,19 +4365,19 @@
           <t>Associate Customer Insights Manager</t>
         </is>
       </c>
-      <c r="D184" s="71" t="inlineStr">
+      <c r="D184" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B185" s="70" t="n">
+      <c r="A185" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B185" s="73" t="n">
         <v>46277</v>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -4376,19 +4385,19 @@
           <t>Sr. Planner Analyst</t>
         </is>
       </c>
-      <c r="D185" s="71" t="inlineStr">
+      <c r="D185" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457555402/</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B186" s="70" t="n">
+      <c r="A186" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B186" s="73" t="n">
         <v>46277</v>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -4396,19 +4405,19 @@
           <t>Mechanical Engineering Manager</t>
         </is>
       </c>
-      <c r="D186" s="71" t="inlineStr">
+      <c r="D186" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447571908/</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B187" s="70" t="n">
+      <c r="A187" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B187" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -4416,19 +4425,19 @@
           <t>Sr. Manager, Data Protection and Insider Risk</t>
         </is>
       </c>
-      <c r="D187" s="71" t="inlineStr">
+      <c r="D187" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467266843/</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="69" t="inlineStr">
+      <c r="A188" s="72" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B188" s="70" t="n">
+      <c r="B188" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -4436,19 +4445,19 @@
           <t>Brand &amp; Portfolio Marketing Lead - DACH (m/w/d)</t>
         </is>
       </c>
-      <c r="D188" s="71" t="inlineStr">
+      <c r="D188" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467076868/</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="69" t="inlineStr">
+      <c r="A189" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B189" s="70" t="n">
+      <c r="B189" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -4456,19 +4465,19 @@
           <t>Manager, SW System &amp; Solution Dev Engineer</t>
         </is>
       </c>
-      <c r="D189" s="71" t="inlineStr">
+      <c r="D189" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B190" s="70" t="n">
+      <c r="A190" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B190" s="73" t="n">
         <v>46277</v>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -4476,19 +4485,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D190" s="71" t="inlineStr">
+      <c r="D190" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466463712/</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B191" s="70" t="n">
+      <c r="A191" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B191" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -4496,19 +4505,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D191" s="71" t="inlineStr">
+      <c r="D191" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B192" s="70" t="n">
+      <c r="A192" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B192" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -4516,19 +4525,19 @@
           <t>Payor Analytics Senior Pricing Analyst</t>
         </is>
       </c>
-      <c r="D192" s="71" t="inlineStr">
+      <c r="D192" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467785422/</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B193" s="70" t="n">
+      <c r="A193" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B193" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -4536,19 +4545,19 @@
           <t>Associate Marketing Manager, Digital Projects</t>
         </is>
       </c>
-      <c r="D193" s="71" t="inlineStr">
+      <c r="D193" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458569116/</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="69" t="inlineStr">
+      <c r="A194" s="72" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B194" s="70" t="n">
+      <c r="B194" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -4556,19 +4565,19 @@
           <t>Sr Automation Engineer</t>
         </is>
       </c>
-      <c r="D194" s="71" t="inlineStr">
+      <c r="D194" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467078747/</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="69" t="inlineStr">
+      <c r="A195" s="72" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B195" s="70" t="n">
+      <c r="B195" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -4576,19 +4585,19 @@
           <t>Technical Support Representative, Dutch Speaker</t>
         </is>
       </c>
-      <c r="D195" s="71" t="inlineStr">
+      <c r="D195" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4364850511/</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B196" s="70" t="n">
+      <c r="A196" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B196" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -4596,19 +4605,19 @@
           <t>Equipment Technician 3 ( 1A Sunday - Tuesday, every other Wednesday from 5:00AM to 5:00PM)</t>
         </is>
       </c>
-      <c r="D196" s="71" t="inlineStr">
+      <c r="D196" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466422908/</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B197" s="70" t="n">
+      <c r="A197" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B197" s="73" t="n">
         <v>46277</v>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -4616,19 +4625,19 @@
           <t>Sr SW Test Development Engineer</t>
         </is>
       </c>
-      <c r="D197" s="71" t="inlineStr">
+      <c r="D197" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457511030/</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="69" t="inlineStr">
+      <c r="A198" s="72" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B198" s="70" t="n">
+      <c r="B198" s="73" t="n">
         <v>46276</v>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -4636,19 +4645,19 @@
           <t>Production Operator - Days - Athenry</t>
         </is>
       </c>
-      <c r="D198" s="71" t="inlineStr">
+      <c r="D198" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457002672/</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="69" t="inlineStr">
+      <c r="A199" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B199" s="70" t="n">
+      <c r="B199" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -4656,19 +4665,19 @@
           <t>SW Test Development Engineer 2</t>
         </is>
       </c>
-      <c r="D199" s="71" t="inlineStr">
+      <c r="D199" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457076040/</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B200" s="70" t="n">
+      <c r="A200" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B200" s="73" t="n">
         <v>46275</v>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -4676,19 +4685,19 @@
           <t>Senior Staff SW Systems Engineer - Mobile Apps</t>
         </is>
       </c>
-      <c r="D200" s="71" t="inlineStr">
+      <c r="D200" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438120759/</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B201" s="70" t="n">
+      <c r="A201" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B201" s="73" t="n">
         <v>46276</v>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -4696,19 +4705,19 @@
           <t>Staff Algorithm Engineer - Emerging Sensing Technologies</t>
         </is>
       </c>
-      <c r="D201" s="71" t="inlineStr">
+      <c r="D201" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447244362/</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B202" s="70" t="n">
+      <c r="A202" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B202" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -4716,19 +4725,19 @@
           <t>QA Inspector 1 (Shift 1A: Days - Sun - Tues every other Wed from 5AM to 5PM )</t>
         </is>
       </c>
-      <c r="D202" s="71" t="inlineStr">
+      <c r="D202" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456781801/</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B203" s="70" t="n">
+      <c r="A203" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B203" s="73" t="n">
         <v>46280</v>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -4736,19 +4745,19 @@
           <t>Sr New Business Development Manager</t>
         </is>
       </c>
-      <c r="D203" s="71" t="inlineStr">
+      <c r="D203" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467430423/</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="69" t="inlineStr">
+      <c r="A204" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B204" s="70" t="n">
+      <c r="B204" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -4756,19 +4765,19 @@
           <t>Sr. SW Test Development Engineer V&amp;V</t>
         </is>
       </c>
-      <c r="D204" s="71" t="inlineStr">
+      <c r="D204" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387839555/</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B205" s="70" t="n">
+      <c r="A205" s="72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B205" s="73" t="n">
         <v>46276</v>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -4776,19 +4785,19 @@
           <t>Staff SW Development Engineer</t>
         </is>
       </c>
-      <c r="D205" s="71" t="inlineStr">
+      <c r="D205" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466372374/</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="69" t="inlineStr">
+      <c r="A206" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B206" s="70" t="n">
+      <c r="B206" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -4796,19 +4805,19 @@
           <t>Sr SW Development Engineer - Android</t>
         </is>
       </c>
-      <c r="D206" s="71" t="inlineStr">
+      <c r="D206" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465019023/</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="69" t="inlineStr">
+      <c r="A207" s="72" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B207" s="70" t="n">
+      <c r="B207" s="73" t="n">
         <v>46279</v>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -4816,7 +4825,7 @@
           <t>Sr SW Development Engineer - IOS</t>
         </is>
       </c>
-      <c r="D207" s="71" t="inlineStr">
+      <c r="D207" s="74" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465020025/</t>
         </is>
@@ -4862,8 +4871,108 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="75" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B210" s="76" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>Training and Quality Manager (Customer Service)</t>
+        </is>
+      </c>
+      <c r="D210" s="77" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439090281/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B211" s="76" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>Continuous Improvement Analyst (Green Belt)</t>
+        </is>
+      </c>
+      <c r="D211" s="77" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458553387/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="75" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B212" s="76" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>ECAD Technician 2</t>
+        </is>
+      </c>
+      <c r="D212" s="77" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456709938/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="75" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B213" s="76" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Sr Fimware Engineer</t>
+        </is>
+      </c>
+      <c r="D213" s="77" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4366307571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B214" s="76" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 1 ( RDC ) 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
+        </is>
+      </c>
+      <c r="D214" s="77" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459645247/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D209"/>
+  <autoFilter ref="A1:D214"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -5073,6 +5182,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId213"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -712,12 +712,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="73" t="n">
+      <c r="B2" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -725,19 +725,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="74" t="inlineStr">
+      <c r="D2" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="73" t="n">
+      <c r="B3" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -745,19 +745,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="74" t="inlineStr">
+      <c r="D3" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72" t="inlineStr">
+      <c r="A4" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="73" t="n">
+      <c r="B4" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -765,19 +765,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="74" t="inlineStr">
+      <c r="D4" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="75" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="73" t="n">
+      <c r="B5" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -785,19 +785,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="D5" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="72" t="inlineStr">
+      <c r="A6" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="73" t="n">
+      <c r="B6" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -805,19 +805,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="74" t="inlineStr">
+      <c r="D6" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="72" t="inlineStr">
+      <c r="A7" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="73" t="n">
+      <c r="B7" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -825,19 +825,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="74" t="inlineStr">
+      <c r="D7" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="72" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="73" t="n">
+      <c r="B8" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -845,19 +845,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="74" t="inlineStr">
+      <c r="D8" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="73" t="n">
+      <c r="B9" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -865,19 +865,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="74" t="inlineStr">
+      <c r="D9" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="73" t="n">
+      <c r="B10" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -885,19 +885,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="74" t="inlineStr">
+      <c r="D10" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="73" t="n">
+      <c r="B11" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -905,19 +905,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="74" t="inlineStr">
+      <c r="D11" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="73" t="n">
+      <c r="B12" s="76" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -925,19 +925,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="74" t="inlineStr">
+      <c r="D12" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="72" t="inlineStr">
+      <c r="A13" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="73" t="n">
+      <c r="B13" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -945,19 +945,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="74" t="inlineStr">
+      <c r="D13" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="72" t="inlineStr">
+      <c r="A14" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="73" t="n">
+      <c r="B14" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -965,19 +965,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="74" t="inlineStr">
+      <c r="D14" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="73" t="n">
+      <c r="A15" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -985,19 +985,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="74" t="inlineStr">
+      <c r="D15" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="72" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="73" t="n">
+      <c r="B16" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1005,19 +1005,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="74" t="inlineStr">
+      <c r="D16" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="73" t="n">
+      <c r="B17" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1025,19 +1025,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="74" t="inlineStr">
+      <c r="D17" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="72" t="inlineStr">
+      <c r="A18" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="73" t="n">
+      <c r="B18" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1045,19 +1045,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="74" t="inlineStr">
+      <c r="D18" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="73" t="n">
+      <c r="B19" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1065,19 +1065,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="74" t="inlineStr">
+      <c r="D19" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="72" t="inlineStr">
+      <c r="A20" s="75" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="73" t="n">
+      <c r="B20" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1085,19 +1085,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="74" t="inlineStr">
+      <c r="D20" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B21" s="73" t="n">
+      <c r="A21" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1105,19 +1105,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="74" t="inlineStr">
+      <c r="D21" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="72" t="inlineStr">
+      <c r="A22" s="75" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="73" t="n">
+      <c r="B22" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1125,19 +1125,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="74" t="inlineStr">
+      <c r="D22" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B23" s="73" t="n">
+      <c r="A23" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B23" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1145,19 +1145,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="74" t="inlineStr">
+      <c r="D23" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="72" t="inlineStr">
+      <c r="A24" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="73" t="n">
+      <c r="B24" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1165,19 +1165,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="74" t="inlineStr">
+      <c r="D24" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="72" t="inlineStr">
+      <c r="A25" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="73" t="n">
+      <c r="B25" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1185,19 +1185,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="74" t="inlineStr">
+      <c r="D25" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="72" t="inlineStr">
+      <c r="A26" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="73" t="n">
+      <c r="B26" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1205,19 +1205,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="74" t="inlineStr">
+      <c r="D26" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="72" t="inlineStr">
+      <c r="A27" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="73" t="n">
+      <c r="B27" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1225,19 +1225,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="74" t="inlineStr">
+      <c r="D27" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="72" t="inlineStr">
+      <c r="A28" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="73" t="n">
+      <c r="B28" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1245,19 +1245,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="74" t="inlineStr">
+      <c r="D28" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="A29" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="73" t="n">
+      <c r="B29" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1265,19 +1265,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="74" t="inlineStr">
+      <c r="D29" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="72" t="inlineStr">
+      <c r="A30" s="75" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="73" t="n">
+      <c r="B30" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1285,19 +1285,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="74" t="inlineStr">
+      <c r="D30" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="72" t="inlineStr">
+      <c r="A31" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="73" t="n">
+      <c r="B31" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1305,19 +1305,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="74" t="inlineStr">
+      <c r="D31" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="73" t="n">
+      <c r="A32" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1325,19 +1325,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="74" t="inlineStr">
+      <c r="D32" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="73" t="n">
+      <c r="A33" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1345,19 +1345,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="74" t="inlineStr">
+      <c r="D33" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="72" t="inlineStr">
+      <c r="A34" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="73" t="n">
+      <c r="B34" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1365,19 +1365,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="74" t="inlineStr">
+      <c r="D34" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="72" t="inlineStr">
+      <c r="A35" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="73" t="n">
+      <c r="B35" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1385,19 +1385,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="74" t="inlineStr">
+      <c r="D35" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="72" t="inlineStr">
+      <c r="A36" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="73" t="n">
+      <c r="B36" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1405,19 +1405,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="74" t="inlineStr">
+      <c r="D36" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="72" t="inlineStr">
+      <c r="A37" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="73" t="n">
+      <c r="B37" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1425,19 +1425,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="74" t="inlineStr">
+      <c r="D37" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="72" t="inlineStr">
+      <c r="A38" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="73" t="n">
+      <c r="B38" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1445,19 +1445,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="74" t="inlineStr">
+      <c r="D38" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="72" t="inlineStr">
+      <c r="A39" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="73" t="n">
+      <c r="B39" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1465,19 +1465,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="74" t="inlineStr">
+      <c r="D39" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="72" t="inlineStr">
+      <c r="A40" s="75" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="73" t="n">
+      <c r="B40" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1485,19 +1485,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="74" t="inlineStr">
+      <c r="D40" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="72" t="inlineStr">
+      <c r="A41" s="75" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="73" t="n">
+      <c r="B41" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1505,19 +1505,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="74" t="inlineStr">
+      <c r="D41" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B42" s="73" t="n">
+      <c r="A42" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B42" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1525,19 +1525,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="74" t="inlineStr">
+      <c r="D42" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="73" t="n">
+      <c r="A43" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1545,19 +1545,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="74" t="inlineStr">
+      <c r="D43" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="72" t="inlineStr">
+      <c r="A44" s="75" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="73" t="n">
+      <c r="B44" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1565,19 +1565,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="74" t="inlineStr">
+      <c r="D44" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="72" t="inlineStr">
+      <c r="A45" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="73" t="n">
+      <c r="B45" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1585,19 +1585,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="74" t="inlineStr">
+      <c r="D45" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="73" t="n">
+      <c r="A46" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1605,19 +1605,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="74" t="inlineStr">
+      <c r="D46" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="72" t="inlineStr">
+      <c r="A47" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="73" t="n">
+      <c r="B47" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1625,19 +1625,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="74" t="inlineStr">
+      <c r="D47" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="72" t="inlineStr">
+      <c r="A48" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="73" t="n">
+      <c r="B48" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1645,19 +1645,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="74" t="inlineStr">
+      <c r="D48" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="72" t="inlineStr">
+      <c r="A49" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="73" t="n">
+      <c r="B49" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1665,19 +1665,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="74" t="inlineStr">
+      <c r="D49" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="72" t="inlineStr">
+      <c r="A50" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="73" t="n">
+      <c r="B50" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="74" t="inlineStr">
+      <c r="D50" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="72" t="inlineStr">
+      <c r="A51" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="73" t="n">
+      <c r="B51" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1705,19 +1705,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="74" t="inlineStr">
+      <c r="D51" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="72" t="inlineStr">
+      <c r="A52" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="73" t="n">
+      <c r="B52" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1725,19 +1725,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="74" t="inlineStr">
+      <c r="D52" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="72" t="inlineStr">
+      <c r="A53" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="73" t="n">
+      <c r="B53" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1745,19 +1745,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="74" t="inlineStr">
+      <c r="D53" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="72" t="inlineStr">
+      <c r="A54" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="73" t="n">
+      <c r="B54" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="74" t="inlineStr">
+      <c r="D54" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="72" t="inlineStr">
+      <c r="A55" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="73" t="n">
+      <c r="B55" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1785,19 +1785,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="74" t="inlineStr">
+      <c r="D55" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="72" t="inlineStr">
+      <c r="A56" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="73" t="n">
+      <c r="B56" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1805,19 +1805,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="74" t="inlineStr">
+      <c r="D56" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="72" t="inlineStr">
+      <c r="A57" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="73" t="n">
+      <c r="B57" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1825,19 +1825,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="74" t="inlineStr">
+      <c r="D57" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="72" t="inlineStr">
+      <c r="A58" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="73" t="n">
+      <c r="B58" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="74" t="inlineStr">
+      <c r="D58" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="73" t="n">
+      <c r="A59" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1865,19 +1865,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="74" t="inlineStr">
+      <c r="D59" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="72" t="inlineStr">
+      <c r="A60" s="75" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="73" t="n">
+      <c r="B60" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1885,19 +1885,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="74" t="inlineStr">
+      <c r="D60" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B61" s="73" t="n">
+      <c r="A61" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B61" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1905,19 +1905,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="74" t="inlineStr">
+      <c r="D61" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="72" t="inlineStr">
+      <c r="A62" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="73" t="n">
+      <c r="B62" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="74" t="inlineStr">
+      <c r="D62" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="73" t="n">
+      <c r="A63" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1945,19 +1945,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="74" t="inlineStr">
+      <c r="D63" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="72" t="inlineStr">
+      <c r="A64" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="73" t="n">
+      <c r="B64" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1965,19 +1965,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="74" t="inlineStr">
+      <c r="D64" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B65" s="73" t="n">
+      <c r="A65" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B65" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1985,19 +1985,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="74" t="inlineStr">
+      <c r="D65" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="72" t="inlineStr">
+      <c r="A66" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="73" t="n">
+      <c r="B66" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="74" t="inlineStr">
+      <c r="D66" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B67" s="73" t="n">
+      <c r="A67" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B67" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2025,19 +2025,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="74" t="inlineStr">
+      <c r="D67" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="72" t="inlineStr">
+      <c r="A68" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="73" t="n">
+      <c r="B68" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -2045,19 +2045,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="74" t="inlineStr">
+      <c r="D68" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="72" t="inlineStr">
+      <c r="A69" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="73" t="n">
+      <c r="B69" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2065,19 +2065,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="74" t="inlineStr">
+      <c r="D69" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="72" t="inlineStr">
+      <c r="A70" s="75" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="73" t="n">
+      <c r="B70" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="74" t="inlineStr">
+      <c r="D70" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="72" t="inlineStr">
+      <c r="A71" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="73" t="n">
+      <c r="B71" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2105,19 +2105,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="74" t="inlineStr">
+      <c r="D71" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="72" t="inlineStr">
+      <c r="A72" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="73" t="n">
+      <c r="B72" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2125,19 +2125,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="74" t="inlineStr">
+      <c r="D72" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="72" t="inlineStr">
+      <c r="A73" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="73" t="n">
+      <c r="B73" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2145,19 +2145,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="74" t="inlineStr">
+      <c r="D73" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="72" t="inlineStr">
+      <c r="A74" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="73" t="n">
+      <c r="B74" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="74" t="inlineStr">
+      <c r="D74" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="72" t="inlineStr">
+      <c r="A75" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="73" t="n">
+      <c r="B75" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2185,19 +2185,19 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="74" t="inlineStr">
+      <c r="D75" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="72" t="inlineStr">
+      <c r="A76" s="75" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B76" s="73" t="n">
+      <c r="B76" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2205,19 +2205,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D76" s="74" t="inlineStr">
+      <c r="D76" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="72" t="inlineStr">
+      <c r="A77" s="75" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B77" s="73" t="n">
+      <c r="B77" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2225,19 +2225,19 @@
           <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
         </is>
       </c>
-      <c r="D77" s="74" t="inlineStr">
+      <c r="D77" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765129/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="72" t="inlineStr">
+      <c r="A78" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="73" t="n">
+      <c r="B78" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D78" s="74" t="inlineStr">
+      <c r="D78" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="72" t="inlineStr">
+      <c r="A79" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B79" s="73" t="n">
+      <c r="B79" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2265,19 +2265,19 @@
           <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
-      <c r="D79" s="74" t="inlineStr">
+      <c r="D79" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="72" t="inlineStr">
+      <c r="A80" s="75" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B80" s="73" t="n">
+      <c r="B80" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2285,19 +2285,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D80" s="74" t="inlineStr">
+      <c r="D80" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="72" t="inlineStr">
+      <c r="A81" s="75" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B81" s="73" t="n">
+      <c r="B81" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2305,19 +2305,19 @@
           <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
         </is>
       </c>
-      <c r="D81" s="74" t="inlineStr">
+      <c r="D81" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450696746/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="72" t="inlineStr">
+      <c r="A82" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="73" t="n">
+      <c r="B82" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Logistics Analyst</t>
         </is>
       </c>
-      <c r="D82" s="74" t="inlineStr">
+      <c r="D82" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461266744/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="72" t="inlineStr">
+      <c r="A83" s="75" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B83" s="73" t="n">
+      <c r="B83" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2345,19 +2345,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D83" s="74" t="inlineStr">
+      <c r="D83" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="72" t="inlineStr">
+      <c r="A84" s="75" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B84" s="73" t="n">
+      <c r="B84" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2365,19 +2365,19 @@
           <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D84" s="74" t="inlineStr">
+      <c r="D84" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459309508/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="72" t="inlineStr">
+      <c r="A85" s="75" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" s="73" t="n">
+      <c r="B85" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2385,19 +2385,19 @@
           <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
         </is>
       </c>
-      <c r="D85" s="74" t="inlineStr">
+      <c r="D85" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770007/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="72" t="inlineStr">
+      <c r="A86" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="73" t="n">
+      <c r="B86" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D86" s="74" t="inlineStr">
+      <c r="D86" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="72" t="inlineStr">
+      <c r="A87" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B87" s="73" t="n">
+      <c r="B87" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2425,19 +2425,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D87" s="74" t="inlineStr">
+      <c r="D87" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="72" t="inlineStr">
+      <c r="A88" s="75" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B88" s="73" t="n">
+      <c r="B88" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2445,19 +2445,19 @@
           <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
-      <c r="D88" s="74" t="inlineStr">
+      <c r="D88" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="72" t="inlineStr">
+      <c r="A89" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="73" t="n">
+      <c r="B89" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2465,19 +2465,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D89" s="74" t="inlineStr">
+      <c r="D89" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="72" t="inlineStr">
+      <c r="A90" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B90" s="73" t="n">
+      <c r="B90" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2485,19 +2485,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D90" s="74" t="inlineStr">
+      <c r="D90" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="72" t="inlineStr">
+      <c r="A91" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B91" s="73" t="n">
+      <c r="B91" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2505,19 +2505,19 @@
           <t>Contract Administration Representative (French-speaking)</t>
         </is>
       </c>
-      <c r="D91" s="74" t="inlineStr">
+      <c r="D91" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461090763/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="72" t="inlineStr">
+      <c r="A92" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B92" s="73" t="n">
+      <c r="B92" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2525,19 +2525,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D92" s="74" t="inlineStr">
+      <c r="D92" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="72" t="inlineStr">
+      <c r="A93" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B93" s="73" t="n">
+      <c r="B93" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2545,19 +2545,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D93" s="74" t="inlineStr">
+      <c r="D93" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="72" t="inlineStr">
+      <c r="A94" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B94" s="73" t="n">
+      <c r="B94" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2565,19 +2565,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D94" s="74" t="inlineStr">
+      <c r="D94" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453089165/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="72" t="inlineStr">
+      <c r="A95" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B95" s="73" t="n">
+      <c r="B95" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2585,19 +2585,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D95" s="74" t="inlineStr">
+      <c r="D95" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="72" t="inlineStr">
+      <c r="A96" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B96" s="73" t="n">
+      <c r="B96" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2605,19 +2605,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D96" s="74" t="inlineStr">
+      <c r="D96" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="72" t="inlineStr">
+      <c r="A97" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B97" s="73" t="n">
+      <c r="B97" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2625,19 +2625,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D97" s="74" t="inlineStr">
+      <c r="D97" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="72" t="inlineStr">
+      <c r="A98" s="75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B98" s="73" t="n">
+      <c r="B98" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2645,19 +2645,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D98" s="74" t="inlineStr">
+      <c r="D98" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="72" t="inlineStr">
+      <c r="A99" s="75" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B99" s="73" t="n">
+      <c r="B99" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2665,19 +2665,19 @@
           <t>Technical Support Representative 2</t>
         </is>
       </c>
-      <c r="D99" s="74" t="inlineStr">
+      <c r="D99" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438880089/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="72" t="inlineStr">
+      <c r="A100" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B100" s="73" t="n">
+      <c r="B100" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2685,19 +2685,19 @@
           <t>Spanish Bilingual Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D100" s="74" t="inlineStr">
+      <c r="D100" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458704406/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="72" t="inlineStr">
+      <c r="A101" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B101" s="73" t="n">
+      <c r="B101" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2705,19 +2705,19 @@
           <t>Spanish Bilingual TSR</t>
         </is>
       </c>
-      <c r="D101" s="74" t="inlineStr">
+      <c r="D101" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407814543/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B102" s="73" t="n">
+      <c r="A102" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B102" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2725,19 +2725,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D102" s="74" t="inlineStr">
+      <c r="D102" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="72" t="inlineStr">
+      <c r="A103" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B103" s="73" t="n">
+      <c r="B103" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2745,19 +2745,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D103" s="74" t="inlineStr">
+      <c r="D103" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B104" s="73" t="n">
+      <c r="A104" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B104" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2765,19 +2765,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D104" s="74" t="inlineStr">
+      <c r="D104" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B105" s="73" t="n">
+      <c r="A105" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B105" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2785,19 +2785,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D105" s="74" t="inlineStr">
+      <c r="D105" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B106" s="73" t="n">
+      <c r="A106" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B106" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2805,19 +2805,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D106" s="74" t="inlineStr">
+      <c r="D106" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439353245/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="72" t="inlineStr">
+      <c r="A107" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B107" s="73" t="n">
+      <c r="B107" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2825,19 +2825,19 @@
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="D107" s="74" t="inlineStr">
+      <c r="D107" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="72" t="inlineStr">
+      <c r="A108" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B108" s="73" t="n">
+      <c r="B108" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2845,19 +2845,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D108" s="74" t="inlineStr">
+      <c r="D108" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082223/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="72" t="inlineStr">
+      <c r="A109" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B109" s="73" t="n">
+      <c r="B109" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2865,19 +2865,19 @@
           <t>Business Process Analyst</t>
         </is>
       </c>
-      <c r="D109" s="74" t="inlineStr">
+      <c r="D109" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414569192/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B110" s="73" t="n">
+      <c r="A110" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2885,19 +2885,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D110" s="74" t="inlineStr">
+      <c r="D110" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456380639/</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B111" s="73" t="n">
+      <c r="A111" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B111" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2905,19 +2905,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D111" s="74" t="inlineStr">
+      <c r="D111" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456364824/</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="72" t="inlineStr">
+      <c r="A112" s="75" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B112" s="73" t="n">
+      <c r="B112" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -2925,19 +2925,19 @@
           <t>Associate Marketing Manager</t>
         </is>
       </c>
-      <c r="D112" s="74" t="inlineStr">
+      <c r="D112" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451399530/</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B113" s="73" t="n">
+      <c r="A113" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B113" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -2945,19 +2945,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D113" s="74" t="inlineStr">
+      <c r="D113" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B114" s="73" t="n">
+      <c r="A114" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B114" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -2965,19 +2965,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D114" s="74" t="inlineStr">
+      <c r="D114" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="72" t="inlineStr">
+      <c r="A115" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B115" s="73" t="n">
+      <c r="B115" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -2985,19 +2985,19 @@
           <t>Senior Sterilization Engineer</t>
         </is>
       </c>
-      <c r="D115" s="74" t="inlineStr">
+      <c r="D115" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410980549/</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="72" t="inlineStr">
+      <c r="A116" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B116" s="73" t="n">
+      <c r="B116" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -3005,19 +3005,19 @@
           <t>Accounts Payable Process Expert (Maternity Cover)</t>
         </is>
       </c>
-      <c r="D116" s="74" t="inlineStr">
+      <c r="D116" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462464542/</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="72" t="inlineStr">
+      <c r="A117" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B117" s="73" t="n">
+      <c r="B117" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -3025,19 +3025,19 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D117" s="74" t="inlineStr">
+      <c r="D117" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B118" s="73" t="n">
+      <c r="A118" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B118" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -3045,19 +3045,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D118" s="74" t="inlineStr">
+      <c r="D118" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="72" t="inlineStr">
+      <c r="A119" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B119" s="73" t="n">
+      <c r="B119" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3065,19 +3065,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D119" s="74" t="inlineStr">
+      <c r="D119" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B120" s="73" t="n">
+      <c r="A120" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B120" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3085,19 +3085,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D120" s="74" t="inlineStr">
+      <c r="D120" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="72" t="inlineStr">
+      <c r="A121" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B121" s="73" t="n">
+      <c r="B121" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3105,19 +3105,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D121" s="74" t="inlineStr">
+      <c r="D121" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B122" s="73" t="n">
+      <c r="A122" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B122" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3125,19 +3125,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D122" s="74" t="inlineStr">
+      <c r="D122" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="72" t="inlineStr">
+      <c r="A123" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B123" s="73" t="n">
+      <c r="B123" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3145,19 +3145,19 @@
           <t>Staff SRE SW Development Engineer</t>
         </is>
       </c>
-      <c r="D123" s="74" t="inlineStr">
+      <c r="D123" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387683946/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B124" s="73" t="n">
+      <c r="A124" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B124" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3165,19 +3165,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D124" s="74" t="inlineStr">
+      <c r="D124" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B125" s="73" t="n">
+      <c r="A125" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B125" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3185,19 +3185,19 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D125" s="74" t="inlineStr">
+      <c r="D125" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="72" t="inlineStr">
+      <c r="A126" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B126" s="73" t="n">
+      <c r="B126" s="76" t="n">
         <v>46276</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3205,19 +3205,19 @@
           <t>Third Party Risk and Supplier Onboarding Manager</t>
         </is>
       </c>
-      <c r="D126" s="74" t="inlineStr">
+      <c r="D126" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466048486/</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="72" t="inlineStr">
+      <c r="A127" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B127" s="73" t="n">
+      <c r="B127" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3225,19 +3225,19 @@
           <t>Senior Service Designer, Technical Support</t>
         </is>
       </c>
-      <c r="D127" s="74" t="inlineStr">
+      <c r="D127" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455960251/</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B128" s="73" t="n">
+      <c r="A128" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B128" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -3245,19 +3245,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D128" s="74" t="inlineStr">
+      <c r="D128" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464945232/</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="72" t="inlineStr">
+      <c r="A129" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B129" s="73" t="n">
+      <c r="B129" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -3265,19 +3265,19 @@
           <t>Supervisor Manufacturing</t>
         </is>
       </c>
-      <c r="D129" s="74" t="inlineStr">
+      <c r="D129" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4428861138/</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="72" t="inlineStr">
+      <c r="A130" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B130" s="73" t="n">
+      <c r="B130" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -3285,19 +3285,19 @@
           <t>Staff Database Administrator</t>
         </is>
       </c>
-      <c r="D130" s="74" t="inlineStr">
+      <c r="D130" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322200/</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="72" t="inlineStr">
+      <c r="A131" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B131" s="73" t="n">
+      <c r="B131" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -3305,19 +3305,19 @@
           <t>Payroll Analyst (ANZ)</t>
         </is>
       </c>
-      <c r="D131" s="74" t="inlineStr">
+      <c r="D131" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456178209/</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="72" t="inlineStr">
+      <c r="A132" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B132" s="73" t="n">
+      <c r="B132" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -3325,19 +3325,19 @@
           <t>SW Test Development Engineer 1</t>
         </is>
       </c>
-      <c r="D132" s="74" t="inlineStr">
+      <c r="D132" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465029007/</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B133" s="73" t="n">
+      <c r="A133" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B133" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -3345,19 +3345,19 @@
           <t>Sr Workplace Solutions Analyst</t>
         </is>
       </c>
-      <c r="D133" s="74" t="inlineStr">
+      <c r="D133" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322161/</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="72" t="inlineStr">
+      <c r="A134" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B134" s="73" t="n">
+      <c r="B134" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -3365,19 +3365,19 @@
           <t>Staff SW Development Engineer</t>
         </is>
       </c>
-      <c r="D134" s="74" t="inlineStr">
+      <c r="D134" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465323573/</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="72" t="inlineStr">
+      <c r="A135" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B135" s="73" t="n">
+      <c r="B135" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3385,19 +3385,19 @@
           <t>Director, Business Program Management Office</t>
         </is>
       </c>
-      <c r="D135" s="74" t="inlineStr">
+      <c r="D135" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456105988/</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="72" t="inlineStr">
+      <c r="A136" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B136" s="73" t="n">
+      <c r="B136" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3405,19 +3405,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D136" s="74" t="inlineStr">
+      <c r="D136" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456115187/</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B137" s="73" t="n">
+      <c r="A137" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B137" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -3425,19 +3425,19 @@
           <t>Systems Design &amp; Test Engineer 2</t>
         </is>
       </c>
-      <c r="D137" s="74" t="inlineStr">
+      <c r="D137" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443989564/</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B138" s="73" t="n">
+      <c r="A138" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B138" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -3445,19 +3445,19 @@
           <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
         </is>
       </c>
-      <c r="D138" s="74" t="inlineStr">
+      <c r="D138" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439394782/</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="72" t="inlineStr">
+      <c r="A139" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B139" s="73" t="n">
+      <c r="B139" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -3465,19 +3465,19 @@
           <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
-      <c r="D139" s="74" t="inlineStr">
+      <c r="D139" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="72" t="inlineStr">
+      <c r="A140" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B140" s="73" t="n">
+      <c r="B140" s="76" t="n">
         <v>46278</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -3485,19 +3485,19 @@
           <t>Sr. Financial Analyst</t>
         </is>
       </c>
-      <c r="D140" s="74" t="inlineStr">
+      <c r="D140" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4421230278/</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="72" t="inlineStr">
+      <c r="A141" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B141" s="73" t="n">
+      <c r="B141" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -3505,19 +3505,19 @@
           <t>Sr Cybersecurity Analyst</t>
         </is>
       </c>
-      <c r="D141" s="74" t="inlineStr">
+      <c r="D141" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439085443/</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="72" t="inlineStr">
+      <c r="A142" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B142" s="73" t="n">
+      <c r="B142" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -3525,19 +3525,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D142" s="74" t="inlineStr">
+      <c r="D142" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="72" t="inlineStr">
+      <c r="A143" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B143" s="73" t="n">
+      <c r="B143" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -3545,19 +3545,19 @@
           <t>Trade Compliance Analyst</t>
         </is>
       </c>
-      <c r="D143" s="74" t="inlineStr">
+      <c r="D143" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467033928/</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B144" s="73" t="n">
+      <c r="A144" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B144" s="76" t="n">
         <v>46278</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -3565,19 +3565,19 @@
           <t>Sr Manufacturing Engineer</t>
         </is>
       </c>
-      <c r="D144" s="74" t="inlineStr">
+      <c r="D144" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447583072/</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="72" t="inlineStr">
+      <c r="A145" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B145" s="73" t="n">
+      <c r="B145" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -3585,19 +3585,19 @@
           <t>Staff Vendor Management Analyst</t>
         </is>
       </c>
-      <c r="D145" s="74" t="inlineStr">
+      <c r="D145" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458212554/</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="72" t="inlineStr">
+      <c r="A146" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B146" s="73" t="n">
+      <c r="B146" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -3605,19 +3605,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D146" s="74" t="inlineStr">
+      <c r="D146" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458218533/</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="72" t="inlineStr">
+      <c r="A147" s="75" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B147" s="73" t="n">
+      <c r="B147" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -3625,19 +3625,19 @@
           <t>APAC Product Manager - OTC/Consumer Health</t>
         </is>
       </c>
-      <c r="D147" s="74" t="inlineStr">
+      <c r="D147" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4422693615/</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="72" t="inlineStr">
+      <c r="A148" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B148" s="73" t="n">
+      <c r="B148" s="76" t="n">
         <v>46278</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -3645,19 +3645,19 @@
           <t>Supervisor Technical Support - Manila</t>
         </is>
       </c>
-      <c r="D148" s="74" t="inlineStr">
+      <c r="D148" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417742237/</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="72" t="inlineStr">
+      <c r="A149" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B149" s="73" t="n">
+      <c r="B149" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -3665,19 +3665,19 @@
           <t>Staff Desktop Support Engineer</t>
         </is>
       </c>
-      <c r="D149" s="74" t="inlineStr">
+      <c r="D149" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4398315987/</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B150" s="73" t="n">
+      <c r="A150" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B150" s="76" t="n">
         <v>46276</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -3685,19 +3685,19 @@
           <t>Director HW Design Quality Engineering - New Product Introductions</t>
         </is>
       </c>
-      <c r="D150" s="74" t="inlineStr">
+      <c r="D150" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456789792/</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="72" t="inlineStr">
+      <c r="A151" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B151" s="73" t="n">
+      <c r="B151" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -3705,19 +3705,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D151" s="74" t="inlineStr">
+      <c r="D151" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B152" s="73" t="n">
+      <c r="A152" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B152" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -3725,19 +3725,19 @@
           <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
         </is>
       </c>
-      <c r="D152" s="74" t="inlineStr">
+      <c r="D152" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="72" t="inlineStr">
+      <c r="A153" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B153" s="73" t="n">
+      <c r="B153" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -3745,19 +3745,19 @@
           <t>Supervisor, Applications Support</t>
         </is>
       </c>
-      <c r="D153" s="74" t="inlineStr">
+      <c r="D153" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456333076/</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B154" s="73" t="n">
+      <c r="A154" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B154" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -3765,19 +3765,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D154" s="74" t="inlineStr">
+      <c r="D154" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="72" t="inlineStr">
+      <c r="A155" s="75" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B155" s="73" t="n">
+      <c r="B155" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -3785,19 +3785,19 @@
           <t>Territory Business Manager - South Island</t>
         </is>
       </c>
-      <c r="D155" s="74" t="inlineStr">
+      <c r="D155" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456111920/</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="72" t="inlineStr">
+      <c r="A156" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B156" s="73" t="n">
+      <c r="B156" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -3805,19 +3805,19 @@
           <t>Sr Staff Program Manager</t>
         </is>
       </c>
-      <c r="D156" s="74" t="inlineStr">
+      <c r="D156" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448138066/</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B157" s="73" t="n">
+      <c r="A157" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B157" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -3825,19 +3825,19 @@
           <t>Senior Manager- Manufacturing IT Strategic Initiatives and Architecture</t>
         </is>
       </c>
-      <c r="D157" s="74" t="inlineStr">
+      <c r="D157" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4421221561/</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="72" t="inlineStr">
+      <c r="A158" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B158" s="73" t="n">
+      <c r="B158" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -3845,19 +3845,19 @@
           <t>Manager Process Engineering</t>
         </is>
       </c>
-      <c r="D158" s="74" t="inlineStr">
+      <c r="D158" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467096658/</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="72" t="inlineStr">
+      <c r="A159" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B159" s="73" t="n">
+      <c r="B159" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -3865,19 +3865,19 @@
           <t>SW Development Engineer 2 - IOS</t>
         </is>
       </c>
-      <c r="D159" s="74" t="inlineStr">
+      <c r="D159" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465306719/</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="72" t="inlineStr">
+      <c r="A160" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B160" s="73" t="n">
+      <c r="B160" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -3885,19 +3885,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D160" s="74" t="inlineStr">
+      <c r="D160" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B161" s="73" t="n">
+      <c r="A161" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B161" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -3905,19 +3905,19 @@
           <t>District Business Manager - Ohio</t>
         </is>
       </c>
-      <c r="D161" s="74" t="inlineStr">
+      <c r="D161" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458551771/</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="72" t="inlineStr">
+      <c r="A162" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B162" s="73" t="n">
+      <c r="B162" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -3925,19 +3925,19 @@
           <t>Systems Engineer</t>
         </is>
       </c>
-      <c r="D162" s="74" t="inlineStr">
+      <c r="D162" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4375183129/</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="72" t="inlineStr">
+      <c r="A163" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B163" s="73" t="n">
+      <c r="B163" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -3945,19 +3945,19 @@
           <t>Lead Firmware V&amp;V</t>
         </is>
       </c>
-      <c r="D163" s="74" t="inlineStr">
+      <c r="D163" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4402920307/</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="72" t="inlineStr">
+      <c r="A164" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B164" s="73" t="n">
+      <c r="B164" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -3965,19 +3965,19 @@
           <t>Sr. Systems Engineer</t>
         </is>
       </c>
-      <c r="D164" s="74" t="inlineStr">
+      <c r="D164" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461756319/</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B165" s="73" t="n">
+      <c r="A165" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B165" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -3985,19 +3985,19 @@
           <t>Senior Lead Government Affairs Manager - Federal</t>
         </is>
       </c>
-      <c r="D165" s="74" t="inlineStr">
+      <c r="D165" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440825647/</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="72" t="inlineStr">
+      <c r="A166" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B166" s="73" t="n">
+      <c r="B166" s="76" t="n">
         <v>46274</v>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -4005,19 +4005,19 @@
           <t>Staff Database Administrator</t>
         </is>
       </c>
-      <c r="D166" s="74" t="inlineStr">
+      <c r="D166" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456333107/</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B167" s="73" t="n">
+      <c r="A167" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B167" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -4025,19 +4025,19 @@
           <t>Equipment Technician 2 (2A Sunday - Tuesday, every other Saturday from 5:00PM - 5:00AM )</t>
         </is>
       </c>
-      <c r="D167" s="74" t="inlineStr">
+      <c r="D167" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466467687/</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B168" s="73" t="n">
+      <c r="A168" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B168" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -4045,19 +4045,19 @@
           <t>Equipment Technician 2 (2B Wednesday - Friday, every other Saturday from 5:00PM - 5:00AM)</t>
         </is>
       </c>
-      <c r="D168" s="74" t="inlineStr">
+      <c r="D168" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466428944/</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B169" s="73" t="n">
+      <c r="A169" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B169" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -4065,19 +4065,19 @@
           <t>New Business Development Manager, Trade Partnerships (eCommerce)</t>
         </is>
       </c>
-      <c r="D169" s="74" t="inlineStr">
+      <c r="D169" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459020959/</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="72" t="inlineStr">
+      <c r="A170" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B170" s="73" t="n">
+      <c r="B170" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -4085,19 +4085,19 @@
           <t>Sr Firmware V&amp;V</t>
         </is>
       </c>
-      <c r="D170" s="74" t="inlineStr">
+      <c r="D170" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4402292560/</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B171" s="73" t="n">
+      <c r="A171" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B171" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -4105,19 +4105,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D171" s="74" t="inlineStr">
+      <c r="D171" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457557361/</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B172" s="73" t="n">
+      <c r="A172" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B172" s="76" t="n">
         <v>46278</v>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -4125,19 +4125,19 @@
           <t>Staff Enterprise Applications Developer - IBM Maximo</t>
         </is>
       </c>
-      <c r="D172" s="74" t="inlineStr">
+      <c r="D172" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411935028/</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B173" s="73" t="n">
+      <c r="A173" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B173" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -4145,19 +4145,19 @@
           <t>Equipment Technician 4 ( Dobson ) 2B Night Shift: Wed-Fri, every other Sat.</t>
         </is>
       </c>
-      <c r="D173" s="74" t="inlineStr">
+      <c r="D173" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467703315/</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B174" s="73" t="n">
+      <c r="A174" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B174" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -4165,19 +4165,19 @@
           <t>HCP Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D174" s="74" t="inlineStr">
+      <c r="D174" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442796306/</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B175" s="73" t="n">
+      <c r="A175" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B175" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -4185,19 +4185,19 @@
           <t>Sr. Federal Clinical Educator - East</t>
         </is>
       </c>
-      <c r="D175" s="74" t="inlineStr">
+      <c r="D175" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455357586/</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="72" t="inlineStr">
+      <c r="A176" s="75" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B176" s="73" t="n">
+      <c r="B176" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -4205,19 +4205,19 @@
           <t>Sr Legal Counsel, EMEA Privacy</t>
         </is>
       </c>
-      <c r="D176" s="74" t="inlineStr">
+      <c r="D176" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448305175/</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="72" t="inlineStr">
+      <c r="A177" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B177" s="73" t="n">
+      <c r="B177" s="76" t="n">
         <v>46281</v>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -4225,19 +4225,19 @@
           <t>Lead Financial Analyst</t>
         </is>
       </c>
-      <c r="D177" s="74" t="inlineStr">
+      <c r="D177" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467930929/</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="72" t="inlineStr">
+      <c r="A178" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B178" s="73" t="n">
+      <c r="B178" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -4245,19 +4245,19 @@
           <t>SW Development Engineer 2 - Android</t>
         </is>
       </c>
-      <c r="D178" s="74" t="inlineStr">
+      <c r="D178" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464610755/</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="72" t="inlineStr">
+      <c r="A179" s="75" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B179" s="73" t="n">
+      <c r="B179" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -4265,19 +4265,19 @@
           <t>Manager Accounts Payable</t>
         </is>
       </c>
-      <c r="D179" s="74" t="inlineStr">
+      <c r="D179" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467753397/</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B180" s="73" t="n">
+      <c r="A180" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B180" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -4285,19 +4285,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D180" s="74" t="inlineStr">
+      <c r="D180" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="72" t="inlineStr">
+      <c r="A181" s="75" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B181" s="73" t="n">
+      <c r="B181" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -4305,19 +4305,19 @@
           <t>Senior Market Access Manager CEE – Healthcare</t>
         </is>
       </c>
-      <c r="D181" s="74" t="inlineStr">
+      <c r="D181" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467756362/</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="72" t="inlineStr">
+      <c r="A182" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B182" s="73" t="n">
+      <c r="B182" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -4325,19 +4325,19 @@
           <t>Sr Equipment Engineer</t>
         </is>
       </c>
-      <c r="D182" s="74" t="inlineStr">
+      <c r="D182" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467749492/</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B183" s="73" t="n">
+      <c r="A183" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B183" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -4345,19 +4345,19 @@
           <t>Territory Business Manager - Central / SE Alabama</t>
         </is>
       </c>
-      <c r="D183" s="74" t="inlineStr">
+      <c r="D183" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448610622/</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B184" s="73" t="n">
+      <c r="A184" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B184" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -4365,19 +4365,19 @@
           <t>Associate Customer Insights Manager</t>
         </is>
       </c>
-      <c r="D184" s="74" t="inlineStr">
+      <c r="D184" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B185" s="73" t="n">
+      <c r="A185" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B185" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -4385,19 +4385,19 @@
           <t>Sr. Planner Analyst</t>
         </is>
       </c>
-      <c r="D185" s="74" t="inlineStr">
+      <c r="D185" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457555402/</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B186" s="73" t="n">
+      <c r="A186" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B186" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -4405,19 +4405,19 @@
           <t>Mechanical Engineering Manager</t>
         </is>
       </c>
-      <c r="D186" s="74" t="inlineStr">
+      <c r="D186" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447571908/</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B187" s="73" t="n">
+      <c r="A187" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B187" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -4425,19 +4425,19 @@
           <t>Sr. Manager, Data Protection and Insider Risk</t>
         </is>
       </c>
-      <c r="D187" s="74" t="inlineStr">
+      <c r="D187" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467266843/</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="72" t="inlineStr">
+      <c r="A188" s="75" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B188" s="73" t="n">
+      <c r="B188" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -4445,19 +4445,19 @@
           <t>Brand &amp; Portfolio Marketing Lead - DACH (m/w/d)</t>
         </is>
       </c>
-      <c r="D188" s="74" t="inlineStr">
+      <c r="D188" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467076868/</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="72" t="inlineStr">
+      <c r="A189" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B189" s="73" t="n">
+      <c r="B189" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -4465,19 +4465,19 @@
           <t>Manager, SW System &amp; Solution Dev Engineer</t>
         </is>
       </c>
-      <c r="D189" s="74" t="inlineStr">
+      <c r="D189" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B190" s="73" t="n">
+      <c r="A190" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B190" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -4485,19 +4485,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D190" s="74" t="inlineStr">
+      <c r="D190" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466463712/</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B191" s="73" t="n">
+      <c r="A191" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B191" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -4505,19 +4505,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D191" s="74" t="inlineStr">
+      <c r="D191" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B192" s="73" t="n">
+      <c r="A192" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B192" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -4525,19 +4525,19 @@
           <t>Payor Analytics Senior Pricing Analyst</t>
         </is>
       </c>
-      <c r="D192" s="74" t="inlineStr">
+      <c r="D192" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467785422/</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B193" s="73" t="n">
+      <c r="A193" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B193" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -4545,19 +4545,19 @@
           <t>Associate Marketing Manager, Digital Projects</t>
         </is>
       </c>
-      <c r="D193" s="74" t="inlineStr">
+      <c r="D193" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458569116/</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="72" t="inlineStr">
+      <c r="A194" s="75" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B194" s="73" t="n">
+      <c r="B194" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -4565,19 +4565,19 @@
           <t>Sr Automation Engineer</t>
         </is>
       </c>
-      <c r="D194" s="74" t="inlineStr">
+      <c r="D194" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467078747/</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="72" t="inlineStr">
+      <c r="A195" s="75" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B195" s="73" t="n">
+      <c r="B195" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -4585,19 +4585,19 @@
           <t>Technical Support Representative, Dutch Speaker</t>
         </is>
       </c>
-      <c r="D195" s="74" t="inlineStr">
+      <c r="D195" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4364850511/</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B196" s="73" t="n">
+      <c r="A196" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B196" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -4605,19 +4605,19 @@
           <t>Equipment Technician 3 ( 1A Sunday - Tuesday, every other Wednesday from 5:00AM to 5:00PM)</t>
         </is>
       </c>
-      <c r="D196" s="74" t="inlineStr">
+      <c r="D196" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466422908/</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B197" s="73" t="n">
+      <c r="A197" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B197" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -4625,19 +4625,19 @@
           <t>Sr SW Test Development Engineer</t>
         </is>
       </c>
-      <c r="D197" s="74" t="inlineStr">
+      <c r="D197" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457511030/</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="72" t="inlineStr">
+      <c r="A198" s="75" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B198" s="73" t="n">
+      <c r="B198" s="76" t="n">
         <v>46276</v>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -4645,19 +4645,19 @@
           <t>Production Operator - Days - Athenry</t>
         </is>
       </c>
-      <c r="D198" s="74" t="inlineStr">
+      <c r="D198" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457002672/</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="72" t="inlineStr">
+      <c r="A199" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B199" s="73" t="n">
+      <c r="B199" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -4665,19 +4665,19 @@
           <t>SW Test Development Engineer 2</t>
         </is>
       </c>
-      <c r="D199" s="74" t="inlineStr">
+      <c r="D199" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457076040/</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B200" s="73" t="n">
+      <c r="A200" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B200" s="76" t="n">
         <v>46275</v>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -4685,19 +4685,19 @@
           <t>Senior Staff SW Systems Engineer - Mobile Apps</t>
         </is>
       </c>
-      <c r="D200" s="74" t="inlineStr">
+      <c r="D200" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438120759/</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B201" s="73" t="n">
+      <c r="A201" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B201" s="76" t="n">
         <v>46276</v>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -4705,19 +4705,19 @@
           <t>Staff Algorithm Engineer - Emerging Sensing Technologies</t>
         </is>
       </c>
-      <c r="D201" s="74" t="inlineStr">
+      <c r="D201" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447244362/</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B202" s="73" t="n">
+      <c r="A202" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B202" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -4725,19 +4725,19 @@
           <t>QA Inspector 1 (Shift 1A: Days - Sun - Tues every other Wed from 5AM to 5PM )</t>
         </is>
       </c>
-      <c r="D202" s="74" t="inlineStr">
+      <c r="D202" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456781801/</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B203" s="73" t="n">
+      <c r="A203" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B203" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -4745,19 +4745,19 @@
           <t>Sr New Business Development Manager</t>
         </is>
       </c>
-      <c r="D203" s="74" t="inlineStr">
+      <c r="D203" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467430423/</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="72" t="inlineStr">
+      <c r="A204" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B204" s="73" t="n">
+      <c r="B204" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -4765,19 +4765,19 @@
           <t>Sr. SW Test Development Engineer V&amp;V</t>
         </is>
       </c>
-      <c r="D204" s="74" t="inlineStr">
+      <c r="D204" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387839555/</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B205" s="73" t="n">
+      <c r="A205" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B205" s="76" t="n">
         <v>46276</v>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -4785,19 +4785,19 @@
           <t>Staff SW Development Engineer</t>
         </is>
       </c>
-      <c r="D205" s="74" t="inlineStr">
+      <c r="D205" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466372374/</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="72" t="inlineStr">
+      <c r="A206" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B206" s="73" t="n">
+      <c r="B206" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -4805,19 +4805,19 @@
           <t>Sr SW Development Engineer - Android</t>
         </is>
       </c>
-      <c r="D206" s="74" t="inlineStr">
+      <c r="D206" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465019023/</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="72" t="inlineStr">
+      <c r="A207" s="75" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B207" s="73" t="n">
+      <c r="B207" s="76" t="n">
         <v>46279</v>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -4825,19 +4825,19 @@
           <t>Sr SW Development Engineer - IOS</t>
         </is>
       </c>
-      <c r="D207" s="74" t="inlineStr">
+      <c r="D207" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465020025/</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B208" s="73" t="n">
+      <c r="A208" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B208" s="76" t="n">
         <v>46277</v>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -4845,19 +4845,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D208" s="74" t="inlineStr">
+      <c r="D208" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457557359/</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B209" s="73" t="n">
+      <c r="A209" s="75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B209" s="76" t="n">
         <v>46280</v>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -4865,7 +4865,7 @@
           <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
-      <c r="D209" s="74" t="inlineStr">
+      <c r="D209" s="77" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -680,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D214"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3214,120 +3223,120 @@
     <row r="127">
       <c r="A127" s="75" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B127" s="76" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Senior Service Designer, Technical Support</t>
+          <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
         </is>
       </c>
       <c r="D127" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455960251/</t>
+          <t>https://www.linkedin.com/jobs/view/4439394782/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B128" s="76" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Process Development Engineer</t>
+          <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
       <c r="D128" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
+          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="75" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B129" s="76" t="n">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Supervisor Manufacturing</t>
+          <t>Sr. Financial Analyst</t>
         </is>
       </c>
       <c r="D129" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4428861138/</t>
+          <t>https://www.linkedin.com/jobs/view/4421230278/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B130" s="76" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Staff Database Administrator</t>
+          <t>Sr Cybersecurity Analyst</t>
         </is>
       </c>
       <c r="D130" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
+          <t>https://www.linkedin.com/jobs/view/4439085443/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B131" s="76" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Payroll Analyst (ANZ)</t>
+          <t>SW Development Engineer 2</t>
         </is>
       </c>
       <c r="D131" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
+          <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B132" s="76" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>SW Test Development Engineer 1</t>
+          <t>Trade Compliance Analyst</t>
         </is>
       </c>
       <c r="D132" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
+          <t>https://www.linkedin.com/jobs/view/4467033928/</t>
         </is>
       </c>
     </row>
@@ -3338,216 +3347,216 @@
         </is>
       </c>
       <c r="B133" s="76" t="n">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Sr Workplace Solutions Analyst</t>
+          <t>Sr Manufacturing Engineer</t>
         </is>
       </c>
       <c r="D133" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
+          <t>https://www.linkedin.com/jobs/view/4447583072/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B134" s="76" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Staff SW Development Engineer</t>
+          <t>Staff Vendor Management Analyst</t>
         </is>
       </c>
       <c r="D134" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
+          <t>https://www.linkedin.com/jobs/view/4458212554/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B135" s="76" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Director, Business Program Management Office</t>
+          <t>Staff Equipment Engineer</t>
         </is>
       </c>
       <c r="D135" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
+          <t>https://www.linkedin.com/jobs/view/4458218533/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="75" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B136" s="76" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Engineering Technician 4</t>
+          <t>APAC Product Manager - OTC/Consumer Health</t>
         </is>
       </c>
       <c r="D136" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
+          <t>https://www.linkedin.com/jobs/view/4422693615/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B137" s="76" t="n">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Systems Design &amp; Test Engineer 2</t>
+          <t>Supervisor Technical Support - Manila</t>
         </is>
       </c>
       <c r="D137" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
+          <t>https://www.linkedin.com/jobs/view/4417742237/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B138" s="76" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
+          <t>Staff Desktop Support Engineer</t>
         </is>
       </c>
       <c r="D138" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4439394782/</t>
+          <t>https://www.linkedin.com/jobs/view/4398315987/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B139" s="76" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>SW Development Engineer 1 - Android</t>
+          <t>Director HW Design Quality Engineering - New Product Introductions</t>
         </is>
       </c>
       <c r="D139" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
+          <t>https://www.linkedin.com/jobs/view/4456789792/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="75" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B140" s="76" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Sr. Financial Analyst</t>
+          <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
       <c r="D140" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4421230278/</t>
+          <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B141" s="76" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Sr Cybersecurity Analyst</t>
+          <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
         </is>
       </c>
       <c r="D141" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4439085443/</t>
+          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B142" s="76" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>SW Development Engineer 2</t>
+          <t>Hardware Engineer 2</t>
         </is>
       </c>
       <c r="D142" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4460357219/</t>
+          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="75" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B143" s="76" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Trade Compliance Analyst</t>
+          <t>Sr Staff Program Manager</t>
         </is>
       </c>
       <c r="D143" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467033928/</t>
+          <t>https://www.linkedin.com/jobs/view/4448138066/</t>
         </is>
       </c>
     </row>
@@ -3558,16 +3567,16 @@
         </is>
       </c>
       <c r="B144" s="76" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Sr Manufacturing Engineer</t>
+          <t>Senior Manager- Manufacturing IT Strategic Initiatives and Architecture</t>
         </is>
       </c>
       <c r="D144" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4447583072/</t>
+          <t>https://www.linkedin.com/jobs/view/4421221561/</t>
         </is>
       </c>
     </row>
@@ -3582,19 +3591,19 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Staff Vendor Management Analyst</t>
+          <t>Manager Process Engineering</t>
         </is>
       </c>
       <c r="D145" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4458212554/</t>
+          <t>https://www.linkedin.com/jobs/view/4467096658/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="75" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B146" s="76" t="n">
@@ -3602,19 +3611,19 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Staff Equipment Engineer</t>
+          <t>SW Development Engineer 2 - IOS</t>
         </is>
       </c>
       <c r="D146" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4458218533/</t>
+          <t>https://www.linkedin.com/jobs/view/4465306719/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="75" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B147" s="76" t="n">
@@ -3622,39 +3631,39 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>APAC Product Manager - OTC/Consumer Health</t>
+          <t>Staff Systems Engineer</t>
         </is>
       </c>
       <c r="D147" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4422693615/</t>
+          <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B148" s="76" t="n">
-        <v>46278</v>
+        <v>46275</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Supervisor Technical Support - Manila</t>
+          <t>District Business Manager - Ohio</t>
         </is>
       </c>
       <c r="D148" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4417742237/</t>
+          <t>https://www.linkedin.com/jobs/view/4458551771/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="75" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B149" s="76" t="n">
@@ -3662,32 +3671,32 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Staff Desktop Support Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D149" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4398315987/</t>
+          <t>https://www.linkedin.com/jobs/view/4375183129/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B150" s="76" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Director HW Design Quality Engineering - New Product Introductions</t>
+          <t>Lead Firmware V&amp;V</t>
         </is>
       </c>
       <c r="D150" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456789792/</t>
+          <t>https://www.linkedin.com/jobs/view/4402920307/</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3711,12 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Manager SW Test Development Engineering</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="D151" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4281993770/</t>
+          <t>https://www.linkedin.com/jobs/view/4461756319/</t>
         </is>
       </c>
     </row>
@@ -3722,32 +3731,32 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
+          <t>Senior Lead Government Affairs Manager - Federal</t>
         </is>
       </c>
       <c r="D152" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
+          <t>https://www.linkedin.com/jobs/view/4440825647/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B153" s="76" t="n">
-        <v>46274</v>
+        <v>46277</v>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Supervisor, Applications Support</t>
+          <t>Equipment Technician 2 (2A Sunday - Tuesday, every other Saturday from 5:00PM - 5:00AM )</t>
         </is>
       </c>
       <c r="D153" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456333076/</t>
+          <t>https://www.linkedin.com/jobs/view/4466467687/</t>
         </is>
       </c>
     </row>
@@ -3758,56 +3767,56 @@
         </is>
       </c>
       <c r="B154" s="76" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Hardware Engineer 2</t>
+          <t>Equipment Technician 2 (2B Wednesday - Friday, every other Saturday from 5:00PM - 5:00AM)</t>
         </is>
       </c>
       <c r="D154" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
+          <t>https://www.linkedin.com/jobs/view/4466428944/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="75" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B155" s="76" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Territory Business Manager - South Island</t>
+          <t>New Business Development Manager, Trade Partnerships (eCommerce)</t>
         </is>
       </c>
       <c r="D155" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456111920/</t>
+          <t>https://www.linkedin.com/jobs/view/4459020959/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B156" s="76" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Sr Staff Program Manager</t>
+          <t>Sr Firmware V&amp;V</t>
         </is>
       </c>
       <c r="D156" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4448138066/</t>
+          <t>https://www.linkedin.com/jobs/view/4402292560/</t>
         </is>
       </c>
     </row>
@@ -3818,76 +3827,76 @@
         </is>
       </c>
       <c r="B157" s="76" t="n">
-        <v>46279</v>
+        <v>46277</v>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Senior Manager- Manufacturing IT Strategic Initiatives and Architecture</t>
+          <t>Sr Software QA Engineer</t>
         </is>
       </c>
       <c r="D157" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4421221561/</t>
+          <t>https://www.linkedin.com/jobs/view/4457557361/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="75" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B158" s="76" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Manager Process Engineering</t>
+          <t>Staff Enterprise Applications Developer - IBM Maximo</t>
         </is>
       </c>
       <c r="D158" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467096658/</t>
+          <t>https://www.linkedin.com/jobs/view/4411935028/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B159" s="76" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>SW Development Engineer 2 - IOS</t>
+          <t>Equipment Technician 4 ( Dobson ) 2B Night Shift: Wed-Fri, every other Sat.</t>
         </is>
       </c>
       <c r="D159" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4465306719/</t>
+          <t>https://www.linkedin.com/jobs/view/4467703315/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B160" s="76" t="n">
-        <v>46279</v>
+        <v>46277</v>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Staff Systems Engineer</t>
+          <t>HCP Marketing Manager (Stelo)</t>
         </is>
       </c>
       <c r="D160" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461770016/</t>
+          <t>https://www.linkedin.com/jobs/view/4442796306/</t>
         </is>
       </c>
     </row>
@@ -3902,52 +3911,52 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>District Business Manager - Ohio</t>
+          <t>Sr. Federal Clinical Educator - East</t>
         </is>
       </c>
       <c r="D161" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4458551771/</t>
+          <t>https://www.linkedin.com/jobs/view/4455357586/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B162" s="76" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr Legal Counsel, EMEA Privacy</t>
         </is>
       </c>
       <c r="D162" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4375183129/</t>
+          <t>https://www.linkedin.com/jobs/view/4448305175/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B163" s="76" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Lead Firmware V&amp;V</t>
+          <t>Lead Financial Analyst</t>
         </is>
       </c>
       <c r="D163" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4402920307/</t>
+          <t>https://www.linkedin.com/jobs/view/4467930929/</t>
         </is>
       </c>
     </row>
@@ -3962,92 +3971,92 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>SW Development Engineer 2 - Android</t>
         </is>
       </c>
       <c r="D164" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461756319/</t>
+          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B165" s="76" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Senior Lead Government Affairs Manager - Federal</t>
+          <t>Manager Accounts Payable</t>
         </is>
       </c>
       <c r="D165" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4440825647/</t>
+          <t>https://www.linkedin.com/jobs/view/4467753397/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B166" s="76" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Staff Database Administrator</t>
+          <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
       <c r="D166" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4456333107/</t>
+          <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B167" s="76" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Equipment Technician 2 (2A Sunday - Tuesday, every other Saturday from 5:00PM - 5:00AM )</t>
+          <t>Senior Market Access Manager CEE – Healthcare</t>
         </is>
       </c>
       <c r="D167" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4466467687/</t>
+          <t>https://www.linkedin.com/jobs/view/4467756362/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B168" s="76" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Equipment Technician 2 (2B Wednesday - Friday, every other Saturday from 5:00PM - 5:00AM)</t>
+          <t>Sr Equipment Engineer</t>
         </is>
       </c>
       <c r="D168" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4466428944/</t>
+          <t>https://www.linkedin.com/jobs/view/4467749492/</t>
         </is>
       </c>
     </row>
@@ -4058,36 +4067,36 @@
         </is>
       </c>
       <c r="B169" s="76" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>New Business Development Manager, Trade Partnerships (eCommerce)</t>
+          <t>Territory Business Manager - Central / SE Alabama</t>
         </is>
       </c>
       <c r="D169" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4459020959/</t>
+          <t>https://www.linkedin.com/jobs/view/4448610622/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B170" s="76" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Sr Firmware V&amp;V</t>
+          <t>Associate Customer Insights Manager</t>
         </is>
       </c>
       <c r="D170" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4402292560/</t>
+          <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
@@ -4102,12 +4111,12 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Sr Software QA Engineer</t>
+          <t>Sr. Planner Analyst</t>
         </is>
       </c>
       <c r="D171" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4457557361/</t>
+          <t>https://www.linkedin.com/jobs/view/4457555402/</t>
         </is>
       </c>
     </row>
@@ -4118,16 +4127,16 @@
         </is>
       </c>
       <c r="B172" s="76" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Staff Enterprise Applications Developer - IBM Maximo</t>
+          <t>Mechanical Engineering Manager</t>
         </is>
       </c>
       <c r="D172" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4411935028/</t>
+          <t>https://www.linkedin.com/jobs/view/4447571908/</t>
         </is>
       </c>
     </row>
@@ -4138,123 +4147,123 @@
         </is>
       </c>
       <c r="B173" s="76" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Equipment Technician 4 ( Dobson ) 2B Night Shift: Wed-Fri, every other Sat.</t>
+          <t>Sr. Manager, Data Protection and Insider Risk</t>
         </is>
       </c>
       <c r="D173" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467703315/</t>
+          <t>https://www.linkedin.com/jobs/view/4467266843/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B174" s="76" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>HCP Marketing Manager (Stelo)</t>
+          <t>Brand &amp; Portfolio Marketing Lead - DACH (m/w/d)</t>
         </is>
       </c>
       <c r="D174" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4442796306/</t>
+          <t>https://www.linkedin.com/jobs/view/4467076868/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B175" s="76" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Sr. Federal Clinical Educator - East</t>
+          <t>Manager, SW System &amp; Solution Dev Engineer</t>
         </is>
       </c>
       <c r="D175" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455357586/</t>
+          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="75" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B176" s="76" t="n">
-        <v>46280</v>
+        <v>46277</v>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Sr Legal Counsel, EMEA Privacy</t>
+          <t>Process Development Engineer 2</t>
         </is>
       </c>
       <c r="D176" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4448305175/</t>
+          <t>https://www.linkedin.com/jobs/view/4466463712/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B177" s="76" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Lead Financial Analyst</t>
+          <t>Sr Software QA Engineer</t>
         </is>
       </c>
       <c r="D177" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467930929/</t>
+          <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B178" s="76" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>SW Development Engineer 2 - Android</t>
+          <t>Payor Analytics Senior Pricing Analyst</t>
         </is>
       </c>
       <c r="D178" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
+          <t>https://www.linkedin.com/jobs/view/4467785422/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="75" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B179" s="76" t="n">
@@ -4262,59 +4271,59 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Manager Accounts Payable</t>
+          <t>Associate Marketing Manager, Digital Projects</t>
         </is>
       </c>
       <c r="D179" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467753397/</t>
+          <t>https://www.linkedin.com/jobs/view/4458569116/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B180" s="76" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Staff Business Financial Analyst - IT Infrastructure</t>
+          <t>Sr Automation Engineer</t>
         </is>
       </c>
       <c r="D180" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461264820/</t>
+          <t>https://www.linkedin.com/jobs/view/4467078747/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="75" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B181" s="76" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Senior Market Access Manager CEE – Healthcare</t>
+          <t>Technical Support Representative, Dutch Speaker</t>
         </is>
       </c>
       <c r="D181" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467756362/</t>
+          <t>https://www.linkedin.com/jobs/view/4364850511/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="75" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B182" s="76" t="n">
@@ -4322,12 +4331,12 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Sr Equipment Engineer</t>
+          <t>Equipment Technician 3 ( 1A Sunday - Tuesday, every other Wednesday from 5:00AM to 5:00PM)</t>
         </is>
       </c>
       <c r="D182" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467749492/</t>
+          <t>https://www.linkedin.com/jobs/view/4466422908/</t>
         </is>
       </c>
     </row>
@@ -4338,56 +4347,56 @@
         </is>
       </c>
       <c r="B183" s="76" t="n">
-        <v>46280</v>
+        <v>46277</v>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Territory Business Manager - Central / SE Alabama</t>
+          <t>Sr SW Test Development Engineer</t>
         </is>
       </c>
       <c r="D183" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4448610622/</t>
+          <t>https://www.linkedin.com/jobs/view/4457511030/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B184" s="76" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Associate Customer Insights Manager</t>
+          <t>Production Operator - Days - Athenry</t>
         </is>
       </c>
       <c r="D184" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4434083415/</t>
+          <t>https://www.linkedin.com/jobs/view/4457002672/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B185" s="76" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Sr. Planner Analyst</t>
+          <t>SW Test Development Engineer 2</t>
         </is>
       </c>
       <c r="D185" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4457555402/</t>
+          <t>https://www.linkedin.com/jobs/view/4457076040/</t>
         </is>
       </c>
     </row>
@@ -4398,16 +4407,16 @@
         </is>
       </c>
       <c r="B186" s="76" t="n">
-        <v>46277</v>
+        <v>46275</v>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Manager</t>
+          <t>Senior Staff SW Systems Engineer - Mobile Apps</t>
         </is>
       </c>
       <c r="D186" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4447571908/</t>
+          <t>https://www.linkedin.com/jobs/view/4438120759/</t>
         </is>
       </c>
     </row>
@@ -4418,76 +4427,76 @@
         </is>
       </c>
       <c r="B187" s="76" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Sr. Manager, Data Protection and Insider Risk</t>
+          <t>Staff Algorithm Engineer - Emerging Sensing Technologies</t>
         </is>
       </c>
       <c r="D187" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467266843/</t>
+          <t>https://www.linkedin.com/jobs/view/4447244362/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B188" s="76" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Brand &amp; Portfolio Marketing Lead - DACH (m/w/d)</t>
+          <t>QA Inspector 1 (Shift 1A: Days - Sun - Tues every other Wed from 5AM to 5PM )</t>
         </is>
       </c>
       <c r="D188" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467076868/</t>
+          <t>https://www.linkedin.com/jobs/view/4456781801/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B189" s="76" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Manager, SW System &amp; Solution Dev Engineer</t>
+          <t>Sr New Business Development Manager</t>
         </is>
       </c>
       <c r="D189" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
+          <t>https://www.linkedin.com/jobs/view/4467430423/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B190" s="76" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Process Development Engineer 2</t>
+          <t>Sr. SW Test Development Engineer V&amp;V</t>
         </is>
       </c>
       <c r="D190" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4466463712/</t>
+          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
         </is>
       </c>
     </row>
@@ -4498,116 +4507,116 @@
         </is>
       </c>
       <c r="B191" s="76" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Sr Software QA Engineer</t>
+          <t>Staff SW Development Engineer</t>
         </is>
       </c>
       <c r="D191" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4453636185/</t>
+          <t>https://www.linkedin.com/jobs/view/4466372374/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B192" s="76" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Payor Analytics Senior Pricing Analyst</t>
+          <t>Sr SW Development Engineer - Android</t>
         </is>
       </c>
       <c r="D192" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467785422/</t>
+          <t>https://www.linkedin.com/jobs/view/4465019023/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B193" s="76" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Associate Marketing Manager, Digital Projects</t>
+          <t>Sr SW Development Engineer - IOS</t>
         </is>
       </c>
       <c r="D193" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4458569116/</t>
+          <t>https://www.linkedin.com/jobs/view/4465020025/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="75" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B194" s="76" t="n">
-        <v>46279</v>
+        <v>46277</v>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Sr Automation Engineer</t>
+          <t>Sr Process Engineer</t>
         </is>
       </c>
       <c r="D194" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467078747/</t>
+          <t>https://www.linkedin.com/jobs/view/4457557359/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="75" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B195" s="76" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Technical Support Representative, Dutch Speaker</t>
+          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
       <c r="D195" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4364850511/</t>
+          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B196" s="76" t="n">
-        <v>46280</v>
+        <v>46277</v>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Equipment Technician 3 ( 1A Sunday - Tuesday, every other Wednesday from 5:00AM to 5:00PM)</t>
+          <t>Training and Quality Manager (Customer Service)</t>
         </is>
       </c>
       <c r="D196" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4466422908/</t>
+          <t>https://www.linkedin.com/jobs/view/4439090281/</t>
         </is>
       </c>
     </row>
@@ -4618,36 +4627,36 @@
         </is>
       </c>
       <c r="B197" s="76" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Sr SW Test Development Engineer</t>
+          <t>Continuous Improvement Analyst (Green Belt)</t>
         </is>
       </c>
       <c r="D197" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4457511030/</t>
+          <t>https://www.linkedin.com/jobs/view/4458553387/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="75" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B198" s="76" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Production Operator - Days - Athenry</t>
+          <t>ECAD Technician 2</t>
         </is>
       </c>
       <c r="D198" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4457002672/</t>
+          <t>https://www.linkedin.com/jobs/view/4456709938/</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4671,12 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>SW Test Development Engineer 2</t>
+          <t>Sr Fimware Engineer</t>
         </is>
       </c>
       <c r="D199" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4457076040/</t>
+          <t>https://www.linkedin.com/jobs/view/4366307571/</t>
         </is>
       </c>
     </row>
@@ -4678,301 +4687,221 @@
         </is>
       </c>
       <c r="B200" s="76" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff SW Systems Engineer - Mobile Apps</t>
+          <t>QA Inspector 1 ( RDC ) 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
       <c r="D200" s="77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4438120759/</t>
+          <t>https://www.linkedin.com/jobs/view/4459645247/</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="75" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B201" s="76" t="n">
-        <v>46276</v>
+      <c r="A201" s="78" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B201" s="79" t="n">
+        <v>46279</v>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Staff Algorithm Engineer - Emerging Sensing Technologies</t>
-        </is>
-      </c>
-      <c r="D201" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4447244362/</t>
+          <t>SW Test Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="D201" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="75" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B202" s="76" t="n">
+      <c r="A202" s="78" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B202" s="79" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Security</t>
+        </is>
+      </c>
+      <c r="D202" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448891179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="78" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B203" s="79" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer 2</t>
+        </is>
+      </c>
+      <c r="D203" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461767088/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B204" s="79" t="n">
         <v>46280</v>
       </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>QA Inspector 1 (Shift 1A: Days - Sun - Tues every other Wed from 5AM to 5PM )</t>
-        </is>
-      </c>
-      <c r="D202" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456781801/</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="75" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B203" s="76" t="n">
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager - Sensor Automation</t>
+        </is>
+      </c>
+      <c r="D204" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461540445/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="78" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B205" s="79" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>Lead Business Process Analyst - SCM</t>
+        </is>
+      </c>
+      <c r="D205" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467935835/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B206" s="79" t="n">
         <v>46280</v>
       </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>Sr New Business Development Manager</t>
-        </is>
-      </c>
-      <c r="D203" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4467430423/</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="75" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B204" s="76" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>Sr. SW Test Development Engineer V&amp;V</t>
-        </is>
-      </c>
-      <c r="D204" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="75" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B205" s="76" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>Staff SW Development Engineer</t>
-        </is>
-      </c>
-      <c r="D205" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4466372374/</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="75" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B206" s="76" t="n">
-        <v>46279</v>
-      </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Sr SW Development Engineer - Android</t>
-        </is>
-      </c>
-      <c r="D206" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465019023/</t>
+          <t>Sr Hardware Engineer</t>
+        </is>
+      </c>
+      <c r="D206" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4409130436/</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="75" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B207" s="76" t="n">
-        <v>46279</v>
+      <c r="A207" s="78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B207" s="79" t="n">
+        <v>46282</v>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Sr SW Development Engineer - IOS</t>
-        </is>
-      </c>
-      <c r="D207" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465020025/</t>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="D207" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467190296/</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="75" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B208" s="76" t="n">
-        <v>46277</v>
+      <c r="A208" s="78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B208" s="79" t="n">
+        <v>46281</v>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Sr Process Engineer</t>
-        </is>
-      </c>
-      <c r="D208" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4457557359/</t>
+          <t>Lab Technician 2 - Monday through Friday, 7:00AM to 3:30PM</t>
+        </is>
+      </c>
+      <c r="D208" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467923935/</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="75" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B209" s="76" t="n">
+      <c r="A209" s="78" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B209" s="79" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>Lead Applications Developer (Oracle Fusion SCM and Procurement)</t>
+        </is>
+      </c>
+      <c r="D209" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448836213/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B210" s="79" t="n">
         <v>46280</v>
       </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
-        </is>
-      </c>
-      <c r="D209" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="75" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B210" s="76" t="n">
-        <v>46277</v>
-      </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Training and Quality Manager (Customer Service)</t>
-        </is>
-      </c>
-      <c r="D210" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4439090281/</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="75" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B211" s="76" t="n">
-        <v>46280</v>
-      </c>
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>Continuous Improvement Analyst (Green Belt)</t>
-        </is>
-      </c>
-      <c r="D211" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4458553387/</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="75" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B212" s="76" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>ECAD Technician 2</t>
-        </is>
-      </c>
-      <c r="D212" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456709938/</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="75" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B213" s="76" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>Sr Fimware Engineer</t>
-        </is>
-      </c>
-      <c r="D213" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4366307571/</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="75" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B214" s="76" t="n">
-        <v>46280</v>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>QA Inspector 1 ( RDC ) 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
-        </is>
-      </c>
-      <c r="D214" s="77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4459645247/</t>
+          <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
+        </is>
+      </c>
+      <c r="D210" s="80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D214"/>
+  <autoFilter ref="A1:D210"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -5183,10 +5112,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId213"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -723,120 +732,120 @@
     <row r="2">
       <c r="A2" s="78" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B2" s="79" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Lead Financial Analyst</t>
+          <t>Senior Technical Project Manager</t>
         </is>
       </c>
       <c r="D2" s="80" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4467930929/</t>
+          <t>https://www.linkedin.com/jobs/view/4467190296/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="78" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B3" s="79" t="n">
-        <v>46281</v>
+      <c r="A3" s="81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B3" s="82" t="n">
+        <v>46283</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Supervisor Security</t>
-        </is>
-      </c>
-      <c r="D3" s="80" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4448891179/</t>
+          <t>Associate Facilities Engineer</t>
+        </is>
+      </c>
+      <c r="D3" s="83" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468859683/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="78" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B4" s="79" t="n">
-        <v>46281</v>
+      <c r="A4" s="81" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="n">
+        <v>46283</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Lead Business Process Analyst - SCM</t>
-        </is>
-      </c>
-      <c r="D4" s="80" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4467935835/</t>
+          <t>Sr Supervisor Manufacturing</t>
+        </is>
+      </c>
+      <c r="D4" s="83" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468856812/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n">
-        <v>46282</v>
+      <c r="B5" s="82" t="n">
+        <v>46283</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Senior Technical Project Manager</t>
-        </is>
-      </c>
-      <c r="D5" s="80" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4467190296/</t>
+          <t>Employee Relations &amp; Performance Management Program Specialist</t>
+        </is>
+      </c>
+      <c r="D5" s="83" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468861635/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B6" s="79" t="n">
-        <v>46281</v>
+      <c r="B6" s="82" t="n">
+        <v>46283</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Lab Technician 2 - Monday through Friday, 7:00AM to 3:30PM</t>
-        </is>
-      </c>
-      <c r="D6" s="80" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4467923935/</t>
+          <t>Product Manager, Consumer Mobile App</t>
+        </is>
+      </c>
+      <c r="D6" s="83" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468867601/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B7" s="79" t="n">
-        <v>46281</v>
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="n">
+        <v>46283</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Lead Applications Developer (Oracle Fusion SCM and Procurement)</t>
-        </is>
-      </c>
-      <c r="D7" s="80" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4448836213/</t>
+          <t>Inside Sales Representative 3</t>
+        </is>
+      </c>
+      <c r="D7" s="83" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468863641/</t>
         </is>
       </c>
     </row>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -698,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -730,12 +739,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="78" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B2" s="79" t="n">
+      <c r="A2" s="81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B2" s="82" t="n">
         <v>46282</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -743,7 +752,7 @@
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="D2" s="80" t="inlineStr">
+      <c r="D2" s="83" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467190296/</t>
         </is>
@@ -849,8 +858,1488 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B8" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 1 - Android</t>
+        </is>
+      </c>
+      <c r="D8" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="84" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B9" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Sr Legal Counsel, EMEA Privacy</t>
+        </is>
+      </c>
+      <c r="D9" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448305175/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B10" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Sr Cybersecurity Analyst</t>
+        </is>
+      </c>
+      <c r="D10" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439085443/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="84" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B11" s="85" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="D11" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441484584/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="84" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B12" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D12" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461765131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="84" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B13" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D13" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464354416/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="84" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B14" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D14" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459303523/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B15" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="D15" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="84" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B16" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D16" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464339507/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Sr Regulatory Affairs Specialist</t>
+        </is>
+      </c>
+      <c r="D17" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448601784/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B18" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2 - Android</t>
+        </is>
+      </c>
+      <c r="D18" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="84" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B19" s="85" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="D19" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468819369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="84" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B20" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Trade Compliance Analyst</t>
+        </is>
+      </c>
+      <c r="D20" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467033928/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Manager Quality Compliance</t>
+        </is>
+      </c>
+      <c r="D21" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464662874/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="84" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B22" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Manager Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D22" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467753397/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B23" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D23" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4460357219/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B24" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Staff Business Financial Analyst - IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="D24" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461264820/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B25" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D25" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4257269392/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B26" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D26" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453360435/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="84" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B27" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>APAC Product Manager - OTC/Consumer Health</t>
+        </is>
+      </c>
+      <c r="D27" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4422693615/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="84" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B28" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Senior Market Access Manager CEE – Healthcare</t>
+        </is>
+      </c>
+      <c r="D28" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467756362/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="84" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B29" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Staff Equipment Engineer</t>
+        </is>
+      </c>
+      <c r="D29" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458218533/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="84" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B30" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Sr Equipment Engineer</t>
+        </is>
+      </c>
+      <c r="D30" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467749492/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="84" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B31" s="85" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Technical Support - Manila</t>
+        </is>
+      </c>
+      <c r="D31" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417742237/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manufacturing Engineer</t>
+        </is>
+      </c>
+      <c r="D32" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447583072/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Sr QA Engineer</t>
+        </is>
+      </c>
+      <c r="D33" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465859501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="84" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B34" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Customer Advocacy</t>
+        </is>
+      </c>
+      <c r="D34" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454022788/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="84" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B35" s="85" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="D35" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449638538/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="84" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B36" s="85" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D36" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459651196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="84" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B37" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Staff Vendor Management Analyst</t>
+        </is>
+      </c>
+      <c r="D37" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458212554/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B38" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Manager SW Test Development Engineering</t>
+        </is>
+      </c>
+      <c r="D38" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4281993770/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="84" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B39" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Staff Desktop Support Engineer</t>
+        </is>
+      </c>
+      <c r="D39" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4398315987/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="84" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B40" s="85" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer 2</t>
+        </is>
+      </c>
+      <c r="D40" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459826448/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Document Control and Training Specialist 1 ( Monday to Friday, 8:00 AM - 5:00 PM )</t>
+        </is>
+      </c>
+      <c r="D41" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B42" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Staff SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D42" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="85" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Planner Analyst</t>
+        </is>
+      </c>
+      <c r="D43" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457555402/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B44" s="85" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering Manager</t>
+        </is>
+      </c>
+      <c r="D44" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447571908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="84" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B45" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Manufacturing</t>
+        </is>
+      </c>
+      <c r="D45" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448832646/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="85" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Sr Process Engineer</t>
+        </is>
+      </c>
+      <c r="D46" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448615086/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B47" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Desktop Support Specialist 2</t>
+        </is>
+      </c>
+      <c r="D47" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466386358/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Data Protection and Insider Risk</t>
+        </is>
+      </c>
+      <c r="D48" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467266843/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="84" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B49" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Brand &amp; Portfolio Marketing Lead - DACH (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D49" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467076868/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B50" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Manager, SW System &amp; Solution Dev Engineer</t>
+        </is>
+      </c>
+      <c r="D50" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B51" s="85" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Territory Business Manager - Columbus, GA</t>
+        </is>
+      </c>
+      <c r="D51" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449902344/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="85" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Process Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D52" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466463712/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="84" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B53" s="85" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Sr DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="D53" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4460303379/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Sr Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="D54" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453636185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B55" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Continuous Improvement Analyst (Green Belt)</t>
+        </is>
+      </c>
+      <c r="D55" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458553387/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="84" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B56" s="85" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D56" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459369335/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B57" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Hardware Engineer 2</t>
+        </is>
+      </c>
+      <c r="D57" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B58" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager, Software Systems &amp; Solutions</t>
+        </is>
+      </c>
+      <c r="D58" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4218028502/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="84" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B59" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>QC Inspector 1</t>
+        </is>
+      </c>
+      <c r="D59" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458226419/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B60" s="85" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Hardware Engineer 2</t>
+        </is>
+      </c>
+      <c r="D60" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468302054/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="84" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B61" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Senior Market Access Manager CEE – Healthcare</t>
+        </is>
+      </c>
+      <c r="D61" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467764326/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B62" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Staff Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D62" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461770016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Payor Analytics Senior Pricing Analyst</t>
+        </is>
+      </c>
+      <c r="D63" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467785422/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="84" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B64" s="85" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Dexcom are Hiring Technicians for Front End Night Shift</t>
+        </is>
+      </c>
+      <c r="D64" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4431256111/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="84" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B65" s="85" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Sr DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="D65" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4460300749/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B66" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Associate Marketing Manager, Digital Projects</t>
+        </is>
+      </c>
+      <c r="D66" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458569116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B67" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D67" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461756319/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="84" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B68" s="85" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Castilla y León</t>
+        </is>
+      </c>
+      <c r="D68" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458922088/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B69" s="85" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Sr SW Design Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D69" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450008915/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="84" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B70" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Sr Automation Engineer</t>
+        </is>
+      </c>
+      <c r="D70" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467078747/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B71" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>ECAD Technician 2</t>
+        </is>
+      </c>
+      <c r="D71" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456709938/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B72" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Staff SRE SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D72" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387683946/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="84" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B73" s="85" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing Technician 3 (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D73" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459362978/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B74" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
+        </is>
+      </c>
+      <c r="D74" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455128356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="84" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B75" s="85" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Lead Applications Developer (Oracle Fusion SCM and Procurement)</t>
+        </is>
+      </c>
+      <c r="D75" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448836213/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B76" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Sr Technical Writer</t>
+        </is>
+      </c>
+      <c r="D76" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465024024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B77" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D77" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457076040/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="84" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B78" s="85" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Senior Research Scientist (AI)</t>
+        </is>
+      </c>
+      <c r="D78" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449121123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B79" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 1 (Shift 1A: Days - Sun - Tues every other Wed from 5AM to 5PM )</t>
+        </is>
+      </c>
+      <c r="D79" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456781801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B80" s="85" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
+        </is>
+      </c>
+      <c r="D80" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455289751/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B81" s="85" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Sr. SW Test Development Engineer V&amp;V</t>
+        </is>
+      </c>
+      <c r="D81" s="86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D81"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -858,6 +2347,80 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -716,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -748,12 +757,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="84" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B2" s="85" t="n">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B2" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -761,19 +770,19 @@
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="D2" s="86" t="inlineStr">
+      <c r="D2" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4467190296/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B3" s="85" t="n">
+      <c r="A3" s="87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -781,19 +790,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D3" s="86" t="inlineStr">
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4468859683/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="85" t="n">
+      <c r="B4" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -801,19 +810,19 @@
           <t>Sr Supervisor Manufacturing</t>
         </is>
       </c>
-      <c r="D4" s="86" t="inlineStr">
+      <c r="D4" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4468856812/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B5" s="85" t="n">
+      <c r="A5" s="87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B5" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -821,19 +830,19 @@
           <t>Employee Relations &amp; Performance Management Program Specialist</t>
         </is>
       </c>
-      <c r="D5" s="86" t="inlineStr">
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4468861635/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="84" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B6" s="85" t="n">
+      <c r="A6" s="87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B6" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -841,19 +850,19 @@
           <t>Product Manager, Consumer Mobile App</t>
         </is>
       </c>
-      <c r="D6" s="86" t="inlineStr">
+      <c r="D6" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4468867601/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="84" t="inlineStr">
+      <c r="A7" s="87" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B7" s="85" t="n">
+      <c r="B7" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -861,19 +870,19 @@
           <t>Inside Sales Representative 3</t>
         </is>
       </c>
-      <c r="D7" s="86" t="inlineStr">
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4468863641/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="84" t="inlineStr">
+      <c r="A8" s="87" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="85" t="n">
+      <c r="B8" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -881,19 +890,19 @@
           <t>Business Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D8" s="86" t="inlineStr">
+      <c r="D8" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441484584/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="84" t="inlineStr">
+      <c r="A9" s="87" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="85" t="n">
+      <c r="B9" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -901,19 +910,19 @@
           <t>Accountant</t>
         </is>
       </c>
-      <c r="D9" s="86" t="inlineStr">
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4468819369/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="84" t="inlineStr">
+      <c r="A10" s="87" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B10" s="85" t="n">
+      <c r="B10" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -921,19 +930,19 @@
           <t>Senior Project Manager</t>
         </is>
       </c>
-      <c r="D10" s="86" t="inlineStr">
+      <c r="D10" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449638538/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="inlineStr">
+      <c r="A11" s="87" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B11" s="85" t="n">
+      <c r="B11" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -941,19 +950,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D11" s="86" t="inlineStr">
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459651196/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="84" t="inlineStr">
+      <c r="A12" s="87" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B12" s="85" t="n">
+      <c r="B12" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -961,19 +970,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D12" s="86" t="inlineStr">
+      <c r="D12" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459826448/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="84" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="85" t="n">
+      <c r="A13" s="87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -981,19 +990,19 @@
           <t>Territory Business Manager - Columbus, GA</t>
         </is>
       </c>
-      <c r="D13" s="86" t="inlineStr">
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449902344/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="84" t="inlineStr">
+      <c r="A14" s="87" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B14" s="85" t="n">
+      <c r="B14" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1001,19 +1010,19 @@
           <t>Sr DevOps Engineer</t>
         </is>
       </c>
-      <c r="D14" s="86" t="inlineStr">
+      <c r="D14" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460303379/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="84" t="inlineStr">
+      <c r="A15" s="87" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B15" s="85" t="n">
+      <c r="B15" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1021,19 +1030,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D15" s="86" t="inlineStr">
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459369335/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="84" t="inlineStr">
+      <c r="A16" s="87" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B16" s="85" t="n">
+      <c r="B16" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1041,19 +1050,19 @@
           <t>Dexcom are Hiring Technicians for Front End Night Shift</t>
         </is>
       </c>
-      <c r="D16" s="86" t="inlineStr">
+      <c r="D16" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4431256111/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="84" t="inlineStr">
+      <c r="A17" s="87" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B17" s="85" t="n">
+      <c r="B17" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1061,19 +1070,19 @@
           <t>Sr DevOps Engineer</t>
         </is>
       </c>
-      <c r="D17" s="86" t="inlineStr">
+      <c r="D17" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460300749/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="84" t="inlineStr">
+      <c r="A18" s="87" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B18" s="85" t="n">
+      <c r="B18" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1081,19 +1090,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D18" s="86" t="inlineStr">
+      <c r="D18" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458922088/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="84" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B19" s="85" t="n">
+      <c r="A19" s="87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B19" s="88" t="n">
         <v>46283</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1101,19 +1110,19 @@
           <t>Sr SW Design Quality Engineer</t>
         </is>
       </c>
-      <c r="D19" s="86" t="inlineStr">
+      <c r="D19" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450008915/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="84" t="inlineStr">
+      <c r="A20" s="87" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B20" s="85" t="n">
+      <c r="B20" s="88" t="n">
         <v>46282</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1121,7 +1130,7 @@
           <t>Manufacturing Technician 3 (Front End Night Shift)</t>
         </is>
       </c>
-      <c r="D20" s="86" t="inlineStr">
+      <c r="D20" s="89" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459362978/</t>
         </is>
@@ -2107,8 +2116,28 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="90" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B70" s="91" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Controls Technician 3 (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D70" s="92" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461204612/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D69"/>
+  <autoFilter ref="A1:D70"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -2178,6 +2207,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -734,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -766,12 +775,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="90" t="inlineStr">
+      <c r="A2" s="93" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B2" s="91" t="n">
+      <c r="B2" s="94" t="n">
         <v>46289</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -779,7 +788,7 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D2" s="92" t="inlineStr">
+      <c r="D2" s="95" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4469636551/</t>
         </is>
@@ -865,14 +874,1358 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B7" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Contact Center Platform Analyst</t>
+        </is>
+      </c>
+      <c r="D7" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462857053/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="96" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B8" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Galicia</t>
+        </is>
+      </c>
+      <c r="D8" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461768038/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="96" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B9" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Castilla y León</t>
+        </is>
+      </c>
+      <c r="D9" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461762151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B10" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Facility Maintenance Technician 2</t>
+        </is>
+      </c>
+      <c r="D10" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470284570/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="96" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B11" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Galicia</t>
+        </is>
+      </c>
+      <c r="D11" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461765127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Lead Legal Counsel - Employment</t>
+        </is>
+      </c>
+      <c r="D12" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4430864197/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="97" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Manager Materials</t>
+        </is>
+      </c>
+      <c r="D13" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472070795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B14" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Pricing Business Analyst</t>
+        </is>
+      </c>
+      <c r="D14" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470613503/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="96" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B15" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Galicia</t>
+        </is>
+      </c>
+      <c r="D15" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461754390/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="96" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B16" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Castilla y León</t>
+        </is>
+      </c>
+      <c r="D16" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461772012/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B17" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Account Payables Specialist</t>
+        </is>
+      </c>
+      <c r="D17" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470941961/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B18" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Senior Pricing Business Analyst</t>
+        </is>
+      </c>
+      <c r="D18" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470605704/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B19" s="97" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Staff Program Manager</t>
+        </is>
+      </c>
+      <c r="D19" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451501447/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="96" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B20" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D20" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Staff Business Financial Analyst - IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="D21" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461275610/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B22" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Product Support Representative, German Speaker</t>
+        </is>
+      </c>
+      <c r="D22" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4471672610/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="96" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B23" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Sourcing Manager</t>
+        </is>
+      </c>
+      <c r="D23" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461541376/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="96" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B24" s="97" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Field Value, Access and Policy Lead</t>
+        </is>
+      </c>
+      <c r="D24" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4469966430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B25" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Sr Project Lead - APAC</t>
+        </is>
+      </c>
+      <c r="D25" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461543326/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B26" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Product Support Representative, German Speaker</t>
+        </is>
+      </c>
+      <c r="D26" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4471681056/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B27" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Product Support Representative, German Speaker</t>
+        </is>
+      </c>
+      <c r="D27" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4471682057/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B28" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Product Support Representative, German Speaker</t>
+        </is>
+      </c>
+      <c r="D28" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4471666814/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B29" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>New Business Development Manager (Senior Analyst, Strategic Finance )</t>
+        </is>
+      </c>
+      <c r="D29" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434090087/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B30" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Staff Business Financial Analyst - IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="D30" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461277558/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="96" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B31" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>IT Service Desk Specialist 2</t>
+        </is>
+      </c>
+      <c r="D31" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4471495287/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="96" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B32" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D32" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B33" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Product Support Representative, German Speaker</t>
+        </is>
+      </c>
+      <c r="D33" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4471680112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="96" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B34" s="97" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>IT Procurement Analyst</t>
+        </is>
+      </c>
+      <c r="D34" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463313428/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B35" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Staff QA Engineer</t>
+        </is>
+      </c>
+      <c r="D35" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470672224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Staff Process Engineer</t>
+        </is>
+      </c>
+      <c r="D36" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461543337/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B37" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Sr Product Surveillance Engineer - Software QA</t>
+        </is>
+      </c>
+      <c r="D37" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470235354/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B38" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
+        </is>
+      </c>
+      <c r="D38" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B39" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
+        </is>
+      </c>
+      <c r="D39" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443109225/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B40" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Sr Process Engineer</t>
+        </is>
+      </c>
+      <c r="D40" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435122348/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Manager - Process Engineering</t>
+        </is>
+      </c>
+      <c r="D41" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470673233/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="96" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B42" s="97" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>IT Procurement Analyst</t>
+        </is>
+      </c>
+      <c r="D42" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463314400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Sr Staff QA Engineer</t>
+        </is>
+      </c>
+      <c r="D43" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470232400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B44" s="97" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Sr Supply Chain Analyst</t>
+        </is>
+      </c>
+      <c r="D44" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463169639/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="96" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B45" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
+        </is>
+      </c>
+      <c r="D45" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453079245/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B46" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 1</t>
+        </is>
+      </c>
+      <c r="D46" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470900552/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="96" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B47" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Intelligence Analyst - Geopolitical</t>
+        </is>
+      </c>
+      <c r="D47" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444046742/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B48" s="97" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing Associate 3</t>
+        </is>
+      </c>
+      <c r="D48" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472025090/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B49" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Director of Sensor Research</t>
+        </is>
+      </c>
+      <c r="D49" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427088373/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B50" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Stelo Retail and E-Commerce Distribution Director</t>
+        </is>
+      </c>
+      <c r="D50" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470668480/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B51" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Sr Business Process Analyst</t>
+        </is>
+      </c>
+      <c r="D51" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470277781/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="96" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B52" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Planning Manager</t>
+        </is>
+      </c>
+      <c r="D52" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454556094/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="96" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B53" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
+        </is>
+      </c>
+      <c r="D53" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463699027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Sr Product Surveillance Engineer - Software QA</t>
+        </is>
+      </c>
+      <c r="D54" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470232428/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B55" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 4</t>
+        </is>
+      </c>
+      <c r="D55" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461760270/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="96" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B56" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
+        </is>
+      </c>
+      <c r="D56" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453091134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B57" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Sr IT Project Manager</t>
+        </is>
+      </c>
+      <c r="D57" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="96" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B58" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Field Value, Access and Policy Lead</t>
+        </is>
+      </c>
+      <c r="D58" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4469461250/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Process Development Engineer</t>
+        </is>
+      </c>
+      <c r="D59" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443563067/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="96" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B60" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 2</t>
+        </is>
+      </c>
+      <c r="D60" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470688971/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B61" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Sr Staff Endpoint Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D61" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453076275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B62" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D62" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436151688/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="97" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager QA Engineering</t>
+        </is>
+      </c>
+      <c r="D63" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4469971334/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="96" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B64" s="97" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 3 (Front End Day Shift)</t>
+        </is>
+      </c>
+      <c r="D64" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="96" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B65" s="97" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Senior Telecom Engineer (Genesys Cloud)</t>
+        </is>
+      </c>
+      <c r="D65" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463370784/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B66" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Corporate Compliance Analyst (Maternity cover)</t>
+        </is>
+      </c>
+      <c r="D66" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470452123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B67" s="97" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Sr Staff Endpoint Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D67" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453090143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B68" s="97" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 2 - 2A Shift: Sun-Tues, every other Sat, Can work anytime from 5pm-5am (Open)</t>
+        </is>
+      </c>
+      <c r="D68" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4470244088/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="96" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B69" s="97" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Product Support Representative, Dutch Speaker</t>
+        </is>
+      </c>
+      <c r="D69" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4471666834/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="96" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B70" s="97" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Lab Supervisor (Manufacturing) - Back End Day Shift</t>
+        </is>
+      </c>
+      <c r="D70" s="98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463359959/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D6"/>
+  <autoFilter ref="A1:D70"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -743,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -775,12 +784,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="93" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B2" s="94" t="n">
+      <c r="A2" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B2" s="97" t="n">
         <v>46289</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -788,19 +797,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D2" s="95" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4469636551/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="93" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B3" s="94" t="n">
+      <c r="A3" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B3" s="97" t="n">
         <v>46290</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -808,19 +817,19 @@
           <t>Senior Legal Counsel</t>
         </is>
       </c>
-      <c r="D3" s="95" t="inlineStr">
+      <c r="D3" s="98" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4470052741/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="93" t="inlineStr">
+      <c r="A4" s="96" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B4" s="94" t="n">
+      <c r="B4" s="97" t="n">
         <v>46290</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -828,19 +837,19 @@
           <t>Quality Assurance Analyst 1</t>
         </is>
       </c>
-      <c r="D4" s="95" t="inlineStr">
+      <c r="D4" s="98" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4471876062/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="93" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B5" s="94" t="n">
+      <c r="A5" s="96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B5" s="97" t="n">
         <v>46290</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -848,19 +857,19 @@
           <t>Manufacturing Technician 4 ( Dobson ) Night Shift 2B - Wednesday to Friday every other Saturday from 5PM - 5AM</t>
         </is>
       </c>
-      <c r="D5" s="95" t="inlineStr">
+      <c r="D5" s="98" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4470066278/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="93" t="inlineStr">
+      <c r="A6" s="96" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B6" s="94" t="n">
+      <c r="B6" s="97" t="n">
         <v>46290</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -868,7 +877,7 @@
           <t>Senior Enterprise Applications Developer (Web Applications)</t>
         </is>
       </c>
-      <c r="D6" s="95" t="inlineStr">
+      <c r="D6" s="98" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4471880000/</t>
         </is>
@@ -897,300 +906,300 @@
     <row r="8">
       <c r="A8" s="96" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B8" s="97" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Territory Sales Manager - Galicia</t>
+          <t>Manager Materials</t>
         </is>
       </c>
       <c r="D8" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461768038/</t>
+          <t>https://www.linkedin.com/jobs/view/4472070795/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="96" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B9" s="97" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Territory Sales Manager - Castilla y León</t>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
       <c r="D9" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461762151/</t>
+          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="96" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B10" s="97" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Facility Maintenance Technician 2</t>
+          <t>Product Support Representative, German Speaker</t>
         </is>
       </c>
       <c r="D10" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470284570/</t>
+          <t>https://www.linkedin.com/jobs/view/4471672610/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="96" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B11" s="97" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Territory Sales Manager - Galicia</t>
+          <t>Product Support Representative, German Speaker</t>
         </is>
       </c>
       <c r="D11" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461765127/</t>
+          <t>https://www.linkedin.com/jobs/view/4471681056/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="96" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B12" s="97" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Lead Legal Counsel - Employment</t>
+          <t>Product Support Representative, German Speaker</t>
         </is>
       </c>
       <c r="D12" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4430864197/</t>
+          <t>https://www.linkedin.com/jobs/view/4471682057/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="96" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B13" s="97" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Manager Materials</t>
+          <t>Product Support Representative, German Speaker</t>
         </is>
       </c>
       <c r="D13" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472070795/</t>
+          <t>https://www.linkedin.com/jobs/view/4471666814/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="96" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B14" s="97" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Pricing Business Analyst</t>
+          <t>IT Service Desk Specialist 2</t>
         </is>
       </c>
       <c r="D14" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470613503/</t>
+          <t>https://www.linkedin.com/jobs/view/4471495287/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="96" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B15" s="97" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Territory Sales Manager - Galicia</t>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
       <c r="D15" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461754390/</t>
+          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="96" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B16" s="97" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Territory Sales Manager - Castilla y León</t>
+          <t>Product Support Representative, German Speaker</t>
         </is>
       </c>
       <c r="D16" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461772012/</t>
+          <t>https://www.linkedin.com/jobs/view/4471680112/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="96" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B17" s="97" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Account Payables Specialist</t>
+          <t>IT Procurement Analyst</t>
         </is>
       </c>
       <c r="D17" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470941961/</t>
+          <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="96" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B18" s="97" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Senior Pricing Business Analyst</t>
+          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
         </is>
       </c>
       <c r="D18" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470605704/</t>
+          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="96" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B19" s="97" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Staff Program Manager</t>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
       <c r="D19" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4451501447/</t>
+          <t>https://www.linkedin.com/jobs/view/4443109225/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="96" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B20" s="97" t="n">
-        <v>46291</v>
+        <v>46289</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+          <t>Sr Process Engineer</t>
         </is>
       </c>
       <c r="D20" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
+          <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="96" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B21" s="97" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Staff Business Financial Analyst - IT Infrastructure</t>
+          <t>IT Procurement Analyst</t>
         </is>
       </c>
       <c r="D21" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461275610/</t>
+          <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="96" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B22" s="97" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Product Support Representative, German Speaker</t>
+          <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
       <c r="D22" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471672610/</t>
+          <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
@@ -1201,116 +1210,116 @@
         </is>
       </c>
       <c r="B23" s="97" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Sourcing Manager</t>
+          <t>Intelligence Analyst - Geopolitical</t>
         </is>
       </c>
       <c r="D23" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461541376/</t>
+          <t>https://www.linkedin.com/jobs/view/4444046742/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="96" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B24" s="97" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Field Value, Access and Policy Lead</t>
+          <t>Manufacturing Associate 3</t>
         </is>
       </c>
       <c r="D24" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4469966430/</t>
+          <t>https://www.linkedin.com/jobs/view/4472025090/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="96" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B25" s="97" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Sr Project Lead - APAC</t>
+          <t>Director of Sensor Research</t>
         </is>
       </c>
       <c r="D25" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461543326/</t>
+          <t>https://www.linkedin.com/jobs/view/4427088373/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="96" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B26" s="97" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Product Support Representative, German Speaker</t>
+          <t>Planning Manager</t>
         </is>
       </c>
       <c r="D26" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471681056/</t>
+          <t>https://www.linkedin.com/jobs/view/4454556094/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="96" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B27" s="97" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Product Support Representative, German Speaker</t>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
       <c r="D27" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471682057/</t>
+          <t>https://www.linkedin.com/jobs/view/4463699027/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="96" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B28" s="97" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Product Support Representative, German Speaker</t>
+          <t>Sr IT Project Manager</t>
         </is>
       </c>
       <c r="D28" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471666814/</t>
+          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
         </is>
       </c>
     </row>
@@ -1321,16 +1330,16 @@
         </is>
       </c>
       <c r="B29" s="97" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>New Business Development Manager (Senior Analyst, Strategic Finance )</t>
+          <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
       <c r="D29" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4434090087/</t>
+          <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
@@ -1341,56 +1350,56 @@
         </is>
       </c>
       <c r="B30" s="97" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Staff Business Financial Analyst - IT Infrastructure</t>
+          <t>SW Test Development Engineer 2</t>
         </is>
       </c>
       <c r="D30" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4461277558/</t>
+          <t>https://www.linkedin.com/jobs/view/4436151688/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="96" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B31" s="97" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>IT Service Desk Specialist 2</t>
+          <t>Engineering Technician 3 (Front End Day Shift)</t>
         </is>
       </c>
       <c r="D31" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471495287/</t>
+          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="96" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B32" s="97" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+          <t>Senior Telecom Engineer (Genesys Cloud)</t>
         </is>
       </c>
       <c r="D32" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
+          <t>https://www.linkedin.com/jobs/view/4463370784/</t>
         </is>
       </c>
     </row>
@@ -1405,19 +1414,19 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Product Support Representative, German Speaker</t>
+          <t>Product Support Representative, Dutch Speaker</t>
         </is>
       </c>
       <c r="D33" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471680112/</t>
+          <t>https://www.linkedin.com/jobs/view/4471666834/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="96" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B34" s="97" t="n">
@@ -1425,737 +1434,597 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>IT Procurement Analyst</t>
+          <t>Lab Supervisor (Manufacturing) - Back End Day Shift</t>
         </is>
       </c>
       <c r="D34" s="98" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463313428/</t>
+          <t>https://www.linkedin.com/jobs/view/4463359959/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B35" s="97" t="n">
-        <v>46288</v>
+      <c r="A35" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B35" s="100" t="n">
+        <v>46294</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Staff QA Engineer</t>
-        </is>
-      </c>
-      <c r="D35" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470672224/</t>
+          <t>Sr. Planner Analyst</t>
+        </is>
+      </c>
+      <c r="D35" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473061549/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="97" t="n">
-        <v>46287</v>
+      <c r="A36" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="100" t="n">
+        <v>46295</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Staff Process Engineer</t>
-        </is>
-      </c>
-      <c r="D36" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4461543337/</t>
+          <t>Manager Internal Audit (IT)</t>
+        </is>
+      </c>
+      <c r="D36" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473579857/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B37" s="97" t="n">
-        <v>46287</v>
+      <c r="A37" s="99" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B37" s="100" t="n">
+        <v>46293</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Sr Product Surveillance Engineer - Software QA</t>
-        </is>
-      </c>
-      <c r="D37" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470235354/</t>
+          <t>Territory Business Manager</t>
+        </is>
+      </c>
+      <c r="D37" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464350389/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B38" s="97" t="n">
-        <v>46291</v>
+      <c r="A38" s="99" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B38" s="100" t="n">
+        <v>46294</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
-        </is>
-      </c>
-      <c r="D38" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
+          <t>Sr Workforce Management Analyst (Scheduler)</t>
+        </is>
+      </c>
+      <c r="D38" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473211143/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="96" t="inlineStr">
+      <c r="A39" s="99" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B39" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>AR Specialist 1</t>
+        </is>
+      </c>
+      <c r="D39" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473724594/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Facility Maintenance Technician 3</t>
+        </is>
+      </c>
+      <c r="D40" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473587635/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Sr Workplace Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="D41" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="99" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B42" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Senior Facilities Technician (Front End Days)</t>
+        </is>
+      </c>
+      <c r="D42" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473942583/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="99" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B43" s="100" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Quality Assurance Analyst 2</t>
+        </is>
+      </c>
+      <c r="D43" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473214091/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B44" s="100" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Planner Analyst</t>
+        </is>
+      </c>
+      <c r="D44" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473071241/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="99" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B39" s="97" t="n">
-        <v>46289</v>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
-        </is>
-      </c>
-      <c r="D39" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443109225/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="96" t="inlineStr">
+      <c r="B45" s="100" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Senior Manager, Customer Service Enablement &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D45" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473010090/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="99" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B40" s="97" t="n">
-        <v>46289</v>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Sr Process Engineer</t>
-        </is>
-      </c>
-      <c r="D40" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4435122348/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="97" t="n">
-        <v>46288</v>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Manager - Process Engineering</t>
-        </is>
-      </c>
-      <c r="D41" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470673233/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="96" t="inlineStr">
+      <c r="B46" s="100" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Manufacturing</t>
+        </is>
+      </c>
+      <c r="D46" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4474140193/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B47" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Hardware Engineer</t>
+        </is>
+      </c>
+      <c r="D47" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473944585/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="99" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B42" s="97" t="n">
+      <c r="B48" s="100" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="D48" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473271365/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="99" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B49" s="100" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 3</t>
+        </is>
+      </c>
+      <c r="D49" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473060599/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="99" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B50" s="100" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Business Process Analyst</t>
+        </is>
+      </c>
+      <c r="D50" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473098746/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B51" s="100" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing Associate 3 - Monday-Friday 6AM-2:30PM</t>
+        </is>
+      </c>
+      <c r="D51" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473013016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Hardware Engineer 2</t>
+        </is>
+      </c>
+      <c r="D52" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473581818/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B53" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 1</t>
+        </is>
+      </c>
+      <c r="D53" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473718736/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="100" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing Technician 2</t>
+        </is>
+      </c>
+      <c r="D54" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472795834/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B55" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager, Partnership Operations and Contracting</t>
+        </is>
+      </c>
+      <c r="D55" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464670623/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B56" s="100" t="n">
         <v>46290</v>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>IT Procurement Analyst</t>
-        </is>
-      </c>
-      <c r="D42" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463314400/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="97" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Sr Staff QA Engineer</t>
-        </is>
-      </c>
-      <c r="D43" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470232400/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="96" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Staff Medical Device Engineer - R&amp;D Process Development</t>
+        </is>
+      </c>
+      <c r="D56" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472087255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="99" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B57" s="100" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Kundenservice Medizintechnik (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D57" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472613048/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="99" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B44" s="97" t="n">
-        <v>46290</v>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Sr Supply Chain Analyst</t>
-        </is>
-      </c>
-      <c r="D44" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463169639/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="96" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B45" s="97" t="n">
-        <v>46288</v>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
-        </is>
-      </c>
-      <c r="D45" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453079245/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="96" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B46" s="97" t="n">
-        <v>46288</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Engineering Technician 1</t>
-        </is>
-      </c>
-      <c r="D46" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470900552/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="96" t="inlineStr">
+      <c r="B58" s="100" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>QC Inspector 2</t>
+        </is>
+      </c>
+      <c r="D58" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472497423/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="100" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Software QA Engineer 2</t>
+        </is>
+      </c>
+      <c r="D59" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="99" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B47" s="97" t="n">
-        <v>46291</v>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Intelligence Analyst - Geopolitical</t>
-        </is>
-      </c>
-      <c r="D47" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4444046742/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="96" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B48" s="97" t="n">
-        <v>46290</v>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Manufacturing Associate 3</t>
-        </is>
-      </c>
-      <c r="D48" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4472025090/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B49" s="97" t="n">
-        <v>46289</v>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Director of Sensor Research</t>
-        </is>
-      </c>
-      <c r="D49" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4427088373/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B50" s="97" t="n">
-        <v>46288</v>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Stelo Retail and E-Commerce Distribution Director</t>
-        </is>
-      </c>
-      <c r="D50" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470668480/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="96" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B51" s="97" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Sr Business Process Analyst</t>
-        </is>
-      </c>
-      <c r="D51" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470277781/</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="96" t="inlineStr">
+      <c r="B60" s="100" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Sr Enterprise Developer (Power Platform Developer)</t>
+        </is>
+      </c>
+      <c r="D60" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="99" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B52" s="97" t="n">
-        <v>46291</v>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Planning Manager</t>
-        </is>
-      </c>
-      <c r="D52" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4454556094/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="96" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B53" s="97" t="n">
-        <v>46291</v>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
-        </is>
-      </c>
-      <c r="D53" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463699027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B54" s="97" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Sr Product Surveillance Engineer - Software QA</t>
-        </is>
-      </c>
-      <c r="D54" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470232428/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="96" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B55" s="97" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Engineering Technician 4</t>
-        </is>
-      </c>
-      <c r="D55" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4461760270/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="96" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B56" s="97" t="n">
-        <v>46288</v>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
-        </is>
-      </c>
-      <c r="D56" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453091134/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="96" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B57" s="97" t="n">
-        <v>46291</v>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Sr IT Project Manager</t>
-        </is>
-      </c>
-      <c r="D57" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="96" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B58" s="97" t="n">
-        <v>46288</v>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Field Value, Access and Policy Lead</t>
-        </is>
-      </c>
-      <c r="D58" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4469461250/</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="97" t="n">
-        <v>46289</v>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Senior Staff Process Development Engineer</t>
-        </is>
-      </c>
-      <c r="D59" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443563067/</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="96" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B60" s="97" t="n">
-        <v>46288</v>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>QA Inspector 2</t>
-        </is>
-      </c>
-      <c r="D60" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470688971/</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B61" s="97" t="n">
-        <v>46288</v>
+      <c r="B61" s="100" t="n">
+        <v>46295</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Sr Staff Endpoint Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D61" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453076275/</t>
+          <t>Senior Process Engineer - Chemistry</t>
+        </is>
+      </c>
+      <c r="D61" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473935971/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B62" s="97" t="n">
-        <v>46291</v>
+      <c r="A62" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B62" s="100" t="n">
+        <v>46294</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>SW Test Development Engineer 2</t>
-        </is>
-      </c>
-      <c r="D62" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4436151688/</t>
+          <t>Lab Technician 2 - Monday through Friday 7AM to 3:30PM</t>
+        </is>
+      </c>
+      <c r="D62" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473063485/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="97" t="n">
-        <v>46286</v>
+      <c r="A63" s="99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="100" t="n">
+        <v>46295</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Sr Manager QA Engineering</t>
-        </is>
-      </c>
-      <c r="D63" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4469971334/</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="96" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B64" s="97" t="n">
-        <v>46291</v>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Engineering Technician 3 (Front End Day Shift)</t>
-        </is>
-      </c>
-      <c r="D64" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="96" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B65" s="97" t="n">
-        <v>46290</v>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Senior Telecom Engineer (Genesys Cloud)</t>
-        </is>
-      </c>
-      <c r="D65" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463370784/</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="96" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B66" s="97" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Compliance Analyst (Maternity cover)</t>
-        </is>
-      </c>
-      <c r="D66" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470452123/</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B67" s="97" t="n">
-        <v>46288</v>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Sr Staff Endpoint Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D67" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453090143/</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B68" s="97" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>QA Inspector 2 - 2A Shift: Sun-Tues, every other Sat, Can work anytime from 5pm-5am (Open)</t>
-        </is>
-      </c>
-      <c r="D68" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4470244088/</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="96" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B69" s="97" t="n">
-        <v>46289</v>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Product Support Representative, Dutch Speaker</t>
-        </is>
-      </c>
-      <c r="D69" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4471666834/</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="96" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B70" s="97" t="n">
-        <v>46290</v>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>Lab Supervisor (Manufacturing) - Back End Day Shift</t>
-        </is>
-      </c>
-      <c r="D70" s="98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463359959/</t>
+          <t>Senior Analytical Scientist</t>
+        </is>
+      </c>
+      <c r="D63" s="101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473940805/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D70"/>
+  <autoFilter ref="A1:D63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -2219,13 +2088,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
